--- a/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
+++ b/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H481"/>
+  <dimension ref="A1:H505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20721,6 +20721,1074 @@
         </is>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>481</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>D25</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>p042_q45</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Hỏi có bao nhiêu giá trị $m$ nguyên trong đoạn $[-2017;2017]$ để phương trình $\log(mx)=2\log(x+1)$ có nghiệm duy nhất?
+A. $2018$.
+B. $2017$.
+C. $4035$.
+D. $2019$.</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>A. $2018$.</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1, x\ne0$. $\log(mx)=2\log(x+1)\Leftrightarrow mx=(x+1)^2 \Leftrightarrow m=\dfrac{(x+1)^2}{x}=f(x)$.
+$f'(x)=\dfrac{x^2-1}{x^2}=0\Leftrightarrow x=\pm1$ (chỉ nhận $x=1$ do điều kiện). $f(1)=4$, $f\to-\infty$ khi $x\to-1^+$, $f\to+\infty$ khi $x\to0^-$ hoặc $x\to+\infty$.
+Phương trình có nghiệm duy nhất khi $m=4$ hoặc $m&lt;0$. Với $m\in[-2017;2017]\cap\mathbb{Z}$, có $2017$ giá trị âm cộng thêm $m=4$, tổng cộng $2018$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>482</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>D25</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>p042_q45</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Hỏi có bao nhiêu giá trị $m$ nguyên trong đoạn $[-100;100]$ để phương trình $\log(mx)=2\log(x+2)$ có nghiệm duy nhất?
+A. $100$.
+B. $101$.
+C. $102$.
+D. $201$.</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>B. $101$.</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-2, x\ne0$. $\log(mx)=2\log(x+2)\Leftrightarrow mx=(x+2)^2 \Leftrightarrow m=\dfrac{(x+2)^2}{x}=f(x)$.
+$f'(x)=\dfrac{x^2-4}{x^2}=0\Leftrightarrow x=\pm2$ (chỉ nhận $x=2$ do điều kiện). $f(2)=8$, $f\to-\infty$ khi $x\to-2^+$, $f\to+\infty$ khi $x\to0^-$ hoặc $x\to+\infty$.
+Phương trình có nghiệm duy nhất khi $m=8$ hoặc $m&lt;0$. Với $m\in[-100;100]\cap\mathbb{Z}$, có $100$ giá trị âm cộng thêm $m=8$, tổng cộng $101$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>483</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>D25</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>p042_q45</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Hỏi có bao nhiêu giá trị $m$ nguyên trong đoạn $[-50;50]$ để phương trình $\log(mx)=2\log(x+1)$ có nghiệm duy nhất?
+A. $52$.
+B. $50$.
+C. $101$.
+D. $51$.</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>D. $51$.</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1, x\ne0$. $\log(mx)=2\log(x+1)\Leftrightarrow mx=(x+1)^2 \Leftrightarrow m=\dfrac{(x+1)^2}{x}=f(x)$.
+$f'(x)=\dfrac{x^2-1}{x^2}=0\Leftrightarrow x=\pm1$ (chỉ nhận $x=1$ do điều kiện). $f(1)=4$, $f\to-\infty$ khi $x\to-1^+$, $f\to+\infty$ khi $x\to0^-$ hoặc $x\to+\infty$.
+Phương trình có nghiệm duy nhất khi $m=4$ hoặc $m&lt;0$. Với $m\in[-50;50]\cap\mathbb{Z}$, có $50$ giá trị âm cộng thêm $m=4$, tổng cộng $51$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>484</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>D25</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>p042_q45</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Hỏi có bao nhiêu giá trị $m$ nguyên trong đoạn $[-200;200]$ để phương trình $\log(mx)=2\log(x+3)$ có nghiệm duy nhất?
+A. $401$.
+B. $202$.
+C. $201$.
+D. $200$.</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>C. $201$.</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-3, x\ne0$. $\log(mx)=2\log(x+3)\Leftrightarrow mx=(x+3)^2 \Leftrightarrow m=\dfrac{(x+3)^2}{x}=f(x)$.
+$f'(x)=\dfrac{x^2-9}{x^2}=0\Leftrightarrow x=\pm3$ (chỉ nhận $x=3$ do điều kiện). $f(3)=12$, $f\to-\infty$ khi $x\to-3^+$, $f\to+\infty$ khi $x\to0^-$ hoặc $x\to+\infty$.
+Phương trình có nghiệm duy nhất khi $m=12$ hoặc $m&lt;0$. Với $m\in[-200;200]\cap\mathbb{Z}$, có $200$ giá trị âm cộng thêm $m=12$, tổng cộng $201$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>485</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>D25</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>p042_q45</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Hỏi có bao nhiêu giá trị $m$ nguyên trong đoạn $[-30;30]$ để phương trình $\log(mx)=2\log(x+1)$ có nghiệm duy nhất?
+A. $30$.
+B. $31$.
+C. $61$.
+D. $32$.</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>B. $31$.</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1, x\ne0$. $\log(mx)=2\log(x+1)\Leftrightarrow mx=(x+1)^2 \Leftrightarrow m=\dfrac{(x+1)^2}{x}=f(x)$.
+$f'(x)=\dfrac{x^2-1}{x^2}=0\Leftrightarrow x=\pm1$ (chỉ nhận $x=1$ do điều kiện). $f(1)=4$, $f\to-\infty$ khi $x\to-1^+$, $f\to+\infty$ khi $x\to0^-$ hoặc $x\to+\infty$.
+Phương trình có nghiệm duy nhất khi $m=4$ hoặc $m&lt;0$. Với $m\in[-30;30]\cap\mathbb{Z}$, có $30$ giá trị âm cộng thêm $m=4$, tổng cộng $31$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>486</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>D25</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>p042_q45</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Hỏi có bao nhiêu giá trị $m$ nguyên trong đoạn $[-500;500]$ để phương trình $\log(mx)=2\log(x+2)$ có nghiệm duy nhất?
+A. $1001$.
+B. $500$.
+C. $502$.
+D. $501$.</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>D. $501$.</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-2, x\ne0$. $\log(mx)=2\log(x+2)\Leftrightarrow mx=(x+2)^2 \Leftrightarrow m=\dfrac{(x+2)^2}{x}=f(x)$.
+$f'(x)=\dfrac{x^2-4}{x^2}=0\Leftrightarrow x=\pm2$ (chỉ nhận $x=2$ do điều kiện). $f(2)=8$, $f\to-\infty$ khi $x\to-2^+$, $f\to+\infty$ khi $x\to0^-$ hoặc $x\to+\infty$.
+Phương trình có nghiệm duy nhất khi $m=8$ hoặc $m&lt;0$. Với $m\in[-500;500]\cap\mathbb{Z}$, có $500$ giá trị âm cộng thêm $m=8$, tổng cộng $501$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>487</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>D41</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>p090_q47</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $0\le x\le 2020$ và $\log_{3}(3x+3)+x=2y+9^y$?
+A. $3$.
+B. $2020$.
+C. $5$.
+D. $4$.</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>D. $4$.</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>$\log_{3}(3x+3)+x=2y+3^{2y} \Leftrightarrow 1+\log_{3}(x+1)+x=2y+3^{2y}$. Đặt $t=\log_{3}(x+1)$ suy ra $t+3^t=2y+3^{2y}$. Xét $f(h)=h+3^h$ đồng biến trên $\mathbb{R}$ nên $t=2y \Leftrightarrow x+1=3^{2y}$. Do $0\le x\le2020$ nên $0\le y\le\log_{3}(2021)/2\approx3.46$, suy ra $y\in\{0,1,\ldots,3\}$, có $4$ cặp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>488</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>D41</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>p090_q47</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $0\le x\le 100$ và $\log_{2}(2x+2)+x=2y+4^y$?
+A. $5$.
+B. $4$.
+C. $3$.
+D. $100$.</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>B. $4$.</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>$\log_{2}(2x+2)+x=2y+2^{2y} \Leftrightarrow 1+\log_{2}(x+1)+x=2y+2^{2y}$. Đặt $t=\log_{2}(x+1)$ suy ra $t+2^t=2y+2^{2y}$. Xét $f(h)=h+2^h$ đồng biến trên $\mathbb{R}$ nên $t=2y \Leftrightarrow x+1=2^{2y}$. Do $0\le x\le100$ nên $0\le y\le\log_{2}(101)/2\approx3.33$, suy ra $y\in\{0,1,\ldots,3\}$, có $4$ cặp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>489</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>D41</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>p090_q47</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $0\le x\le 500$ và $\log_{3}(3x+3)+x=2y+9^y$?
+A. $4$.
+B. $500$.
+C. $2$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>$\log_{3}(3x+3)+x=2y+3^{2y} \Leftrightarrow 1+\log_{3}(x+1)+x=2y+3^{2y}$. Đặt $t=\log_{3}(x+1)$ suy ra $t+3^t=2y+3^{2y}$. Xét $f(h)=h+3^h$ đồng biến trên $\mathbb{R}$ nên $t=2y \Leftrightarrow x+1=3^{2y}$. Do $0\le x\le500$ nên $0\le y\le\log_{3}(501)/2\approx2.83$, suy ra $y\in\{0,1,\ldots,2\}$, có $3$ cặp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>490</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>D41</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>p090_q47</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $0\le x\le 50$ và $\log_{2}(2x+2)+x=2y+4^y$?
+A. $2$.
+B. $4$.
+C. $50$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>$\log_{2}(2x+2)+x=2y+2^{2y} \Leftrightarrow 1+\log_{2}(x+1)+x=2y+2^{2y}$. Đặt $t=\log_{2}(x+1)$ suy ra $t+2^t=2y+2^{2y}$. Xét $f(h)=h+2^h$ đồng biến trên $\mathbb{R}$ nên $t=2y \Leftrightarrow x+1=2^{2y}$. Do $0\le x\le50$ nên $0\le y\le\log_{2}(51)/2\approx2.84$, suy ra $y\in\{0,1,\ldots,2\}$, có $3$ cặp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>D41</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>p090_q47</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $0\le x\le 1000$ và $\log_{5}(5x+5)+x=2y+25^y$?
+A. $2$.
+B. $3$.
+C. $1000$.
+D. $4$.</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>B. $3$.</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>$\log_{5}(5x+5)+x=2y+5^{2y} \Leftrightarrow 1+\log_{5}(x+1)+x=2y+5^{2y}$. Đặt $t=\log_{5}(x+1)$ suy ra $t+5^t=2y+5^{2y}$. Xét $f(h)=h+5^h$ đồng biến trên $\mathbb{R}$ nên $t=2y \Leftrightarrow x+1=5^{2y}$. Do $0\le x\le1000$ nên $0\le y\le\log_{5}(1001)/2\approx2.15$, suy ra $y\in\{0,1,\ldots,2\}$, có $3$ cặp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>D41</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>p090_q47</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $0\le x\le 200$ và $\log_{2}(2x+2)+x=2y+4^y$?
+A. $5$.
+B. $3$.
+C. $4$.
+D. $200$.</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>C. $4$.</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>$\log_{2}(2x+2)+x=2y+2^{2y} \Leftrightarrow 1+\log_{2}(x+1)+x=2y+2^{2y}$. Đặt $t=\log_{2}(x+1)$ suy ra $t+2^t=2y+2^{2y}$. Xét $f(h)=h+2^h$ đồng biến trên $\mathbb{R}$ nên $t=2y \Leftrightarrow x+1=2^{2y}$. Do $0\le x\le200$ nên $0\le y\le\log_{2}(201)/2\approx3.83$, suy ra $y\in\{0,1,\ldots,3\}$, có $4$ cặp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>D74</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>p179_q37</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\log_{9}x^2-\log_{3}(6x-1)=-\log_{3}m$ ($m$ là tham số thực). Có tất cả bao nhiêu giá trị nguyên của $m$ để phương trình đã cho có nghiệm?
+A. $Vô số$.
+B. $7$.
+C. $5$.
+D. $6$.</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>C. $5$.</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;\dfrac1{6}, m&gt;0$. $\log_{3}x+\log_{3}m=\log_{3}(6x-1)\Leftrightarrow mx=6x-1\Leftrightarrow x(6-m)=1$. Với $m\ne6$: $x=\dfrac1{6-m}&gt;\dfrac1{6}\Leftrightarrow 0&lt;m&lt;6$. Vậy $m\in\{1,\ldots,5\}$, có $5$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>D74</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>p179_q37</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\log_{4}x^2-\log_{2}(5x-1)=-\log_{2}m$ ($m$ là tham số thực). Có tất cả bao nhiêu giá trị nguyên của $m$ để phương trình đã cho có nghiệm?
+A. $5$.
+B. $4$.
+C. $6$.
+D. $Vô số$.</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>B. $4$.</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;\dfrac1{5}, m&gt;0$. $\log_{2}x+\log_{2}m=\log_{2}(5x-1)\Leftrightarrow mx=5x-1\Leftrightarrow x(5-m)=1$. Với $m\ne5$: $x=\dfrac1{5-m}&gt;\dfrac1{5}\Leftrightarrow 0&lt;m&lt;5$. Vậy $m\in\{1,\ldots,4\}$, có $4$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>D74</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>p179_q37</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\log_{9}x^2-\log_{3}(8x-1)=-\log_{3}m$ ($m$ là tham số thực). Có tất cả bao nhiêu giá trị nguyên của $m$ để phương trình đã cho có nghiệm?
+A. $9$.
+B. $Vô số$.
+C. $8$.
+D. $7$.</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>D. $7$.</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;\dfrac1{8}, m&gt;0$. $\log_{3}x+\log_{3}m=\log_{3}(8x-1)\Leftrightarrow mx=8x-1\Leftrightarrow x(8-m)=1$. Với $m\ne8$: $x=\dfrac1{8-m}&gt;\dfrac1{8}\Leftrightarrow 0&lt;m&lt;8$. Vậy $m\in\{1,\ldots,7\}$, có $7$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>D74</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>p179_q37</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\log_{25}x^2-\log_{5}(10x-1)=-\log_{5}m$ ($m$ là tham số thực). Có tất cả bao nhiêu giá trị nguyên của $m$ để phương trình đã cho có nghiệm?
+A. $Vô số$.
+B. $10$.
+C. $11$.
+D. $9$.</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>D. $9$.</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;\dfrac1{10}, m&gt;0$. $\log_{5}x+\log_{5}m=\log_{5}(10x-1)\Leftrightarrow mx=10x-1\Leftrightarrow x(10-m)=1$. Với $m\ne10$: $x=\dfrac1{10-m}&gt;\dfrac1{10}\Leftrightarrow 0&lt;m&lt;10$. Vậy $m\in\{1,\ldots,9\}$, có $9$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>D74</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>p179_q37</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\log_{4}x^2-\log_{2}(7x-1)=-\log_{2}m$ ($m$ là tham số thực). Có tất cả bao nhiêu giá trị nguyên của $m$ để phương trình đã cho có nghiệm?
+A. $7$.
+B. $Vô số$.
+C. $6$.
+D. $8$.</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>C. $6$.</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;\dfrac1{7}, m&gt;0$. $\log_{2}x+\log_{2}m=\log_{2}(7x-1)\Leftrightarrow mx=7x-1\Leftrightarrow x(7-m)=1$. Với $m\ne7$: $x=\dfrac1{7-m}&gt;\dfrac1{7}\Leftrightarrow 0&lt;m&lt;7$. Vậy $m\in\{1,\ldots,6\}$, có $6$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>498</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>D74</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>p179_q37</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\log_{9}x^2-\log_{3}(4x-1)=-\log_{3}m$ ($m$ là tham số thực). Có tất cả bao nhiêu giá trị nguyên của $m$ để phương trình đã cho có nghiệm?
+A. $Vô số$.
+B. $3$.
+C. $4$.
+D. $5$.</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>B. $3$.</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;\dfrac1{4}, m&gt;0$. $\log_{3}x+\log_{3}m=\log_{3}(4x-1)\Leftrightarrow mx=4x-1\Leftrightarrow x(4-m)=1$. Với $m\ne4$: $x=\dfrac1{4-m}&gt;\dfrac1{4}\Leftrightarrow 0&lt;m&lt;4$. Vậy $m\in\{1,\ldots,3\}$, có $3$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>499</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>D92</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>p240_q31</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên thuộc tập xác định của hàm số $y=\log[(6-x)(x+2)]$?
+A. $Vô số$.
+B. $8$.
+C. $6$.
+D. $7$.</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>D. $7$.</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Điều kiện $(6-x)(x+2)&gt;0\Leftrightarrow -2&lt;x&lt;6\Rightarrow \mathscr{D}=(-2;6)$. Vậy có $7$ số nguyên thuộc tập xác định.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>500</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>D92</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>p240_q31</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên thuộc tập xác định của hàm số $y=\log[(10-x)(x+3)]$?
+A. $12$.
+B. $13$.
+C. $11$.
+D. $Vô số$.</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>A. $12$.</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Điều kiện $(10-x)(x+3)&gt;0\Leftrightarrow -3&lt;x&lt;10\Rightarrow \mathscr{D}=(-3;10)$. Vậy có $12$ số nguyên thuộc tập xác định.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>501</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>D92</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>p240_q31</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên thuộc tập xác định của hàm số $y=\log[(8-x)(x+5)]$?
+A. $12$.
+B. $11$.
+C. $13$.
+D. $Vô số$.</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>A. $12$.</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Điều kiện $(8-x)(x+5)&gt;0\Leftrightarrow -5&lt;x&lt;8\Rightarrow \mathscr{D}=(-5;8)$. Vậy có $12$ số nguyên thuộc tập xác định.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>502</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>D92</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>p240_q31</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên thuộc tập xác định của hàm số $y=\log[(15-x)(x+4)]$?
+A. $Vô số$.
+B. $17$.
+C. $19$.
+D. $18$.</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>D. $18$.</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Điều kiện $(15-x)(x+4)&gt;0\Leftrightarrow -4&lt;x&lt;15\Rightarrow \mathscr{D}=(-4;15)$. Vậy có $18$ số nguyên thuộc tập xác định.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>503</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>D92</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>p240_q31</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên thuộc tập xác định của hàm số $y=\log[(6-x)(x+6)]$?
+A. $12$.
+B. $10$.
+C. $Vô số$.
+D. $11$.</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>D. $11$.</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Điều kiện $(6-x)(x+6)&gt;0\Leftrightarrow -6&lt;x&lt;6\Rightarrow \mathscr{D}=(-6;6)$. Vậy có $11$ số nguyên thuộc tập xác định.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>504</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>D92</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>p240_q31</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên thuộc tập xác định của hàm số $y=\log[(20-x)(x+2)]$?
+A. $22$.
+B. $21$.
+C. $20$.
+D. $Vô số$.</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>B. $21$.</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Điều kiện $(20-x)(x+2)&gt;0\Leftrightarrow -2&lt;x&lt;20\Rightarrow \mathscr{D}=(-2;20)$. Vậy có $21$ số nguyên thuộc tập xác định.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
+++ b/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H505"/>
+  <dimension ref="A1:H517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21789,6 +21789,534 @@
         </is>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>505</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>D49</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>p110_q17</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Với mọi số thực $a$ dương, $\log_{2}\dfrac{a}{2}$ bằng
+A. $\log_{2} a+1$.
+B. $\log_{2} a-1$.
+C. $1-\log_{2} a$.
+D. $\log_{2} a-2$.</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>B. $\log_{2} a-1$.</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>Ta có $\log_{2}\dfrac{a}{2}=\log_{2} a-\log_{2}2=\log_{2} a-1$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>506</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>D49</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>p110_q17</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Với mọi số thực $a$ dương, $\log_{3}\dfrac{a}{3}$ bằng
+A. $\log_{3} a-3$.
+B. $\log_{3} a-1$.
+C. $1-\log_{3} a$.
+D. $\log_{3} a+1$.</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>B. $\log_{3} a-1$.</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Ta có $\log_{3}\dfrac{a}{3}=\log_{3} a-\log_{3}3=\log_{3} a-1$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>507</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>D49</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>p110_q17</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Với mọi số thực $a$ dương, $\log_{5}\dfrac{a}{5}$ bằng
+A. $\log_{5} a-5$.
+B. $\log_{5} a-1$.
+C. $\log_{5} a+1$.
+D. $1-\log_{5} a$.</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>B. $\log_{5} a-1$.</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>Ta có $\log_{5}\dfrac{a}{5}=\log_{5} a-\log_{5}5=\log_{5} a-1$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>508</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>D49</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>p110_q17</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Với mọi số thực $a$ dương, $\log_{2}\dfrac{a}{4}$ bằng
+A. $\log_{2} a-4$.
+B. $\log_{2} a+2$.
+C. $2-\log_{2} a$.
+D. $\log_{2} a-2$.</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>D. $\log_{2} a-2$.</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>Ta có $\log_{2}\dfrac{a}{4}=\log_{2} a-\log_{2}4=\log_{2} a-2$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>509</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>D49</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>p110_q17</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Với mọi số thực $a$ dương, $\log_{3}\dfrac{a}{9}$ bằng
+A. $\log_{3} a-9$.
+B. $2-\log_{3} a$.
+C. $\log_{3} a-2$.
+D. $\log_{3} a+2$.</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>C. $\log_{3} a-2$.</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Ta có $\log_{3}\dfrac{a}{9}=\log_{3} a-\log_{3}9=\log_{3} a-2$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>510</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>D49</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>p110_q17</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Với mọi số thực $a$ dương, $\log_{2}\dfrac{a}{8}$ bằng
+A. $\log_{2} a+3$.
+B. $\log_{2} a-3$.
+C. $\log_{2} a-8$.
+D. $3-\log_{2} a$.</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>B. $\log_{2} a-3$.</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Ta có $\log_{2}\dfrac{a}{8}=\log_{2} a-\log_{2}8=\log_{2} a-3$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>511</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>p033_q13</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Cho $a$ là số thực dương, $a\neq 1$ và $P=\log_{\sqrt[3]{a}} a^{3}$. Mệnh đề nào dưới đây là đúng?
+A. $P=6$.
+B. $P=1$.
+C. $P=7$.
+D. $P=9$.</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>D. $P=9$.</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>Ta có $P=\log_{a^{1/3}}a^{3}=\dfrac{3}{1/3}\log_a a=9$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>512</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>p033_q13</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Cho $a$ là số thực dương, $a\neq 1$ và $P=\log_{\sqrt{a}} a^{4}$. Mệnh đề nào dưới đây là đúng?
+A. $P=6$.
+B. $P=3$.
+C. $P=8$.
+D. $P=2$.</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>C. $P=8$.</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>Ta có $P=\log_{a^{1/2}}a^{4}=\dfrac{4}{1/2}\log_a a=8$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>513</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>p033_q13</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Cho $a$ là số thực dương, $a\neq 1$ và $P=\log_{\sqrt[4]{a}} a^{2}$. Mệnh đề nào dưới đây là đúng?
+A. $P=8$.
+B. $P=-2$.
+C. $P=6$.
+D. $P=\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>A. $P=8$.</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>Ta có $P=\log_{a^{1/4}}a^{2}=\dfrac{2}{1/4}\log_a a=8$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>514</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>p033_q13</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Cho $a$ là số thực dương, $a\neq 1$ và $P=\log_{\sqrt[3]{a}} a^{6}$. Mệnh đề nào dưới đây là đúng?
+A. $P=18$.
+B. $P=3$.
+C. $P=9$.
+D. $P=2$.</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>A. $P=18$.</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Ta có $P=\log_{a^{1/3}}a^{6}=\dfrac{6}{1/3}\log_a a=18$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>515</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>p033_q13</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Cho $a$ là số thực dương, $a\neq 1$ và $P=\log_{\sqrt{a}} a^{5}$. Mệnh đề nào dưới đây là đúng?
+A. $P=7$.
+B. $P=3$.
+C. $P=\dfrac{5}{2}$.
+D. $P=10$.</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>D. $P=10$.</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>Ta có $P=\log_{a^{1/2}}a^{5}=\dfrac{5}{1/2}\log_a a=10$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>516</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>p033_q13</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Cho $a$ là số thực dương, $a\neq 1$ và $P=\log_{\sqrt[5]{a}} a^{2}$. Mệnh đề nào dưới đây là đúng?
+A. $P=-3$.
+B. $P=10$.
+C. $P=\dfrac{2}{5}$.
+D. $P=7$.</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>B. $P=10$.</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>Ta có $P=\log_{a^{1/5}}a^{2}=\dfrac{2}{1/5}\log_a a=10$.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
+++ b/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H517"/>
+  <dimension ref="A1:H567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22317,6 +22317,2206 @@
         </is>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>517</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>p021_q18</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Tính đạo hàm của hàm số $y = \ln(1+\sqrt{x+1})$.
+A. $y'=\dfrac{2}{\sqrt{x+1}(1+\sqrt{x+1})}$.
+B. $y'=\dfrac{1}{1+\sqrt{x+1}}$.
+C. $y'=\dfrac{1}{2\sqrt{x+1}(1+\sqrt{x+1})}$.
+D. $y'=\dfrac{1}{\sqrt{x+1}(1+\sqrt{x+1})}$.</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>C. $y'=\dfrac{1}{2\sqrt{x+1}(1+\sqrt{x+1})}$.</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>$y'=\dfrac{(1+\sqrt{x+1})'}{1+\sqrt{x+1}}=\dfrac{\frac{1}{2\sqrt{x+1}}}{1+\sqrt{x+1}}=\dfrac{1}{2\sqrt{x+1}(1+\sqrt{x+1})}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>518</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>p021_q18</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Tính đạo hàm của hàm số $y = \ln(1+\sqrt{x+2})$.
+A. $y'=\dfrac{2}{\sqrt{x+2}(1+\sqrt{x+2})}$.
+B. $y'=\dfrac{1}{2\sqrt{x+2}(1+\sqrt{x+2})}$.
+C. $y'=\dfrac{1}{\sqrt{x+2}(1+\sqrt{x+2})}$.
+D. $y'=\dfrac{1}{1+\sqrt{x+2}}$.</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>B. $y'=\dfrac{1}{2\sqrt{x+2}(1+\sqrt{x+2})}$.</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>$y'=\dfrac{(1+\sqrt{x+2})'}{1+\sqrt{x+2}}=\dfrac{\frac{1}{2\sqrt{x+2}}}{1+\sqrt{x+2}}=\dfrac{1}{2\sqrt{x+2}(1+\sqrt{x+2})}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>519</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>p021_q18</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Tính đạo hàm của hàm số $y = \ln(1+\sqrt{x+3})$.
+A. $y'=\dfrac{2}{\sqrt{x+3}(1+\sqrt{x+3})}$.
+B. $y'=\dfrac{1}{1+\sqrt{x+3}}$.
+C. $y'=\dfrac{1}{2\sqrt{x+3}(1+\sqrt{x+3})}$.
+D. $y'=\dfrac{1}{\sqrt{x+3}(1+\sqrt{x+3})}$.</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>C. $y'=\dfrac{1}{2\sqrt{x+3}(1+\sqrt{x+3})}$.</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>$y'=\dfrac{(1+\sqrt{x+3})'}{1+\sqrt{x+3}}=\dfrac{\frac{1}{2\sqrt{x+3}}}{1+\sqrt{x+3}}=\dfrac{1}{2\sqrt{x+3}(1+\sqrt{x+3})}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>520</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>p021_q18</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Tính đạo hàm của hàm số $y = \ln(1+\sqrt{x+0})$.
+A. $y'=\dfrac{2}{\sqrt{x+0}(1+\sqrt{x+0})}$.
+B. $y'=\dfrac{1}{1+\sqrt{x+0}}$.
+C. $y'=\dfrac{1}{2\sqrt{x+0}(1+\sqrt{x+0})}$.
+D. $y'=\dfrac{1}{\sqrt{x+0}(1+\sqrt{x+0})}$.</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>C. $y'=\dfrac{1}{2\sqrt{x+0}(1+\sqrt{x+0})}$.</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>$y'=\dfrac{(1+\sqrt{x+0})'}{1+\sqrt{x+0}}=\dfrac{\frac{1}{2\sqrt{x+0}}}{1+\sqrt{x+0}}=\dfrac{1}{2\sqrt{x+0}(1+\sqrt{x+0})}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>521</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>p021_q18</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Tính đạo hàm của hàm số $y = \ln(1+\sqrt{x+4})$.
+A. $y'=\dfrac{2}{\sqrt{x+4}(1+\sqrt{x+4})}$.
+B. $y'=\dfrac{1}{\sqrt{x+4}(1+\sqrt{x+4})}$.
+C. $y'=\dfrac{1}{1+\sqrt{x+4}}$.
+D. $y'=\dfrac{1}{2\sqrt{x+4}(1+\sqrt{x+4})}$.</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>D. $y'=\dfrac{1}{2\sqrt{x+4}(1+\sqrt{x+4})}$.</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>$y'=\dfrac{(1+\sqrt{x+4})'}{1+\sqrt{x+4}}=\dfrac{\frac{1}{2\sqrt{x+4}}}{1+\sqrt{x+4}}=\dfrac{1}{2\sqrt{x+4}(1+\sqrt{x+4})}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>522</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>p021_q18</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Tính đạo hàm của hàm số $y = \ln(1+\sqrt{x+5})$.
+A. $y'=\dfrac{2}{\sqrt{x+5}(1+\sqrt{x+5})}$.
+B. $y'=\dfrac{1}{\sqrt{x+5}(1+\sqrt{x+5})}$.
+C. $y'=\dfrac{1}{1+\sqrt{x+5}}$.
+D. $y'=\dfrac{1}{2\sqrt{x+5}(1+\sqrt{x+5})}$.</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>D. $y'=\dfrac{1}{2\sqrt{x+5}(1+\sqrt{x+5})}$.</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>$y'=\dfrac{(1+\sqrt{x+5})'}{1+\sqrt{x+5}}=\dfrac{\frac{1}{2\sqrt{x+5}}}{1+\sqrt{x+5}}=\dfrac{1}{2\sqrt{x+5}(1+\sqrt{x+5})}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>523</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>p006_q16</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Cho hàm số $y=f(x)=2^x\cdot7^{x^2}$. Khẳng định nào sau đây là khẳng định **sai**?
+A. $f(x)&lt;1\Leftrightarrow 1+x\log_{2}7&lt;0$.
+B. $f(x)&lt;1\Leftrightarrow x+x^2\log_{2}7&lt;0$.
+C. $f(x)&lt;1\Leftrightarrow x\ln2+x^2\ln7&lt;0$.
+D. $f(x)&lt;1\Leftrightarrow x\log_{7}2+x^2&lt;0$.</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>A. $f(x)&lt;1\Leftrightarrow 1+x\log_{2}7&lt;0$.</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>$f(x)&lt;1\Leftrightarrow\log_{2}f(x)&lt;0\Leftrightarrow x+x^2\log_{2}7&lt;0\Leftrightarrow x(1+x\log_{2}7)&lt;0$, KHÔNG tương đương với $1+x\log_{2}7&lt;0$ (thiếu nhân tử $x$). Vậy khẳng định sai là $1+x\log_{2}7&lt;0$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>524</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>p006_q16</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Cho hàm số $y=f(x)=3^x\cdot5^{x^2}$. Khẳng định nào sau đây là khẳng định **sai**?
+A. $f(x)&lt;1\Leftrightarrow x\ln3+x^2\ln5&lt;0$.
+B. $f(x)&lt;1\Leftrightarrow 1+x\log_{3}5&lt;0$.
+C. $f(x)&lt;1\Leftrightarrow x\log_{5}3+x^2&lt;0$.
+D. $f(x)&lt;1\Leftrightarrow x+x^2\log_{3}5&lt;0$.</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>B. $f(x)&lt;1\Leftrightarrow 1+x\log_{3}5&lt;0$.</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>$f(x)&lt;1\Leftrightarrow\log_{3}f(x)&lt;0\Leftrightarrow x+x^2\log_{3}5&lt;0\Leftrightarrow x(1+x\log_{3}5)&lt;0$, KHÔNG tương đương với $1+x\log_{3}5&lt;0$ (thiếu nhân tử $x$). Vậy khẳng định sai là $1+x\log_{3}5&lt;0$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>525</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>p006_q16</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Cho hàm số $y=f(x)=2^x\cdot9^{x^2}$. Khẳng định nào sau đây là khẳng định **sai**?
+A. $f(x)&lt;1\Leftrightarrow x\log_{9}2+x^2&lt;0$.
+B. $f(x)&lt;1\Leftrightarrow x+x^2\log_{2}9&lt;0$.
+C. $f(x)&lt;1\Leftrightarrow x\ln2+x^2\ln9&lt;0$.
+D. $f(x)&lt;1\Leftrightarrow 1+x\log_{2}9&lt;0$.</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>D. $f(x)&lt;1\Leftrightarrow 1+x\log_{2}9&lt;0$.</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>$f(x)&lt;1\Leftrightarrow\log_{2}f(x)&lt;0\Leftrightarrow x+x^2\log_{2}9&lt;0\Leftrightarrow x(1+x\log_{2}9)&lt;0$, KHÔNG tương đương với $1+x\log_{2}9&lt;0$ (thiếu nhân tử $x$). Vậy khẳng định sai là $1+x\log_{2}9&lt;0$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>526</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>p006_q16</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Cho hàm số $y=f(x)=5^x\cdot3^{x^2}$. Khẳng định nào sau đây là khẳng định **sai**?
+A. $f(x)&lt;1\Leftrightarrow 1+x\log_{5}3&lt;0$.
+B. $f(x)&lt;1\Leftrightarrow x\ln5+x^2\ln3&lt;0$.
+C. $f(x)&lt;1\Leftrightarrow x\log_{3}5+x^2&lt;0$.
+D. $f(x)&lt;1\Leftrightarrow x+x^2\log_{5}3&lt;0$.</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>A. $f(x)&lt;1\Leftrightarrow 1+x\log_{5}3&lt;0$.</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>$f(x)&lt;1\Leftrightarrow\log_{5}f(x)&lt;0\Leftrightarrow x+x^2\log_{5}3&lt;0\Leftrightarrow x(1+x\log_{5}3)&lt;0$, KHÔNG tương đương với $1+x\log_{5}3&lt;0$ (thiếu nhân tử $x$). Vậy khẳng định sai là $1+x\log_{5}3&lt;0$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>527</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>p006_q16</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Cho hàm số $y=f(x)=2^x\cdot11^{x^2}$. Khẳng định nào sau đây là khẳng định **sai**?
+A. $f(x)&lt;1\Leftrightarrow x\ln2+x^2\ln11&lt;0$.
+B. $f(x)&lt;1\Leftrightarrow x+x^2\log_{2}11&lt;0$.
+C. $f(x)&lt;1\Leftrightarrow 1+x\log_{2}11&lt;0$.
+D. $f(x)&lt;1\Leftrightarrow x\log_{11}2+x^2&lt;0$.</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>C. $f(x)&lt;1\Leftrightarrow 1+x\log_{2}11&lt;0$.</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>$f(x)&lt;1\Leftrightarrow\log_{2}f(x)&lt;0\Leftrightarrow x+x^2\log_{2}11&lt;0\Leftrightarrow x(1+x\log_{2}11)&lt;0$, KHÔNG tương đương với $1+x\log_{2}11&lt;0$ (thiếu nhân tử $x$). Vậy khẳng định sai là $1+x\log_{2}11&lt;0$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>528</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>p006_q16</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Cho hàm số $y=f(x)=3^x\cdot7^{x^2}$. Khẳng định nào sau đây là khẳng định **sai**?
+A. $f(x)&lt;1\Leftrightarrow x\ln3+x^2\ln7&lt;0$.
+B. $f(x)&lt;1\Leftrightarrow 1+x\log_{3}7&lt;0$.
+C. $f(x)&lt;1\Leftrightarrow x+x^2\log_{3}7&lt;0$.
+D. $f(x)&lt;1\Leftrightarrow x\log_{7}3+x^2&lt;0$.</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>B. $f(x)&lt;1\Leftrightarrow 1+x\log_{3}7&lt;0$.</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>$f(x)&lt;1\Leftrightarrow\log_{3}f(x)&lt;0\Leftrightarrow x+x^2\log_{3}7&lt;0\Leftrightarrow x(1+x\log_{3}7)&lt;0$, KHÔNG tương đương với $1+x\log_{3}7&lt;0$ (thiếu nhân tử $x$). Vậy khẳng định sai là $1+x\log_{3}7&lt;0$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>529</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>D45</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>p099_q31</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Tập nghiệm của bất phương trình $9^x+2\cdot3^x-3&gt;0$ là
+A. $(-\infty;0)$.
+B. $(1;+\infty)$.
+C. $[0;+\infty)$.
+D. $(0;+\infty)$.</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>D. $(0;+\infty)$.</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>$(3^x-1)(3^x--3)&gt;0$. Vì $3^x&gt;0&gt;-3$ nên $3^x--3&gt;0$ luôn đúng, do đó bất phương trình $\Leftrightarrow 3^x&gt;1\Leftrightarrow x&gt;\log_{3}1$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>530</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>D45</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>p099_q31</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Tập nghiệm của bất phương trình $4^x-3\cdot2^x-4&gt;0$ là
+A. $(2;+\infty)$.
+B. $(3;+\infty)$.
+C. $(-\infty;2)$.
+D. $[2;+\infty)$.</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>A. $(2;+\infty)$.</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>$(2^x-4)(2^x--1)&gt;0$. Vì $2^x&gt;0&gt;-1$ nên $2^x--1&gt;0$ luôn đúng, do đó bất phương trình $\Leftrightarrow 2^x&gt;4\Leftrightarrow x&gt;\log_{2}4$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>531</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>D45</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>p099_q31</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Tập nghiệm của bất phương trình $25^x+4\cdot5^x-5&gt;0$ là
+A. $(0;+\infty)$.
+B. $[0;+\infty)$.
+C. $(1;+\infty)$.
+D. $(-\infty;0)$.</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>A. $(0;+\infty)$.</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>$(5^x-1)(5^x--5)&gt;0$. Vì $5^x&gt;0&gt;-5$ nên $5^x--5&gt;0$ luôn đúng, do đó bất phương trình $\Leftrightarrow 5^x&gt;1\Leftrightarrow x&gt;\log_{5}1$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>532</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>D45</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>p099_q31</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Tập nghiệm của bất phương trình $9^x+7\cdot3^x-18&gt;0$ là
+A. $(\dfrac{\log{\left(2 \right)}}{\log{\left(3 \right)}} + 1;+\infty)$.
+B. $[\dfrac{\log{\left(2 \right)}}{\log{\left(3 \right)}};+\infty)$.
+C. $(\dfrac{\log{\left(2 \right)}}{\log{\left(3 \right)}};+\infty)$.
+D. $(-\infty;\dfrac{\log{\left(2 \right)}}{\log{\left(3 \right)}})$.</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>C. $(\dfrac{\log{\left(2 \right)}}{\log{\left(3 \right)}};+\infty)$.</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>$(3^x-2)(3^x--9)&gt;0$. Vì $3^x&gt;0&gt;-9$ nên $3^x--9&gt;0$ luôn đúng, do đó bất phương trình $\Leftrightarrow 3^x&gt;2\Leftrightarrow x&gt;\log_{3}2$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>533</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>D45</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>p099_q31</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Tập nghiệm của bất phương trình $4^x+7\cdot2^x-8&gt;0$ là
+A. $(-\infty;0)$.
+B. $(1;+\infty)$.
+C. $(0;+\infty)$.
+D. $[0;+\infty)$.</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>C. $(0;+\infty)$.</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>$(2^x-1)(2^x--8)&gt;0$. Vì $2^x&gt;0&gt;-8$ nên $2^x--8&gt;0$ luôn đúng, do đó bất phương trình $\Leftrightarrow 2^x&gt;1\Leftrightarrow x&gt;\log_{2}1$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>534</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>D45</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>p099_q31</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Tập nghiệm của bất phương trình $25^x-4\cdot5^x-5&gt;0$ là
+A. $(2;+\infty)$.
+B. $[1;+\infty)$.
+C. $(-\infty;1)$.
+D. $(1;+\infty)$.</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>D. $(1;+\infty)$.</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>$(5^x-5)(5^x--1)&gt;0$. Vì $5^x&gt;0&gt;-1$ nên $5^x--1&gt;0$ luôn đúng, do đó bất phương trình $\Leftrightarrow 5^x&gt;5\Leftrightarrow x&gt;\log_{5}5$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>535</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>D40</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>p088_q43</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\log_{2}^2(2x)-(m+2)\log_{2}x+m-2=0$ ($m$ là tham số thực). Tập hợp tất cả các giá trị của $m$ để phương trình đã cho có hai nghiệm phân biệt thuộc đoạn $[1;2]$ là
+A. $(2;+\infty)$.
+B. $[1;2]$.
+C. $[1;2)$.
+D. $(1;2)$.</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>C. $[1;2)$.</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{2}x$, PT trở thành $t^2-mt+m-3=0$ $\Leftrightarrow (t-1)(t-(m - 1))=0$ (sau khi rút gọn). $x\in[1;2]\Leftrightarrow t\in[0;1]$. Vậy $m\in[1;2)$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>536</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>D40</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>p088_q43</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\log_{3}^2(3x)-(m+1)\log_{3}x+m-3=0$ ($m$ là tham số thực). Tập hợp tất cả các giá trị của $m$ để phương trình đã cho có hai nghiệm phân biệt thuộc đoạn $[1;3]$ là
+A. $[2;3)$.
+B. $(2;3)$.
+C. $(3;+\infty)$.
+D. $[2;3]$.</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>A. $[2;3)$.</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{3}x$, PT trở thành $t^2-mt+m-4=0$ $\Leftrightarrow (t-1)(t-(m - 2))=0$ (sau khi rút gọn). $x\in[1;3]\Leftrightarrow t\in[0;1]$. Vậy $m\in[2;3)$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>537</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>D40</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>p088_q43</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\log_{2}^2(2x)-(m+3)\log_{2}x+m-1=0$ ($m$ là tham số thực). Tập hợp tất cả các giá trị của $m$ để phương trình đã cho có hai nghiệm phân biệt thuộc đoạn $[1;2]$ là
+A. $[0;1)$.
+B. $(1;+\infty)$.
+C. $(0;1)$.
+D. $[0;1]$.</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>A. $[0;1)$.</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{2}x$, PT trở thành $t^2-mt+m-2=0$ $\Leftrightarrow (t-1)(t-(m))=0$ (sau khi rút gọn). $x\in[1;2]\Leftrightarrow t\in[0;1]$. Vậy $m\in[0;1)$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>538</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>D40</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>p088_q43</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\log_{5}^2(5x)-(m+2)\log_{5}x+m-2=0$ ($m$ là tham số thực). Tập hợp tất cả các giá trị của $m$ để phương trình đã cho có hai nghiệm phân biệt thuộc đoạn $[1;5]$ là
+A. $(1;2)$.
+B. $(2;+\infty)$.
+C. $[1;2)$.
+D. $[1;2]$.</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>C. $[1;2)$.</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{5}x$, PT trở thành $t^2-mt+m-3=0$ $\Leftrightarrow (t-1)(t-(m - 1))=0$ (sau khi rút gọn). $x\in[1;5]\Leftrightarrow t\in[0;1]$. Vậy $m\in[1;2)$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>539</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>D40</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>p088_q43</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\log_{3}^2(3x)-(m+2)\log_{3}x+m-2=0$ ($m$ là tham số thực). Tập hợp tất cả các giá trị của $m$ để phương trình đã cho có hai nghiệm phân biệt thuộc đoạn $[1;3]$ là
+A. $(2;+\infty)$.
+B. $(1;2)$.
+C. $[1;2]$.
+D. $[1;2)$.</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>D. $[1;2)$.</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{3}x$, PT trở thành $t^2-mt+m-3=0$ $\Leftrightarrow (t-1)(t-(m - 1))=0$ (sau khi rút gọn). $x\in[1;3]\Leftrightarrow t\in[0;1]$. Vậy $m\in[1;2)$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>540</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>D40</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>p088_q43</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\log_{2}^2(2x)-(m+1)\log_{2}x+m-3=0$ ($m$ là tham số thực). Tập hợp tất cả các giá trị của $m$ để phương trình đã cho có hai nghiệm phân biệt thuộc đoạn $[1;2]$ là
+A. $[2;3)$.
+B. $(3;+\infty)$.
+C. $(2;3)$.
+D. $[2;3]$.</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>A. $[2;3)$.</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{2}x$, PT trở thành $t^2-mt+m-4=0$ $\Leftrightarrow (t-1)(t-(m - 2))=0$ (sau khi rút gọn). $x\in[1;2]\Leftrightarrow t\in[0;1]$. Vậy $m\in[2;3)$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>541</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>p021_q20</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Tìm tập hợp tất cả các giá trị của tham số thực $m$ để phương trình $6^x+(3-m)2^x-m=0$ có nghiệm thuộc khoảng $(0;1)$.
+A. $[2;4]$.
+B. $(1;4)$.
+C. $(2;4)$.
+D. $(2;5)$.</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>C. $(2;4)$.</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>PT $\Leftrightarrow m=\dfrac{6^x+3\cdot2^x}{2^x+1}=f(x)$. Hàm $f$ đồng biến trên $\mathbb{R}$ (do $6&gt;2$), nên $0&lt;x&lt;1\Leftrightarrow f(0)&lt;f(x)&lt;f(1)\Leftrightarrow 2;4$ vì $f(0)=2, f(1)=4$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>542</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>p021_q20</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Tìm tập hợp tất cả các giá trị của tham số thực $m$ để phương trình $8^x+(4-m)2^x-m=0$ có nghiệm thuộc khoảng $(0;1)$.
+A. $[\dfrac{5}{2};\dfrac{16}{3}]$.
+B. $(\dfrac{5}{2};\dfrac{19}{3})$.
+C. $(\dfrac{5}{2};\dfrac{16}{3})$.
+D. $(\dfrac{3}{2};\dfrac{16}{3})$.</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>C. $(\dfrac{5}{2};\dfrac{16}{3})$.</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>PT $\Leftrightarrow m=\dfrac{8^x+4\cdot2^x}{2^x+1}=f(x)$. Hàm $f$ đồng biến trên $\mathbb{R}$ (do $8&gt;2$), nên $0&lt;x&lt;1\Leftrightarrow f(0)&lt;f(x)&lt;f(1)\Leftrightarrow \dfrac{5}{2};\dfrac{16}{3}$ vì $f(0)=\dfrac{5}{2}, f(1)=\dfrac{16}{3}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>543</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>p021_q20</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Tìm tập hợp tất cả các giá trị của tham số thực $m$ để phương trình $9^x+(2-m)3^x-m=0$ có nghiệm thuộc khoảng $(0;1)$.
+A. $(\dfrac{1}{2};\dfrac{15}{4})$.
+B. $[\dfrac{3}{2};\dfrac{15}{4}]$.
+C. $(\dfrac{3}{2};\dfrac{15}{4})$.
+D. $(\dfrac{3}{2};\dfrac{19}{4})$.</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>C. $(\dfrac{3}{2};\dfrac{15}{4})$.</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>PT $\Leftrightarrow m=\dfrac{9^x+2\cdot3^x}{3^x+1}=f(x)$. Hàm $f$ đồng biến trên $\mathbb{R}$ (do $9&gt;3$), nên $0&lt;x&lt;1\Leftrightarrow f(0)&lt;f(x)&lt;f(1)\Leftrightarrow \dfrac{3}{2};\dfrac{15}{4}$ vì $f(0)=\dfrac{3}{2}, f(1)=\dfrac{15}{4}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>544</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>p021_q20</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Tìm tập hợp tất cả các giá trị của tham số thực $m$ để phương trình $12^x+(6-m)2^x-m=0$ có nghiệm thuộc khoảng $(0;1)$.
+A. $[\dfrac{7}{2};8]$.
+B. $(\dfrac{7}{2};9)$.
+C. $(\dfrac{7}{2};8)$.
+D. $(\dfrac{5}{2};8)$.</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>C. $(\dfrac{7}{2};8)$.</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>PT $\Leftrightarrow m=\dfrac{12^x+6\cdot2^x}{2^x+1}=f(x)$. Hàm $f$ đồng biến trên $\mathbb{R}$ (do $12&gt;2$), nên $0&lt;x&lt;1\Leftrightarrow f(0)&lt;f(x)&lt;f(1)\Leftrightarrow \dfrac{7}{2};8$ vì $f(0)=\dfrac{7}{2}, f(1)=8$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>545</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>p021_q20</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Tìm tập hợp tất cả các giá trị của tham số thực $m$ để phương trình $15^x+(5-m)3^x-m=0$ có nghiệm thuộc khoảng $(0;1)$.
+A. $(3;\dfrac{15}{2})$.
+B. $(3;\dfrac{17}{2})$.
+C. $[3;\dfrac{15}{2}]$.
+D. $(2;\dfrac{15}{2})$.</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>A. $(3;\dfrac{15}{2})$.</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>PT $\Leftrightarrow m=\dfrac{15^x+5\cdot3^x}{3^x+1}=f(x)$. Hàm $f$ đồng biến trên $\mathbb{R}$ (do $15&gt;3$), nên $0&lt;x&lt;1\Leftrightarrow f(0)&lt;f(x)&lt;f(1)\Leftrightarrow 3;\dfrac{15}{2}$ vì $f(0)=3, f(1)=\dfrac{15}{2}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>546</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>p021_q20</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Tìm tập hợp tất cả các giá trị của tham số thực $m$ để phương trình $4^x+(2-m)2^x-m=0$ có nghiệm thuộc khoảng $(0;1)$.
+A. $(\dfrac{3}{2};\dfrac{8}{3})$.
+B. $[\dfrac{3}{2};\dfrac{8}{3}]$.
+C. $(\dfrac{3}{2};\dfrac{11}{3})$.
+D. $(\dfrac{1}{2};\dfrac{8}{3})$.</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>A. $(\dfrac{3}{2};\dfrac{8}{3})$.</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>PT $\Leftrightarrow m=\dfrac{4^x+2\cdot2^x}{2^x+1}=f(x)$. Hàm $f$ đồng biến trên $\mathbb{R}$ (do $4&gt;2$), nên $0&lt;x&lt;1\Leftrightarrow f(0)&lt;f(x)&lt;f(1)\Leftrightarrow \dfrac{3}{2};\dfrac{8}{3}$ vì $f(0)=\dfrac{3}{2}, f(1)=\dfrac{8}{3}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>547</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>p070_q31</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Tổng tất cả các nghiệm của phương trình $\log_{3}(7-3^x)=2-x$ bằng
+A. $4$.
+B. $2$.
+C. $3$.
+D. $7$.</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>B. $2$.</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>ĐK: $7-3^x&gt;0$. $\log_{3}(7-3^x)=2-x \Leftrightarrow 7-3^x=3^{2-x}=\dfrac{3^{2}}{3^x}\Leftrightarrow (3^x)^2-7\cdot3^x+3^{2}=0$. Đặt $t=3^x$, PT có 2 nghiệm $t_1,t_2$ với $t_1t_2=3^{2}$ (Viète), suy ra $3^{x_1+x_2}=3^{2}\Leftrightarrow x_1+x_2=2$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>548</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>p070_q31</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Tổng tất cả các nghiệm của phương trình $\log_{2}(5-2^x)=1-x$ bằng
+A. $1$.
+B. $3$.
+C. $2$.
+D. $5$.</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>A. $1$.</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>ĐK: $5-2^x&gt;0$. $\log_{2}(5-2^x)=1-x \Leftrightarrow 5-2^x=2^{1-x}=\dfrac{2^{1}}{2^x}\Leftrightarrow (2^x)^2-5\cdot2^x+2^{1}=0$. Đặt $t=2^x$, PT có 2 nghiệm $t_1,t_2$ với $t_1t_2=2^{1}$ (Viète), suy ra $2^{x_1+x_2}=2^{1}\Leftrightarrow x_1+x_2=1$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>549</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>p070_q31</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Tổng tất cả các nghiệm của phương trình $\log_{5}(30-5^x)=2-x$ bằng
+A. $3$.
+B. $30$.
+C. $2$.
+D. $4$.</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>C. $2$.</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>ĐK: $30-5^x&gt;0$. $\log_{5}(30-5^x)=2-x \Leftrightarrow 30-5^x=5^{2-x}=\dfrac{5^{2}}{5^x}\Leftrightarrow (5^x)^2-30\cdot5^x+5^{2}=0$. Đặt $t=5^x$, PT có 2 nghiệm $t_1,t_2$ với $t_1t_2=5^{2}$ (Viète), suy ra $5^{x_1+x_2}=5^{2}\Leftrightarrow x_1+x_2=2$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>550</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>p070_q31</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Tổng tất cả các nghiệm của phương trình $\log_{3}(15-3^x)=3-x$ bằng
+A. $3$.
+B. $6$.
+C. $15$.
+D. $4$.</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>A. $3$.</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>ĐK: $15-3^x&gt;0$. $\log_{3}(15-3^x)=3-x \Leftrightarrow 15-3^x=3^{3-x}=\dfrac{3^{3}}{3^x}\Leftrightarrow (3^x)^2-15\cdot3^x+3^{3}=0$. Đặt $t=3^x$, PT có 2 nghiệm $t_1,t_2$ với $t_1t_2=3^{3}$ (Viète), suy ra $3^{x_1+x_2}=3^{3}\Leftrightarrow x_1+x_2=3$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>551</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>p070_q31</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Tổng tất cả các nghiệm của phương trình $\log_{2}(10-2^x)=3-x$ bằng
+A. $10$.
+B. $4$.
+C. $6$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>ĐK: $10-2^x&gt;0$. $\log_{2}(10-2^x)=3-x \Leftrightarrow 10-2^x=2^{3-x}=\dfrac{2^{3}}{2^x}\Leftrightarrow (2^x)^2-10\cdot2^x+2^{3}=0$. Đặt $t=2^x$, PT có 2 nghiệm $t_1,t_2$ với $t_1t_2=2^{3}$ (Viète), suy ra $2^{x_1+x_2}=2^{3}\Leftrightarrow x_1+x_2=3$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>552</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>p070_q31</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Tổng tất cả các nghiệm của phương trình $\log_{3}(20-3^x)=2-x$ bằng
+A. $2$.
+B. $3$.
+C. $20$.
+D. $4$.</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>A. $2$.</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>ĐK: $20-3^x&gt;0$. $\log_{3}(20-3^x)=2-x \Leftrightarrow 20-3^x=3^{2-x}=\dfrac{3^{2}}{3^x}\Leftrightarrow (3^x)^2-20\cdot3^x+3^{2}=0$. Đặt $t=3^x$, PT có 2 nghiệm $t_1,t_2$ với $t_1t_2=3^{2}$ (Viète), suy ra $3^{x_1+x_2}=3^{2}\Leftrightarrow x_1+x_2=2$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>553</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>D67</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>p161_q35</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Gọi $S$ là tập hợp tất cả các giá trị nguyên của tham số $m$ sao cho phương trình $4^x-m\cdot2^{x+1}+5m^2-5=0$ có hai nghiệm phân biệt. Hỏi $S$ có bao nhiêu phần tử?
+A. $0$.
+B. $3$.
+C. $2$.
+D. $1$.</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>D. $1$.</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Đặt $t=2^x&gt;0$: $t^2-4mt+5m^2-5=0$. YCBT $\Leftrightarrow$ PT có 2 nghiệm dương phân biệt $\Leftrightarrow \Delta&gt;0,\ 4m&gt;0,\ 5m^2-5&gt;0 \Leftrightarrow m\in\left(1;\sqrt{5}\right)$. Vậy $S=\{2\}$, có $1$ phần tử.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>554</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>D67</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>p161_q35</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Gọi $S$ là tập hợp tất cả các giá trị nguyên của tham số $m$ sao cho phương trình $4^x-m\cdot2^{x+1}+7m^2-7=0$ có hai nghiệm phân biệt. Hỏi $S$ có bao nhiêu phần tử?
+A. $1$.
+B. $2$.
+C. $3$.
+D. $4$.</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>B. $2$.</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Đặt $t=2^x&gt;0$: $t^2-5mt+7m^2-7=0$. YCBT $\Leftrightarrow$ PT có 2 nghiệm dương phân biệt $\Leftrightarrow \Delta&gt;0,\ 5m&gt;0,\ 7m^2-7&gt;0 \Leftrightarrow m\in\left(1;\dfrac{2 \sqrt{21}}{3}\right)$. Vậy $S=\{2,3\}$, có $2$ phần tử.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>555</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>D67</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>p161_q35</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Gọi $S$ là tập hợp tất cả các giá trị nguyên của tham số $m$ sao cho phương trình $9^x-m\cdot3^{x+1}+5m^2-5=0$ có hai nghiệm phân biệt. Hỏi $S$ có bao nhiêu phần tử?
+A. $2$.
+B. $3$.
+C. $1$.
+D. $0$.</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>C. $1$.</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>Đặt $t=3^x&gt;0$: $t^2-4mt+5m^2-5=0$. YCBT $\Leftrightarrow$ PT có 2 nghiệm dương phân biệt $\Leftrightarrow \Delta&gt;0,\ 4m&gt;0,\ 5m^2-5&gt;0 \Leftrightarrow m\in\left(1;\sqrt{5}\right)$. Vậy $S=\{2\}$, có $1$ phần tử.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>556</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>D67</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>p161_q35</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Gọi $S$ là tập hợp tất cả các giá trị nguyên của tham số $m$ sao cho phương trình $9^x-m\cdot3^{x+1}+7m^2-7=0$ có hai nghiệm phân biệt. Hỏi $S$ có bao nhiêu phần tử?
+A. $3$.
+B. $2$.
+C. $1$.
+D. $4$.</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>B. $2$.</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Đặt $t=3^x&gt;0$: $t^2-5mt+7m^2-7=0$. YCBT $\Leftrightarrow$ PT có 2 nghiệm dương phân biệt $\Leftrightarrow \Delta&gt;0,\ 5m&gt;0,\ 7m^2-7&gt;0 \Leftrightarrow m\in\left(1;\dfrac{2 \sqrt{21}}{3}\right)$. Vậy $S=\{2,3\}$, có $2$ phần tử.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>557</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>D67</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>p161_q35</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Gọi $S$ là tập hợp tất cả các giá trị nguyên của tham số $m$ sao cho phương trình $25^x-m\cdot5^{x+1}+5m^2-5=0$ có hai nghiệm phân biệt. Hỏi $S$ có bao nhiêu phần tử?
+A. $2$.
+B. $1$.
+C. $3$.
+D. $0$.</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>B. $1$.</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Đặt $t=5^x&gt;0$: $t^2-4mt+5m^2-5=0$. YCBT $\Leftrightarrow$ PT có 2 nghiệm dương phân biệt $\Leftrightarrow \Delta&gt;0,\ 4m&gt;0,\ 5m^2-5&gt;0 \Leftrightarrow m\in\left(1;\sqrt{5}\right)$. Vậy $S=\{2\}$, có $1$ phần tử.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>558</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>D67</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>p161_q35</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Gọi $S$ là tập hợp tất cả các giá trị nguyên của tham số $m$ sao cho phương trình $25^x-m\cdot5^{x+1}+7m^2-7=0$ có hai nghiệm phân biệt. Hỏi $S$ có bao nhiêu phần tử?
+A. $3$.
+B. $1$.
+C. $2$.
+D. $4$.</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>C. $2$.</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Đặt $t=5^x&gt;0$: $t^2-5mt+7m^2-7=0$. YCBT $\Leftrightarrow$ PT có 2 nghiệm dương phân biệt $\Leftrightarrow \Delta&gt;0,\ 5m&gt;0,\ 7m^2-7&gt;0 \Leftrightarrow m\in\left(1;\dfrac{2 \sqrt{21}}{3}\right)$. Vậy $S=\{2,3\}$, có $2$ phần tử.</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>559</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>D69</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>p166_q45</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Cho phương trình $3^x+m=\log_{3}(x-m)$ với $m$ là tham số. Có bao nhiêu giá trị nguyên của $m\in(-15;15)$ để phương trình đã cho có nghiệm?
+A. $15$.
+B. $14$.
+C. $29$.
+D. $13$.</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>B. $14$.</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>$\Leftrightarrow 3^x+x=\log_{3}(x-m)+(x-m)$. Xét $f(t)=3^t+t$ đồng biến trên $\mathbb{R}$ nên $x=\log_{3}(x-m)\Leftrightarrow 3^x=x-m\Leftrightarrow 3^x-x=-m$. Xét $g(x)=3^x-x$ có $g'(x)=0$ tại $x\approx-0.0856$, giá trị nhỏ nhất $g_{\min}\approx0.9958$. PT có nghiệm khi $m&lt;-0.9958$. Với $m$ nguyên trong $(-15;15)$, có $14$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>560</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>D69</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>p166_q45</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Cho phương trình $2^x+m=\log_{2}(x-m)$ với $m$ là tham số. Có bao nhiêu giá trị nguyên của $m\in(-10;10)$ để phương trình đã cho có nghiệm?
+A. $9$.
+B. $8$.
+C. $19$.
+D. $10$.</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>A. $9$.</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>$\Leftrightarrow 2^x+x=\log_{2}(x-m)+(x-m)$. Xét $f(t)=2^t+t$ đồng biến trên $\mathbb{R}$ nên $x=\log_{2}(x-m)\Leftrightarrow 2^x=x-m\Leftrightarrow 2^x-x=-m$. Xét $g(x)=2^x-x$ có $g'(x)=0$ tại $x\approx0.5288$, giá trị nhỏ nhất $g_{\min}\approx0.9139$. PT có nghiệm khi $m&lt;-0.9139$. Với $m$ nguyên trong $(-10;10)$, có $9$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>561</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>D69</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>p166_q45</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Cho phương trình $3^x+m=\log_{3}(x-m)$ với $m$ là tham số. Có bao nhiêu giá trị nguyên của $m\in(-20;20)$ để phương trình đã cho có nghiệm?
+A. $19$.
+B. $39$.
+C. $20$.
+D. $18$.</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>A. $19$.</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>$\Leftrightarrow 3^x+x=\log_{3}(x-m)+(x-m)$. Xét $f(t)=3^t+t$ đồng biến trên $\mathbb{R}$ nên $x=\log_{3}(x-m)\Leftrightarrow 3^x=x-m\Leftrightarrow 3^x-x=-m$. Xét $g(x)=3^x-x$ có $g'(x)=0$ tại $x\approx-0.0856$, giá trị nhỏ nhất $g_{\min}\approx0.9958$. PT có nghiệm khi $m&lt;-0.9958$. Với $m$ nguyên trong $(-20;20)$, có $19$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>562</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>D69</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>p166_q45</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Cho phương trình $5^x+m=\log_{5}(x-m)$ với $m$ là tham số. Có bao nhiêu giá trị nguyên của $m\in(-12;12)$ để phương trình đã cho có nghiệm?
+A. $12$.
+B. $11$.
+C. $23$.
+D. $10$.</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>B. $11$.</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>$\Leftrightarrow 5^x+x=\log_{5}(x-m)+(x-m)$. Xét $f(t)=5^t+t$ đồng biến trên $\mathbb{R}$ nên $x=\log_{5}(x-m)\Leftrightarrow 5^x=x-m\Leftrightarrow 5^x-x=-m$. Xét $g(x)=5^x-x$ có $g'(x)=0$ tại $x\approx-0.2957$, giá trị nhỏ nhất $g_{\min}\approx0.9170$. PT có nghiệm khi $m&lt;-0.9170$. Với $m$ nguyên trong $(-12;12)$, có $11$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>563</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>D51</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>p115_q39</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $(4^x-5\cdot2^{x+2}+64)\sqrt{2-\log(4x)}\ge 0$?
+A. $26$.
+B. $24$.
+C. $25$.
+D. $23$.</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>B. $24$.</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>ĐKXĐ: $0&lt;x\le25$. Vì căn $\ge0$ nên BPT $\Leftrightarrow 4^x-20\cdot2^x+64\ge0\Leftrightarrow 2^x\le4$ hoặc $2^x\ge16\Leftrightarrow x\le2$ hoặc $x\ge4$. Kết hợp ĐKXĐ: $S=(0;2]\cup[4;25]$, có $24$ số nguyên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>564</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>D51</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>p115_q39</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $(4^x-5\cdot2^{x+2}+64)\sqrt{3-\log(2x)}\ge 0$?
+A. $499$.
+B. $498$.
+C. $501$.
+D. $500$.</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>A. $499$.</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>ĐKXĐ: $0&lt;x\le500$. Vì căn $\ge0$ nên BPT $\Leftrightarrow 4^x-20\cdot2^x+64\ge0\Leftrightarrow 2^x\le4$ hoặc $2^x\ge16\Leftrightarrow x\le2$ hoặc $x\ge4$. Kết hợp ĐKXĐ: $S=(0;2]\cup[4;500]$, có $499$ số nguyên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>565</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>D51</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>p115_q39</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $(4^x-5\cdot2^{x+2}+64)\sqrt{3-\log(5x)}\ge 0$?
+A. $198$.
+B. $201$.
+C. $200$.
+D. $199$.</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>D. $199$.</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>ĐKXĐ: $0&lt;x\le200$. Vì căn $\ge0$ nên BPT $\Leftrightarrow 4^x-20\cdot2^x+64\ge0\Leftrightarrow 2^x\le4$ hoặc $2^x\ge16\Leftrightarrow x\le2$ hoặc $x\ge4$. Kết hợp ĐKXĐ: $S=(0;2]\cup[4;200]$, có $199$ số nguyên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>566</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>D51</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>p115_q39</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $(4^x-5\cdot2^{x+2}+64)\sqrt{2-\log(2x)}\ge 0$?
+A. $51$.
+B. $48$.
+C. $50$.
+D. $49$.</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>D. $49$.</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>ĐKXĐ: $0&lt;x\le50$. Vì căn $\ge0$ nên BPT $\Leftrightarrow 4^x-20\cdot2^x+64\ge0\Leftrightarrow 2^x\le4$ hoặc $2^x\ge16\Leftrightarrow x\le2$ hoặc $x\ge4$. Kết hợp ĐKXĐ: $S=(0;2]\cup[4;50]$, có $49$ số nguyên.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
+++ b/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H567"/>
+  <dimension ref="A1:H590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24517,6 +24517,1030 @@
         </is>
       </c>
     </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>567</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>p018_q09</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Tìm tập hợp tất cả các giá trị của tham số thực $m$ để hàm số $y = \ln(x^2+1) - mx + 1$ đồng biến trên khoảng $(-\infty; +\infty)$.
+A. $\left(-\infty;1\right)$.
+B. $\left[-1;1\right]$.
+C. $\left(-\infty;-1\right]$.
+D. $\left[1;+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>C. $\left(-\infty;-1\right]$.</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>$y'=\dfrac{2x}{x^2+1}-m\ge0,\forall x \Leftrightarrow m\le\min g(x)$ với $g(x)=\dfrac{2x}{x^2+1}$. $g'(x)=0\Leftrightarrow x=\pm1$. $\min g(x)=g(-1)=-1$. Vậy $m\le-1$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>568</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>p018_q09</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Tìm tập hợp tất cả các giá trị của tham số thực $m$ để hàm số $y = \ln(x^2+4) - mx + 1$ đồng biến trên khoảng $(-\infty; +\infty)$.
+A. $\left[\dfrac{1}{2};+\infty\right)$.
+B. $\left(-\infty;- \dfrac{1}{2}\right]$.
+C. $\left(-\infty;\dfrac{1}{2}\right)$.
+D. $\left[- \dfrac{1}{2};\dfrac{1}{2}\right]$.</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>B. $\left(-\infty;- \dfrac{1}{2}\right]$.</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>$y'=\dfrac{2x}{x^2+4}-m\ge0,\forall x \Leftrightarrow m\le\min g(x)$ với $g(x)=\dfrac{2x}{x^2+4}$. $g'(x)=0\Leftrightarrow x=\pm2$. $\min g(x)=g(-2)=-\dfrac{1}{2}$. Vậy $m\le-\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>569</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>p018_q09</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Tìm tập hợp tất cả các giá trị của tham số thực $m$ để hàm số $y = \ln(x^2+9) - mx + 1$ đồng biến trên khoảng $(-\infty; +\infty)$.
+A. $\left[\dfrac{1}{3};+\infty\right)$.
+B. $\left[- \dfrac{1}{3};\dfrac{1}{3}\right]$.
+C. $\left(-\infty;- \dfrac{1}{3}\right]$.
+D. $\left(-\infty;\dfrac{1}{3}\right)$.</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>C. $\left(-\infty;- \dfrac{1}{3}\right]$.</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>$y'=\dfrac{2x}{x^2+9}-m\ge0,\forall x \Leftrightarrow m\le\min g(x)$ với $g(x)=\dfrac{2x}{x^2+9}$. $g'(x)=0\Leftrightarrow x=\pm3$. $\min g(x)=g(-3)=-\dfrac{1}{3}$. Vậy $m\le-\dfrac{1}{3}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>570</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>p018_q09</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Tìm tập hợp tất cả các giá trị của tham số thực $m$ để hàm số $y = \ln(x^2+16) - mx + 1$ đồng biến trên khoảng $(-\infty; +\infty)$.
+A. $\left[\dfrac{1}{4};+\infty\right)$.
+B. $\left(-\infty;- \dfrac{1}{4}\right]$.
+C. $\left[- \dfrac{1}{4};\dfrac{1}{4}\right]$.
+D. $\left(-\infty;\dfrac{1}{4}\right)$.</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>B. $\left(-\infty;- \dfrac{1}{4}\right]$.</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>$y'=\dfrac{2x}{x^2+16}-m\ge0,\forall x \Leftrightarrow m\le\min g(x)$ với $g(x)=\dfrac{2x}{x^2+16}$. $g'(x)=0\Leftrightarrow x=\pm4$. $\min g(x)=g(-4)=-\dfrac{1}{4}$. Vậy $m\le-\dfrac{1}{4}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>571</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>p018_q09</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Tìm tập hợp tất cả các giá trị của tham số thực $m$ để hàm số $y = \ln(x^2+25) - mx + 1$ đồng biến trên khoảng $(-\infty; +\infty)$.
+A. $\left[- \dfrac{1}{5};\dfrac{1}{5}\right]$.
+B. $\left(-\infty;- \dfrac{1}{5}\right]$.
+C. $\left[\dfrac{1}{5};+\infty\right)$.
+D. $\left(-\infty;\dfrac{1}{5}\right)$.</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>B. $\left(-\infty;- \dfrac{1}{5}\right]$.</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>$y'=\dfrac{2x}{x^2+25}-m\ge0,\forall x \Leftrightarrow m\le\min g(x)$ với $g(x)=\dfrac{2x}{x^2+25}$. $g'(x)=0\Leftrightarrow x=\pm5$. $\min g(x)=g(-5)=-\dfrac{1}{5}$. Vậy $m\le-\dfrac{1}{5}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>572</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>p018_q09</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Tìm tập hợp tất cả các giá trị của tham số thực $m$ để hàm số $y = \ln(x^2+36) - mx + 1$ đồng biến trên khoảng $(-\infty; +\infty)$.
+A. $\left(-\infty;- \dfrac{1}{6}\right]$.
+B. $\left(-\infty;\dfrac{1}{6}\right)$.
+C. $\left[\dfrac{1}{6};+\infty\right)$.
+D. $\left[- \dfrac{1}{6};\dfrac{1}{6}\right]$.</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>A. $\left(-\infty;- \dfrac{1}{6}\right]$.</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>$y'=\dfrac{2x}{x^2+36}-m\ge0,\forall x \Leftrightarrow m\le\min g(x)$ với $g(x)=\dfrac{2x}{x^2+36}$. $g'(x)=0\Leftrightarrow x=\pm6$. $\min g(x)=g(-6)=-\dfrac{1}{6}$. Vậy $m\le-\dfrac{1}{6}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>573</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>D68</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>p161_q37</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Cho $a&gt;0,b&gt;0$ thỏa mãn
+$$\log_{10a+3b+1}((5a)^2+(b)^2+1)+\log_{10ab+1}(10a+3b+1)=2.$$
+Giá trị của $a+2b$ bằng
+A. $11$.
+B. $3$.
+C. $\dfrac{11}{2}$.
+D. $\dfrac{13}{2}$.</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>C. $\dfrac{11}{2}$.</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Áp dụng Cô-si: $(5a)^2+(b)^2+1\ge 10ab+1$. Dấu "=" khi $5a=b$. Kết hợp với dấu "=" ở bước Cô-si thứ hai (hai lôgarit nghịch đảo bằng 1) ta được hệ $\begin{cases}5a=b\\10a+3b+1=10ab+1\end{cases} \Rightarrow a=\dfrac{1}{2}, b=\dfrac{5}{2}$. Vậy $a+2b=\dfrac{11}{2}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>574</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>D68</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>p161_q37</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Cho $a&gt;0,b&gt;0$ thỏa mãn
+$$\log_{4a+3b+1}((2a)^2+(b)^2+1)+\log_{4ab+1}(4a+3b+1)=2.$$
+Giá trị của $a+2b$ bằng
+A. $\dfrac{25}{2}$.
+B. $\dfrac{25}{4}$.
+C. $\dfrac{15}{4}$.
+D. $\dfrac{29}{4}$.</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>B. $\dfrac{25}{4}$.</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Áp dụng Cô-si: $(2a)^2+(b)^2+1\ge 4ab+1$. Dấu "=" khi $2a=b$. Kết hợp với dấu "=" ở bước Cô-si thứ hai (hai lôgarit nghịch đảo bằng 1) ta được hệ $\begin{cases}2a=b\\4a+3b+1=4ab+1\end{cases} \Rightarrow a=\dfrac{5}{4}, b=\dfrac{5}{2}$. Vậy $a+2b=\dfrac{25}{4}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>575</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>D68</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>p161_q37</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Cho $a&gt;0,b&gt;0$ thỏa mãn
+$$\log_{6a+2b+1}((3a)^2+(2b)^2+1)+\log_{12ab+1}(6a+2b+1)=2.$$
+Giá trị của $a+2b$ bằng
+A. $2$.
+B. $4$.
+C. $\dfrac{5}{4}$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>A. $2$.</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Áp dụng Cô-si: $(3a)^2+(2b)^2+1\ge 12ab+1$. Dấu "=" khi $3a=2b$. Kết hợp với dấu "=" ở bước Cô-si thứ hai (hai lôgarit nghịch đảo bằng 1) ta được hệ $\begin{cases}3a=2b\\6a+2b+1=12ab+1\end{cases} \Rightarrow a=\dfrac{1}{2}, b=\dfrac{3}{4}$. Vậy $a+2b=2$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>576</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>D68</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>p161_q37</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Cho $a&gt;0,b&gt;0$ thỏa mãn
+$$\log_{3a+b+1}((a)^2+(b)^2+1)+\log_{2ab+1}(3a+b+1)=2.$$
+Giá trị của $a+2b$ bằng
+A. $12$.
+B. $7$.
+C. $4$.
+D. $6$.</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>D. $6$.</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Áp dụng Cô-si: $(a)^2+(b)^2+1\ge 2ab+1$. Dấu "=" khi $a=b$. Kết hợp với dấu "=" ở bước Cô-si thứ hai (hai lôgarit nghịch đảo bằng 1) ta được hệ $\begin{cases}a=b\\3a+b+1=2ab+1\end{cases} \Rightarrow a=2, b=2$. Vậy $a+2b=6$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>577</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>D68</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>p161_q37</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Cho $a&gt;0,b&gt;0$ thỏa mãn
+$$\log_{6a+2b+1}((3a)^2+(b)^2+1)+\log_{6ab+1}(6a+2b+1)=2.$$
+Giá trị của $a+2b$ bằng
+A. $\dfrac{17}{3}$.
+B. $\dfrac{14}{3}$.
+C. $\dfrac{28}{3}$.
+D. $\dfrac{8}{3}$.</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>B. $\dfrac{14}{3}$.</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Áp dụng Cô-si: $(3a)^2+(b)^2+1\ge 6ab+1$. Dấu "=" khi $3a=b$. Kết hợp với dấu "=" ở bước Cô-si thứ hai (hai lôgarit nghịch đảo bằng 1) ta được hệ $\begin{cases}3a=b\\6a+2b+1=6ab+1\end{cases} \Rightarrow a=\dfrac{2}{3}, b=2$. Vậy $a+2b=\dfrac{14}{3}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>578</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>D68</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>p161_q37</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Cho $a&gt;0,b&gt;0$ thỏa mãn
+$$\log_{8a+b+1}((2a)^2+(b)^2+1)+\log_{4ab+1}(8a+b+1)=2.$$
+Giá trị của $a+2b$ bằng
+A. $\dfrac{15}{4}$.
+B. $\dfrac{25}{2}$.
+C. $\dfrac{25}{4}$.
+D. $\dfrac{29}{4}$.</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>C. $\dfrac{25}{4}$.</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Áp dụng Cô-si: $(2a)^2+(b)^2+1\ge 4ab+1$. Dấu "=" khi $2a=b$. Kết hợp với dấu "=" ở bước Cô-si thứ hai (hai lôgarit nghịch đảo bằng 1) ta được hệ $\begin{cases}2a=b\\8a+b+1=4ab+1\end{cases} \Rightarrow a=\dfrac{5}{4}, b=\dfrac{5}{2}$. Vậy $a+2b=\dfrac{25}{4}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>579</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>D94</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>p243_q44</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Xét tất cả các số thực $x, y$ sao cho $a^{4x-\log_5 a^2}\le 25^{10-y^2}$ với mọi số thực dương $a$. Giá trị lớn nhất của biểu thức $P=x^2+y^2+x-3y$ bằng
+A. $10$.
+B. $21$.
+C. $20$.
+D. $0$.</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>C. $20$.</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_5 a$, điều kiện đúng với mọi $t$ dẫn tới $x^2+y^2\le10$. Theo Bunhiacôpxki: $(1x-3y)^2\le(10)(x^2+y^2)\le(10)\cdot10=100 \Rightarrow 1x-3y\le10$. Vậy $P\le10+10=20$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>580</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>D94</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>p243_q44</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Xét tất cả các số thực $x, y$ sao cho $a^{4x-\log_5 a^2}\le 25^{13-y^2}$ với mọi số thực dương $a$. Giá trị lớn nhất của biểu thức $P=x^2+y^2+2x-3y$ bằng
+A. $0$.
+B. $27$.
+C. $13$.
+D. $26$.</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>D. $26$.</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_5 a$, điều kiện đúng với mọi $t$ dẫn tới $x^2+y^2\le13$. Theo Bunhiacôpxki: $(2x-3y)^2\le(13)(x^2+y^2)\le(13)\cdot13=169 \Rightarrow 2x-3y\le13$. Vậy $P\le13+13=26$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>581</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>D94</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>p243_q44</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Xét tất cả các số thực $x, y$ sao cho $a^{4x-\log_5 a^2}\le 25^{16-y^2}$ với mọi số thực dương $a$. Giá trị lớn nhất của biểu thức $P=x^2+y^2+3x-4y$ bằng
+A. $-4$.
+B. $16$.
+C. $36$.
+D. $32$.</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>C. $36$.</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_5 a$, điều kiện đúng với mọi $t$ dẫn tới $x^2+y^2\le16$. Theo Bunhiacôpxki: $(3x-4y)^2\le(25)(x^2+y^2)\le(25)\cdot16=400 \Rightarrow 3x-4y\le20$. Vậy $P\le16+20=36$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>582</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>D94</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>p243_q44</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Xét tất cả các số thực $x, y$ sao cho $a^{4x-\log_5 a^2}\le 25^{17-y^2}$ với mọi số thực dương $a$. Giá trị lớn nhất của biểu thức $P=x^2+y^2+x-4y$ bằng
+A. $17$.
+B. $0$.
+C. $35$.
+D. $34$.</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>D. $34$.</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_5 a$, điều kiện đúng với mọi $t$ dẫn tới $x^2+y^2\le17$. Theo Bunhiacôpxki: $(1x-4y)^2\le(17)(x^2+y^2)\le(17)\cdot17=289 \Rightarrow 1x-4y\le17$. Vậy $P\le17+17=34$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>583</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>D94</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>p243_q44</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Xét tất cả các số thực $x, y$ sao cho $a^{4x-\log_5 a^2}\le 25^{18-y^2}$ với mọi số thực dương $a$. Giá trị lớn nhất của biểu thức $P=x^2+y^2+3x-3y$ bằng
+A. $18$.
+B. $36$.
+C. $0$.
+D. $37$.</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>B. $36$.</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_5 a$, điều kiện đúng với mọi $t$ dẫn tới $x^2+y^2\le18$. Theo Bunhiacôpxki: $(3x-3y)^2\le(18)(x^2+y^2)\le(18)\cdot18=324 \Rightarrow 3x-3y\le18$. Vậy $P\le18+18=36$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>584</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>D94</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>p243_q44</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Xét tất cả các số thực $x, y$ sao cho $a^{4x-\log_5 a^2}\le 25^{20-y^2}$ với mọi số thực dương $a$. Giá trị lớn nhất của biểu thức $P=x^2+y^2+x-2y$ bằng
+A. $20$.
+B. $40$.
+C. $30$.
+D. $10$.</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>C. $30$.</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_5 a$, điều kiện đúng với mọi $t$ dẫn tới $x^2+y^2\le20$. Theo Bunhiacôpxki: $(1x-2y)^2\le(5)(x^2+y^2)\le(5)\cdot20=100 \Rightarrow 1x-2y\le10$. Vậy $P\le20+10=30$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>585</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>D46</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>p105_q47</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Xét các số thực dương $a,b,x,y$ thỏa mãn $a,b&gt;1$ và $a^x=b^y=(ab)^{1/2}$. Giá trị nhỏ nhất của biểu thức $P=x+2y$ thuộc tập nào dưới đây?
+A. $\left[\dfrac{7}{2};4\right)$.
+B. $\left[\dfrac{5}{2};3\right)$.
+C. $\left[3;\dfrac{7}{2}\right)$.
+D. $\left[4;\dfrac{9}{2}\right)$.</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>B. $\left[\dfrac{5}{2};3\right)$.</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_a b&gt;0$. $x=\dfrac{1}{2}(1+t)$, $y=\dfrac1{2}\left(1+\dfrac1t\right)$. $P=x+2y$ đạt cực tiểu tại $t=\sqrt{2}$, $P_{\min}=\sqrt{2} + \dfrac{3}{2}\approx2.914$, thuộc $\left[\dfrac{5}{2};3\right)$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>586</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>D46</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>p105_q47</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Xét các số thực dương $a,b,x,y$ thỏa mãn $a,b&gt;1$ và $a^x=b^y=(ab)^{1/3}$. Giá trị nhỏ nhất của biểu thức $P=x+2y$ thuộc tập nào dưới đây?
+A. $\left[\dfrac{3}{2};2\right)$.
+B. $\left[3;\dfrac{7}{2}\right)$.
+C. $\left[\dfrac{5}{2};3\right)$.
+D. $\left[2;\dfrac{5}{2}\right)$.</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>A. $\left[\dfrac{3}{2};2\right)$.</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_a b&gt;0$. $x=\dfrac{1}{3}(1+t)$, $y=\dfrac1{3}\left(1+\dfrac1t\right)$. $P=x+2y$ đạt cực tiểu tại $t=\sqrt{2}$, $P_{\min}=\dfrac{2 \sqrt{2}}{3} + 1\approx1.943$, thuộc $\left[\dfrac{3}{2};2\right)$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>587</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>D46</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>p105_q47</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Xét các số thực dương $a,b,x,y$ thỏa mãn $a,b&gt;1$ và $a^x=b^y=(ab)^{1/2}$. Giá trị nhỏ nhất của biểu thức $P=x+3y$ thuộc tập nào dưới đây?
+A. $\left[5;\dfrac{11}{2}\right)$.
+B. $\left[4;\dfrac{9}{2}\right)$.
+C. $\left[\dfrac{7}{2};4\right)$.
+D. $\left[\dfrac{9}{2};5\right)$.</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>C. $\left[\dfrac{7}{2};4\right)$.</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_a b&gt;0$. $x=\dfrac{1}{2}(1+t)$, $y=\dfrac1{2}\left(1+\dfrac1t\right)$. $P=x+3y$ đạt cực tiểu tại $t=\sqrt{3}$, $P_{\min}=\sqrt{3} + 2\approx3.732$, thuộc $\left[\dfrac{7}{2};4\right)$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>588</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>D46</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>p105_q47</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Xét các số thực dương $a,b,x,y$ thỏa mãn $a,b&gt;1$ và $a^x=b^y=(ab)^{1/4}$. Giá trị nhỏ nhất của biểu thức $P=x+2y$ thuộc tập nào dưới đây?
+A. $\left[\dfrac{5}{2};3\right)$.
+B. $\left[1;\dfrac{3}{2}\right)$.
+C. $\left[\dfrac{3}{2};2\right)$.
+D. $\left[2;\dfrac{5}{2}\right)$.</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>B. $\left[1;\dfrac{3}{2}\right)$.</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_a b&gt;0$. $x=\dfrac{1}{4}(1+t)$, $y=\dfrac1{4}\left(1+\dfrac1t\right)$. $P=x+2y$ đạt cực tiểu tại $t=\sqrt{2}$, $P_{\min}=\dfrac{\sqrt{2}}{2} + \dfrac{3}{4}\approx1.457$, thuộc $\left[1;\dfrac{3}{2}\right)$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>589</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>D46</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>p105_q47</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Xét các số thực dương $a,b,x,y$ thỏa mãn $a,b&gt;1$ và $a^x=b^y=(ab)^{1/3}$. Giá trị nhỏ nhất của biểu thức $P=x+3y$ thuộc tập nào dưới đây?
+A. $\left[3;\dfrac{7}{2}\right)$.
+B. $\left[\dfrac{5}{2};3\right)$.
+C. $\left[2;\dfrac{5}{2}\right)$.
+D. $\left[\dfrac{7}{2};4\right)$.</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>C. $\left[2;\dfrac{5}{2}\right)$.</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_a b&gt;0$. $x=\dfrac{1}{3}(1+t)$, $y=\dfrac1{3}\left(1+\dfrac1t\right)$. $P=x+3y$ đạt cực tiểu tại $t=\sqrt{3}$, $P_{\min}=\dfrac{2 \sqrt{3}}{3} + \dfrac{4}{3}\approx2.488$, thuộc $\left[2;\dfrac{5}{2}\right)$.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
+++ b/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H590"/>
+  <dimension ref="A1:H613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25541,6 +25541,1018 @@
         </is>
       </c>
     </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>590</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>D29</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>p056_q34</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu giá trị nguyên dương của tham số $m$ để phương trình sau có nghiệm dương $16^x-2\cdot12^x+(m-2)\cdot9^x=0$?
+A. $4$.
+B. $1$.
+C. $3$.
+D. $2$.</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>D. $2$.</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>Chia hai vế cho $9^x$, đặt $t=\left(4/3\right)^x&gt;0$ (nghiệm dương $x&gt;0\Leftrightarrow t&gt;1$): $t^2-2t+2-m=0\Leftrightarrow m=2+2t-t^2=f(t)$. Vì $f$ nghịch biến trên $(1;+\infty)$ ($k\le2$) nên $m&lt;f(1)=3$. Vậy có $2$ giá trị nguyên dương $m\in\{1,\ldots,2\}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>591</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>D29</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>p056_q34</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu giá trị nguyên dương của tham số $m$ để phương trình sau có nghiệm dương $9^x-2\cdot6^x+(m-2)\cdot4^x=0$?
+A. $2$.
+B. $4$.
+C. $1$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>A. $2$.</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>Chia hai vế cho $4^x$, đặt $t=\left(3/2\right)^x&gt;0$ (nghiệm dương $x&gt;0\Leftrightarrow t&gt;1$): $t^2-2t+2-m=0\Leftrightarrow m=2+2t-t^2=f(t)$. Vì $f$ nghịch biến trên $(1;+\infty)$ ($k\le2$) nên $m&lt;f(1)=3$. Vậy có $2$ giá trị nguyên dương $m\in\{1,\ldots,2\}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>592</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>D29</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>p056_q34</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu giá trị nguyên dương của tham số $m$ để phương trình sau có nghiệm dương $9^x-2\cdot3^x+(m-3)\cdot1^x=0$?
+A. $4$.
+B. $6$.
+C. $2$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>Chia hai vế cho $1^x$, đặt $t=\left(3\right)^x&gt;0$ (nghiệm dương $x&gt;0\Leftrightarrow t&gt;1$): $t^2-2t+3-m=0\Leftrightarrow m=3+2t-t^2=f(t)$. Vì $f$ nghịch biến trên $(1;+\infty)$ ($k\le2$) nên $m&lt;f(1)=4$. Vậy có $3$ giá trị nguyên dương $m\in\{1,\ldots,3\}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>593</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>D29</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>p056_q34</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu giá trị nguyên dương của tham số $m$ để phương trình sau có nghiệm dương $4^x-2\cdot2^x+(m-1)\cdot1^x=0$?
+A. $2$.
+B. $3$.
+C. $0$.
+D. $1$.</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>D. $1$.</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>Chia hai vế cho $1^x$, đặt $t=\left(2\right)^x&gt;0$ (nghiệm dương $x&gt;0\Leftrightarrow t&gt;1$): $t^2-2t+1-m=0\Leftrightarrow m=1+2t-t^2=f(t)$. Vì $f$ nghịch biến trên $(1;+\infty)$ ($k\le2$) nên $m&lt;f(1)=2$. Vậy có $1$ giá trị nguyên dương $m\in\{1,\ldots,1\}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>594</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>D29</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>p056_q34</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu giá trị nguyên dương của tham số $m$ để phương trình sau có nghiệm dương $25^x-2\cdot10^x+(m-3)\cdot4^x=0$?
+A. $2$.
+B. $6$.
+C. $3$.
+D. $4$.</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>C. $3$.</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>Chia hai vế cho $4^x$, đặt $t=\left(5/2\right)^x&gt;0$ (nghiệm dương $x&gt;0\Leftrightarrow t&gt;1$): $t^2-2t+3-m=0\Leftrightarrow m=3+2t-t^2=f(t)$. Vì $f$ nghịch biến trên $(1;+\infty)$ ($k\le2$) nên $m&lt;f(1)=4$. Vậy có $3$ giá trị nguyên dương $m\in\{1,\ldots,3\}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>595</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>D29</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>p056_q34</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu giá trị nguyên dương của tham số $m$ để phương trình sau có nghiệm dương $16^x-2\cdot4^x+(m-2)\cdot1^x=0$?
+A. $1$.
+B. $2$.
+C. $4$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>B. $2$.</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>Chia hai vế cho $1^x$, đặt $t=\left(4\right)^x&gt;0$ (nghiệm dương $x&gt;0\Leftrightarrow t&gt;1$): $t^2-2t+2-m=0\Leftrightarrow m=2+2t-t^2=f(t)$. Vì $f$ nghịch biến trên $(1;+\infty)$ ($k\le2$) nên $m&lt;f(1)=3$. Vậy có $2$ giá trị nguyên dương $m\in\{1,\ldots,2\}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>596</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>D56</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>p128_q39</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\log_{3}\dfrac{x^2-16}{343} &lt; \log_{7}\dfrac{x^2-16}{27}$?
+A. $182$.
+B. $92$.
+C. $185$.
+D. $184$.</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>D. $184$.</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>Đặt $u=x^2-16&gt;0$. Biến đổi (đổi cơ số, gộp về cùng $\log_{3}u$) ta được $u&lt;(21)^{3}$. Vậy $0&lt;x^2-16&lt;(21)^{3} \Leftrightarrow 16&lt;x^2&lt;9277$, có $184$ số nguyên $x$ thỏa mãn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>597</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>D56</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>p128_q39</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\log_{2}\dfrac{x^2-9}{25} &lt; \log_{5}\dfrac{x^2-9}{4}$?
+A. $14$.
+B. $15$.
+C. $12$.
+D. $7$.</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>A. $14$.</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>Đặt $u=x^2-9&gt;0$. Biến đổi (đổi cơ số, gộp về cùng $\log_{2}u$) ta được $u&lt;(10)^{2}$. Vậy $0&lt;x^2-9&lt;(10)^{2} \Leftrightarrow 9&lt;x^2&lt;109$, có $14$ số nguyên $x$ thỏa mãn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>598</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>D56</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>p128_q39</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\log_{2}\dfrac{x^2-4}{27} &lt; \log_{3}\dfrac{x^2-4}{8}$?
+A. $24$.
+B. $12$.
+C. $25$.
+D. $22$.</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>A. $24$.</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>Đặt $u=x^2-4&gt;0$. Biến đổi (đổi cơ số, gộp về cùng $\log_{2}u$) ta được $u&lt;(6)^{3}$. Vậy $0&lt;x^2-4&lt;(6)^{3} \Leftrightarrow 4&lt;x^2&lt;220$, có $24$ số nguyên $x$ thỏa mãn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>599</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>D56</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>p128_q39</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\log_{3}\dfrac{x^2-16}{25} &lt; \log_{5}\dfrac{x^2-16}{9}$?
+A. $20$.
+B. $22$.
+C. $23$.
+D. $11$.</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>B. $22$.</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>Đặt $u=x^2-16&gt;0$. Biến đổi (đổi cơ số, gộp về cùng $\log_{3}u$) ta được $u&lt;(15)^{2}$. Vậy $0&lt;x^2-16&lt;(15)^{2} \Leftrightarrow 16&lt;x^2&lt;241$, có $22$ số nguyên $x$ thỏa mãn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>600</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>D56</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>p128_q39</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\log_{2}\dfrac{x^2-25}{49} &lt; \log_{7}\dfrac{x^2-25}{4}$?
+A. $16$.
+B. $19$.
+C. $18$.
+D. $9$.</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>C. $18$.</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>Đặt $u=x^2-25&gt;0$. Biến đổi (đổi cơ số, gộp về cùng $\log_{2}u$) ta được $u&lt;(14)^{2}$. Vậy $0&lt;x^2-25&lt;(14)^{2} \Leftrightarrow 25&lt;x^2&lt;221$, có $18$ số nguyên $x$ thỏa mãn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>601</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>D83</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>p213_q39</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\left(3^{x^2}-3^{2x}\right)\left[\log_{2}(x+6)-3\right]\le 0$?
+A. $9$.
+B. $8$.
+C. $6$.
+D. $7$.</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>D. $7$.</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>Điều kiện xác định $x&gt;-6$. Xét $f(x)=(3^{x^2}-3^{2x})[\log_{2}(x+6)-3]$. $f(x)=0\Leftrightarrow x^2=2x$ hoặc $x+6=2^{3}\Leftrightarrow x=0$ hoặc $x=2$ (nghiệm kép). Xét dấu: $f(x)\le0$ trên $S=(-6;0]\cup\{2\}$. Vậy có $7$ số nguyên $x$ thỏa mãn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>602</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>D83</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>p213_q39</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\left(2^{x^2}-2^{2x}\right)\left[\log_{2}(x+14)-4\right]\le 0$?
+A. $17$.
+B. $15$.
+C. $14$.
+D. $16$.</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>B. $15$.</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>Điều kiện xác định $x&gt;-14$. Xét $f(x)=(2^{x^2}-2^{2x})[\log_{2}(x+14)-4]$. $f(x)=0\Leftrightarrow x^2=2x$ hoặc $x+14=2^{4}\Leftrightarrow x=0$ hoặc $x=2$ (nghiệm kép). Xét dấu: $f(x)\le0$ trên $S=(-14;0]\cup\{2\}$. Vậy có $15$ số nguyên $x$ thỏa mãn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>603</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>D83</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>p213_q39</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\left(3^{x^2}-3^{2x}\right)\left[\log_{2}(x+30)-5\right]\le 0$?
+A. $31$.
+B. $32$.
+C. $30$.
+D. $33$.</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>A. $31$.</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>Điều kiện xác định $x&gt;-30$. Xét $f(x)=(3^{x^2}-3^{2x})[\log_{2}(x+30)-5]$. $f(x)=0\Leftrightarrow x^2=2x$ hoặc $x+30=2^{5}\Leftrightarrow x=0$ hoặc $x=2$ (nghiệm kép). Xét dấu: $f(x)\le0$ trên $S=(-30;0]\cup\{2\}$. Vậy có $31$ số nguyên $x$ thỏa mãn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>604</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>D83</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>p213_q39</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\left(2^{x^2}-2^{2x}\right)\left[\log_{3}(x+7)-2\right]\le 0$?
+A. $8$.
+B. $7$.
+C. $10$.
+D. $9$.</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>A. $8$.</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>Điều kiện xác định $x&gt;-7$. Xét $f(x)=(2^{x^2}-2^{2x})[\log_{3}(x+7)-2]$. $f(x)=0\Leftrightarrow x^2=2x$ hoặc $x+7=3^{2}\Leftrightarrow x=0$ hoặc $x=2$ (nghiệm kép). Xét dấu: $f(x)\le0$ trên $S=(-7;0]\cup\{2\}$. Vậy có $8$ số nguyên $x$ thỏa mãn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>605</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>D83</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>p213_q39</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\left(3^{x^2}-3^{2x}\right)\left[\log_{3}(x+25)-3\right]\le 0$?
+A. $27$.
+B. $28$.
+C. $26$.
+D. $25$.</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>C. $26$.</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>Điều kiện xác định $x&gt;-25$. Xét $f(x)=(3^{x^2}-3^{2x})[\log_{3}(x+25)-3]$. $f(x)=0\Leftrightarrow x^2=2x$ hoặc $x+25=3^{3}\Leftrightarrow x=0$ hoặc $x=2$ (nghiệm kép). Xét dấu: $f(x)\le0$ trên $S=(-25;0]\cup\{2\}$. Vậy có $26$ số nguyên $x$ thỏa mãn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>606</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>D83</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>p213_q39</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\left(2^{x^2}-2^{2x}\right)\left[\log_{5}(x+23)-2\right]\le 0$?
+A. $23$.
+B. $25$.
+C. $26$.
+D. $24$.</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>D. $24$.</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Điều kiện xác định $x&gt;-23$. Xét $f(x)=(2^{x^2}-2^{2x})[\log_{5}(x+23)-2]$. $f(x)=0\Leftrightarrow x^2=2x$ hoặc $x+23=5^{2}\Leftrightarrow x=0$ hoặc $x=2$ (nghiệm kép). Xét dấu: $f(x)\le0$ trên $S=(-23;0]\cup\{2\}$. Vậy có $24$ số nguyên $x$ thỏa mãn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>607</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>D88</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>p227_q40</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\left[\log_{3}(x^2+1)-\log_{3}(x+21)\right]\left(16-2^{x-1}\right)\ge 0$?
+A. $19$.
+B. $20$.
+C. $18$.
+D. $17$.</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>C. $18$.</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-21$. Nhân tử thứ nhất bằng 0 khi $x^2-x+1-21=0\Leftrightarrow x=-4$ hoặc $x=5$ (đổi dấu khi qua 2 nghiệm này, dương ngoài đoạn $[-4;5]$). Nhân tử thứ hai bằng 0 khi $x=5$ (dương khi $x&lt;5$). Xét dấu tích, tập nghiệm là $S=(-21;-4]\cup\{5\}$, có $18$ số nguyên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>608</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>D88</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>p227_q40</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\left[\log_{2}(x^2+1)-\log_{2}(x+13)\right]\left(8-2^{x-1}\right)\ge 0$?
+A. $12$.
+B. $11$.
+C. $10$.
+D. $13$.</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>B. $11$.</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-13$. Nhân tử thứ nhất bằng 0 khi $x^2-x+1-13=0\Leftrightarrow x=-3$ hoặc $x=4$ (đổi dấu khi qua 2 nghiệm này, dương ngoài đoạn $[-3;4]$). Nhân tử thứ hai bằng 0 khi $x=4$ (dương khi $x&lt;4$). Xét dấu tích, tập nghiệm là $S=(-13;-3]\cup\{4\}$, có $11$ số nguyên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>609</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>D88</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>p227_q40</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\left[\log_{3}(x^2+1)-\log_{3}(x+7)\right]\left(9-3^{x-1}\right)\ge 0$?
+A. $7$.
+B. $6$.
+C. $5$.
+D. $8$.</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>B. $6$.</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-7$. Nhân tử thứ nhất bằng 0 khi $x^2-x+1-7=0\Leftrightarrow x=-2$ hoặc $x=3$ (đổi dấu khi qua 2 nghiệm này, dương ngoài đoạn $[-2;3]$). Nhân tử thứ hai bằng 0 khi $x=3$ (dương khi $x&lt;3$). Xét dấu tích, tập nghiệm là $S=(-7;-2]\cup\{3\}$, có $6$ số nguyên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>610</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>D88</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>p227_q40</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\left[\log_{2}(x^2+1)-\log_{2}(x+31)\right]\left(32-2^{x-1}\right)\ge 0$?
+A. $27$.
+B. $29$.
+C. $28$.
+D. $26$.</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>A. $27$.</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-31$. Nhân tử thứ nhất bằng 0 khi $x^2-x+1-31=0\Leftrightarrow x=-5$ hoặc $x=6$ (đổi dấu khi qua 2 nghiệm này, dương ngoài đoạn $[-5;6]$). Nhân tử thứ hai bằng 0 khi $x=6$ (dương khi $x&lt;6$). Xét dấu tích, tập nghiệm là $S=(-31;-5]\cup\{6\}$, có $27$ số nguyên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>611</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>D88</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>p227_q40</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\left[\log_{3}(x^2+1)-\log_{3}(x+13)\right]\left(27-3^{x-1}\right)\ge 0$?
+A. $11$.
+B. $10$.
+C. $12$.
+D. $13$.</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>A. $11$.</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-13$. Nhân tử thứ nhất bằng 0 khi $x^2-x+1-13=0\Leftrightarrow x=-3$ hoặc $x=4$ (đổi dấu khi qua 2 nghiệm này, dương ngoài đoạn $[-3;4]$). Nhân tử thứ hai bằng 0 khi $x=4$ (dương khi $x&lt;4$). Xét dấu tích, tập nghiệm là $S=(-13;-3]\cup\{4\}$, có $11$ số nguyên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>612</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>D88</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>p227_q40</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ thỏa mãn $\left[\log_{2}(x^2+1)-\log_{2}(x+43)\right]\left(729-3^{x-1}\right)\ge 0$?
+A. $38$.
+B. $37$.
+C. $39$.
+D. $40$.</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>A. $38$.</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-43$. Nhân tử thứ nhất bằng 0 khi $x^2-x+1-43=0\Leftrightarrow x=-6$ hoặc $x=7$ (đổi dấu khi qua 2 nghiệm này, dương ngoài đoạn $[-6;7]$). Nhân tử thứ hai bằng 0 khi $x=7$ (dương khi $x&lt;7$). Xét dấu tích, tập nghiệm là $S=(-43;-6]\cup\{7\}$, có $38$ số nguyên.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
+++ b/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H613"/>
+  <dimension ref="A1:H640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26553,6 +26553,1194 @@
         </is>
       </c>
     </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>613</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>p038_q33</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Cho $a, b$ là các số thực dương thỏa mãn $a\neq 1, a\neq\sqrt{b}$ và $\log_a b=\sqrt{3}$. Tính $P=\log_{\frac{\sqrt{b}}{a}}\sqrt{\dfrac{b}{a}}$.
+A. $P=1 + \sqrt{3}$.
+B. $P=\sqrt{3} + 2$.
+C. $P=- \sqrt{3}$.
+D. $P=- \sqrt{3} - 1$.</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>D. $P=- \sqrt{3} - 1$.</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>$P=\dfrac{\log_a\sqrt{b/a}}{\log_a(\sqrt b/a)}=\dfrac{\frac12(\log_a b-1)}{\frac12\log_a b-1}=\dfrac{\sqrt{3}-1}{\sqrt{3}-2}=- \sqrt{3} - 1$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>614</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>p038_q33</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Cho $a, b$ là các số thực dương thỏa mãn $a\neq 1, a\neq\sqrt{b}$ và $\log_a b=\sqrt{5}$. Tính $P=\log_{\frac{\sqrt{b}}{a}}\sqrt{\dfrac{b}{a}}$.
+A. $P=\sqrt{5} + 3$.
+B. $P=-3 - \sqrt{5}$.
+C. $P=- \sqrt{5} - 2$.
+D. $P=\sqrt{5} + 4$.</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>A. $P=\sqrt{5} + 3$.</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>$P=\dfrac{\log_a\sqrt{b/a}}{\log_a(\sqrt b/a)}=\dfrac{\frac12(\log_a b-1)}{\frac12\log_a b-1}=\dfrac{\sqrt{5}-1}{\sqrt{5}-2}=\sqrt{5} + 3$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>615</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>p038_q33</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Cho $a, b$ là các số thực dương thỏa mãn $a\neq 1, a\neq\sqrt{b}$ và $\log_a b=\sqrt{2}$. Tính $P=\log_{\frac{\sqrt{b}}{a}}\sqrt{\dfrac{b}{a}}$.
+A. $P=\dfrac{\sqrt{2}}{2}$.
+B. $P=\dfrac{\sqrt{2}}{2} + 1$.
+C. $P=1 - \dfrac{\sqrt{2}}{2}$.
+D. $P=- \dfrac{\sqrt{2}}{2}$.</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>D. $P=- \dfrac{\sqrt{2}}{2}$.</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>$P=\dfrac{\log_a\sqrt{b/a}}{\log_a(\sqrt b/a)}=\dfrac{\frac12(\log_a b-1)}{\frac12\log_a b-1}=\dfrac{\sqrt{2}-1}{\sqrt{2}-2}=- \dfrac{\sqrt{2}}{2}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>616</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>p038_q33</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Cho $a, b$ là các số thực dương thỏa mãn $a\neq 1, a\neq\sqrt{b}$ và $\log_a b=\sqrt{7}$. Tính $P=\log_{\frac{\sqrt{b}}{a}}\sqrt{\dfrac{b}{a}}$.
+A. $P=\dfrac{\sqrt{7}}{3} + \dfrac{8}{3}$.
+B. $P=- \dfrac{\sqrt{7}}{3} - \dfrac{2}{3}$.
+C. $P=\dfrac{\sqrt{7}}{3} + \dfrac{5}{3}$.
+D. $P=- \dfrac{5}{3} - \dfrac{\sqrt{7}}{3}$.</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>C. $P=\dfrac{\sqrt{7}}{3} + \dfrac{5}{3}$.</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>$P=\dfrac{\log_a\sqrt{b/a}}{\log_a(\sqrt b/a)}=\dfrac{\frac12(\log_a b-1)}{\frac12\log_a b-1}=\dfrac{\sqrt{7}-1}{\sqrt{7}-2}=\dfrac{\sqrt{7}}{3} + \dfrac{5}{3}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>617</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>p038_q33</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Cho $a, b$ là các số thực dương thỏa mãn $a\neq 1, a\neq\sqrt{b}$ và $\log_a b=3$. Tính $P=\log_{\frac{\sqrt{b}}{a}}\sqrt{\dfrac{b}{a}}$.
+A. $P=-1$.
+B. $P=3$.
+C. $P=2$.
+D. $P=-2$.</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>C. $P=2$.</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>$P=\dfrac{\log_a\sqrt{b/a}}{\log_a(\sqrt b/a)}=\dfrac{\frac12(\log_a b-1)}{\frac12\log_a b-1}=\dfrac{3-1}{3-2}=2$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>618</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>p038_q33</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Cho $a, b$ là các số thực dương thỏa mãn $a\neq 1, a\neq\sqrt{b}$ và $\log_a b=5$. Tính $P=\log_{\frac{\sqrt{b}}{a}}\sqrt{\dfrac{b}{a}}$.
+A. $P=- \dfrac{1}{3}$.
+B. $P=\dfrac{7}{3}$.
+C. $P=- \dfrac{4}{3}$.
+D. $P=\dfrac{4}{3}$.</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>D. $P=\dfrac{4}{3}$.</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>$P=\dfrac{\log_a\sqrt{b/a}}{\log_a(\sqrt b/a)}=\dfrac{\frac12(\log_a b-1)}{\frac12\log_a b-1}=\dfrac{5-1}{5-2}=\dfrac{4}{3}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>619</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>p038_q33</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Cho $a, b$ là các số thực dương thỏa mãn $a\neq 1, a\neq\sqrt{b}$ và $\log_a b=10$. Tính $P=\log_{\frac{\sqrt{b}}{a}}\sqrt{\dfrac{b}{a}}$.
+A. $P=\dfrac{17}{8}$.
+B. $P=- \dfrac{1}{8}$.
+C. $P=\dfrac{9}{8}$.
+D. $P=- \dfrac{9}{8}$.</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>C. $P=\dfrac{9}{8}$.</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>$P=\dfrac{\log_a\sqrt{b/a}}{\log_a(\sqrt b/a)}=\dfrac{\frac12(\log_a b-1)}{\frac12\log_a b-1}=\dfrac{10-1}{10-2}=\dfrac{9}{8}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>620</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>D24</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>p041_q40</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Cho hàm số $y=\dfrac{\ln x}{x^{2}}$, mệnh đề nào dưới đây đúng?
+A. $3y'+xy''=\dfrac{2}{x^{3}}$.
+B. $2y'+xy''=-\dfrac{2}{x^{3}}$.
+C. $y'+xy''=-\dfrac{2}{x^{3}}$.
+D. $3y'+xy''=-\dfrac{2}{x^{3}}$.</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>D. $3y'+xy''=-\dfrac{2}{x^{3}}$.</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>Ta có $x^{2}y=\ln x$. Lấy đạo hàm hai vế: $2xy+x^{2}y'=\dfrac1x$. Lấy đạo hàm tiếp rồi rút gọn (thay lại $y$) ta được $3y'+xy''=-\dfrac{2}{x^{3}}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>621</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>D24</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>p041_q40</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Cho hàm số $y=\dfrac{\ln x}{x^{3}}$, mệnh đề nào dưới đây đúng?
+A. $3y'+xy''=-\dfrac{3}{x^{4}}$.
+B. $4y'+xy''=-\dfrac{3}{x^{4}}$.
+C. $y'+xy''=-\dfrac{3}{x^{4}}$.
+D. $4y'+xy''=\dfrac{3}{x^{4}}$.</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>B. $4y'+xy''=-\dfrac{3}{x^{4}}$.</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>Ta có $x^{3}y=\ln x$. Lấy đạo hàm hai vế: $3x^{2}y+x^{3}y'=\dfrac1x$. Lấy đạo hàm tiếp rồi rút gọn (thay lại $y$) ta được $4y'+xy''=-\dfrac{3}{x^{4}}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>622</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>D24</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>p041_q40</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Cho hàm số $y=\dfrac{\ln x}{x^{4}}$, mệnh đề nào dưới đây đúng?
+A. $5y'+xy''=-\dfrac{4}{x^{5}}$.
+B. $4y'+xy''=-\dfrac{4}{x^{5}}$.
+C. $5y'+xy''=\dfrac{4}{x^{5}}$.
+D. $y'+xy''=-\dfrac{4}{x^{5}}$.</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>A. $5y'+xy''=-\dfrac{4}{x^{5}}$.</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Ta có $x^{4}y=\ln x$. Lấy đạo hàm hai vế: $4x^{3}y+x^{4}y'=\dfrac1x$. Lấy đạo hàm tiếp rồi rút gọn (thay lại $y$) ta được $5y'+xy''=-\dfrac{4}{x^{5}}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>623</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>D24</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>p041_q40</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Cho hàm số $y=\dfrac{\ln x}{x^{5}}$, mệnh đề nào dưới đây đúng?
+A. $6y'+xy''=\dfrac{5}{x^{6}}$.
+B. $6y'+xy''=-\dfrac{5}{x^{6}}$.
+C. $5y'+xy''=-\dfrac{5}{x^{6}}$.
+D. $y'+xy''=-\dfrac{5}{x^{6}}$.</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>B. $6y'+xy''=-\dfrac{5}{x^{6}}$.</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>Ta có $x^{5}y=\ln x$. Lấy đạo hàm hai vế: $5x^{4}y+x^{5}y'=\dfrac1x$. Lấy đạo hàm tiếp rồi rút gọn (thay lại $y$) ta được $6y'+xy''=-\dfrac{5}{x^{6}}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>624</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>D24</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>p041_q40</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Cho hàm số $y=\dfrac{\ln x}{x^{6}}$, mệnh đề nào dưới đây đúng?
+A. $6y'+xy''=-\dfrac{6}{x^{7}}$.
+B. $y'+xy''=-\dfrac{6}{x^{7}}$.
+C. $7y'+xy''=\dfrac{6}{x^{7}}$.
+D. $7y'+xy''=-\dfrac{6}{x^{7}}$.</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>D. $7y'+xy''=-\dfrac{6}{x^{7}}$.</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Ta có $x^{6}y=\ln x$. Lấy đạo hàm hai vế: $6x^{5}y+x^{6}y'=\dfrac1x$. Lấy đạo hàm tiếp rồi rút gọn (thay lại $y$) ta được $7y'+xy''=-\dfrac{6}{x^{7}}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>625</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>D39</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>p087_q41</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Cho $x,y$ là các số thực dương thỏa mãn $\log_{9}x=\log_{6}y=\log_{4}(2x+y)$. Giá trị của $\dfrac{x}{y}$ bằng
+A. $2$.
+B. $\dfrac{3}{2}$.
+C. $- \dfrac{1}{2}$.
+D. $\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>D. $\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>Đặt $t$ là giá trị chung. $x=(9)^t,y=(6)^t,2x+y=(4)^t$. Chia cả hai vế cho $(4)^t$ và đặt $u=(p/q)^t=x/y$: $2u^2+u-1=0\Rightarrow u=\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>626</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>D39</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>p087_q41</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Cho $x,y$ là các số thực dương thỏa mãn $\log_{4}x=\log_{6}y=\log_{9}(2x+y)$. Giá trị của $\dfrac{x}{y}$ bằng
+A. $\dfrac{1}{2}$.
+B. $2$.
+C. $\dfrac{3}{2}$.
+D. $- \dfrac{1}{2}$.</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>A. $\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>Đặt $t$ là giá trị chung. $x=(4)^t,y=(6)^t,2x+y=(9)^t$. Chia cả hai vế cho $(9)^t$ và đặt $u=(p/q)^t=x/y$: $2u^2+u-1=0\Rightarrow u=\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>627</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>D39</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>p087_q41</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Cho $x,y$ là các số thực dương thỏa mãn $\log_{25}x=\log_{10}y=\log_{4}(2x+y)$. Giá trị của $\dfrac{x}{y}$ bằng
+A. $\dfrac{3}{2}$.
+B. $\dfrac{1}{2}$.
+C. $2$.
+D. $- \dfrac{1}{2}$.</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>B. $\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>Đặt $t$ là giá trị chung. $x=(25)^t,y=(10)^t,2x+y=(4)^t$. Chia cả hai vế cho $(4)^t$ và đặt $u=(p/q)^t=x/y$: $2u^2+u-1=0\Rightarrow u=\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>628</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>D39</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>p087_q41</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Cho $x,y$ là các số thực dương thỏa mãn $\log_{16}x=\log_{12}y=\log_{9}(2x+y)$. Giá trị của $\dfrac{x}{y}$ bằng
+A. $\dfrac{3}{2}$.
+B. $- \dfrac{1}{2}$.
+C. $\dfrac{1}{2}$.
+D. $2$.</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>C. $\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>Đặt $t$ là giá trị chung. $x=(16)^t,y=(12)^t,2x+y=(9)^t$. Chia cả hai vế cho $(9)^t$ và đặt $u=(p/q)^t=x/y$: $2u^2+u-1=0\Rightarrow u=\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>629</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>D39</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>p087_q41</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Cho $x,y$ là các số thực dương thỏa mãn $\log_{9}x=\log_{15}y=\log_{25}(2x+y)$. Giá trị của $\dfrac{x}{y}$ bằng
+A. $2$.
+B. $\dfrac{1}{2}$.
+C. $- \dfrac{1}{2}$.
+D. $\dfrac{3}{2}$.</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>B. $\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>Đặt $t$ là giá trị chung. $x=(9)^t,y=(15)^t,2x+y=(25)^t$. Chia cả hai vế cho $(25)^t$ và đặt $u=(p/q)^t=x/y$: $2u^2+u-1=0\Rightarrow u=\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>630</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>D39</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>p087_q41</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Cho $x,y$ là các số thực dương thỏa mãn $\log_{25}x=\log_{15}y=\log_{9}(2x+y)$. Giá trị của $\dfrac{x}{y}$ bằng
+A. $\dfrac{3}{2}$.
+B. $- \dfrac{1}{2}$.
+C. $2$.
+D. $\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>D. $\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Đặt $t$ là giá trị chung. $x=(25)^t,y=(15)^t,2x+y=(9)^t$. Chia cả hai vế cho $(9)^t$ và đặt $u=(p/q)^t=x/y$: $2u^2+u-1=0\Rightarrow u=\dfrac{1}{2}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>631</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>p186_q47</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\left(2\log_{2}^2x-3\log_{2}x-2\right)\sqrt{3^x-m}=0$ ($m$ là tham số thực). Có tất cả bao nhiêu giá trị nguyên dương của $m$ để phương trình đã cho có đúng hai nghiệm phân biệt?
+A. $78$.
+B. $79$.
+C. $81$.
+D. $80$.</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>B. $79$.</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;0,3^x\ge m$. Nhân tử đầu có nghiệm $\log_{2}x=2$ hay $\log_{2}x=-\dfrac12$, tức $x=4$ hoặc $x=\dfrac{\sqrt{2}}{2}$; nhân tử sau có $x=\log_{3}m$. Xét các trường hợp theo $m$ tương tự bản gốc (đối chiếu điều kiện $\ge m$ cho từng nghiệm cố định, cộng thêm miền $m$ để nghiệm thứ ba xuất hiện đúng một lần) cho tổng cộng $79$ giá trị nguyên dương.</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>632</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>p186_q47</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\left(2\log_{2}^2x-3\log_{2}x-2\right)\sqrt{2^x-m}=0$ ($m$ là tham số thực). Có tất cả bao nhiêu giá trị nguyên dương của $m$ để phương trình đã cho có đúng hai nghiệm phân biệt?
+A. $14$.
+B. $16$.
+C. $17$.
+D. $15$.</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>D. $15$.</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;0,2^x\ge m$. Nhân tử đầu có nghiệm $\log_{2}x=2$ hay $\log_{2}x=-\dfrac12$, tức $x=4$ hoặc $x=\dfrac{\sqrt{2}}{2}$; nhân tử sau có $x=\log_{2}m$. Xét các trường hợp theo $m$ tương tự bản gốc (đối chiếu điều kiện $\ge m$ cho từng nghiệm cố định, cộng thêm miền $m$ để nghiệm thứ ba xuất hiện đúng một lần) cho tổng cộng $15$ giá trị nguyên dương.</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>633</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>p186_q47</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\left(2\log_{3}^2x-3\log_{3}x-2\right)\sqrt{2^x-m}=0$ ($m$ là tham số thực). Có tất cả bao nhiêu giá trị nguyên dương của $m$ để phương trình đã cho có đúng hai nghiệm phân biệt?
+A. $250$.
+B. $248$.
+C. $251$.
+D. $249$.</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>D. $249$.</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;0,2^x\ge m$. Nhân tử đầu có nghiệm $\log_{3}x=2$ hay $\log_{3}x=-\dfrac12$, tức $x=9$ hoặc $x=\dfrac{\sqrt{3}}{3}$; nhân tử sau có $x=\log_{2}m$. Xét các trường hợp theo $m$ tương tự bản gốc (đối chiếu điều kiện $\ge m$ cho từng nghiệm cố định, cộng thêm miền $m$ để nghiệm thứ ba xuất hiện đúng một lần) cho tổng cộng $249$ giá trị nguyên dương.</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>634</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>p186_q47</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\left(2\log_{2}^2x-3\log_{2}x-2\right)\sqrt{5^x-m}=0$ ($m$ là tham số thực). Có tất cả bao nhiêu giá trị nguyên dương của $m$ để phương trình đã cho có đúng hai nghiệm phân biệt?
+A. $248$.
+B. $249$.
+C. $246$.
+D. $247$.</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>D. $247$.</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;0,5^x\ge m$. Nhân tử đầu có nghiệm $\log_{2}x=2$ hay $\log_{2}x=-\dfrac12$, tức $x=4$ hoặc $x=\dfrac{\sqrt{2}}{2}$; nhân tử sau có $x=\log_{5}m$. Xét các trường hợp theo $m$ tương tự bản gốc (đối chiếu điều kiện $\ge m$ cho từng nghiệm cố định, cộng thêm miền $m$ để nghiệm thứ ba xuất hiện đúng một lần) cho tổng cộng $247$ giá trị nguyên dương.</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>635</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>p186_q47</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Cho phương trình $\left(2\log_{3}^2x-3\log_{3}x-2\right)\sqrt{5^x-m}=0$ ($m$ là tham số thực). Có tất cả bao nhiêu giá trị nguyên dương của $m$ để phương trình đã cho có đúng hai nghiệm phân biệt?
+A. $248$.
+B. $247$.
+C. $250$.
+D. $249$.</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>A. $248$.</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;0,5^x\ge m$. Nhân tử đầu có nghiệm $\log_{3}x=2$ hay $\log_{3}x=-\dfrac12$, tức $x=9$ hoặc $x=\dfrac{\sqrt{3}}{3}$; nhân tử sau có $x=\log_{5}m$. Xét các trường hợp theo $m$ tương tự bản gốc (đối chiếu điều kiện $\ge m$ cho từng nghiệm cố định, cộng thêm miền $m$ để nghiệm thứ ba xuất hiện đúng một lần) cho tổng cộng $248$ giá trị nguyên dương.</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>636</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>D93</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>p242_q39</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên dương $a$ sao cho ứng với mỗi $a$ có đúng ba số nguyên $b$ thỏa mãn $(3^b-3)(a\cdot2^b-18)&lt;0$?
+A. $75$.
+B. $73$.
+C. $72$.
+D. $74$.</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>B. $73$.</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>Xét hai trường hợp $b&gt;1$ và $b&lt;1$ (dấu của $3^b-3$) rồi tìm khoảng của $a$ tương ứng để đúng 3 giá trị nguyên $b$ thỏa mãn ở mỗi trường hợp; gộp lại được tổng cộng $73$ giá trị nguyên dương $a$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>637</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>D93</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>p242_q39</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên dương $a$ sao cho ứng với mỗi $a$ có đúng ba số nguyên $b$ thỏa mãn $(2^b-2)(a\cdot3^b-24)&lt;0$?
+A. $182$.
+B. $183$.
+C. $185$.
+D. $184$.</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>B. $183$.</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Xét hai trường hợp $b&gt;1$ và $b&lt;1$ (dấu của $2^b-2$) rồi tìm khoảng của $a$ tương ứng để đúng 3 giá trị nguyên $b$ thỏa mãn ở mỗi trường hợp; gộp lại được tổng cộng $183$ giá trị nguyên dương $a$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>638</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>D93</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>p242_q39</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên dương $a$ sao cho ứng với mỗi $a$ có đúng ba số nguyên $b$ thỏa mãn $(3^b-3)(a\cdot2^b-20)&lt;0$?
+A. $82$.
+B. $83$.
+C. $81$.
+D. $80$.</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>C. $81$.</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>Xét hai trường hợp $b&gt;1$ và $b&lt;1$ (dấu của $3^b-3$) rồi tìm khoảng của $a$ tương ứng để đúng 3 giá trị nguyên $b$ thỏa mãn ở mỗi trường hợp; gộp lại được tổng cộng $81$ giá trị nguyên dương $a$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>639</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>D93</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>p242_q39</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên dương $a$ sao cho ứng với mỗi $a$ có đúng ba số nguyên $b$ thỏa mãn $(2^b-2)(a\cdot2^b-16)&lt;0$?
+A. $64$.
+B. $66$.
+C. $63$.
+D. $65$.</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>A. $64$.</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>Xét hai trường hợp $b&gt;1$ và $b&lt;1$ (dấu của $2^b-2$) rồi tìm khoảng của $a$ tương ứng để đúng 3 giá trị nguyên $b$ thỏa mãn ở mỗi trường hợp; gộp lại được tổng cộng $64$ giá trị nguyên dương $a$.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
+++ b/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H640"/>
+  <dimension ref="A1:H648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27741,6 +27741,358 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>640</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>D79</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>p204_q49</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ sao cho ứng với mỗi $x$ có không quá 242 số nguyên $y$ thỏa mãn $\log_{4}(x^2+y)\ge \log_{3}(x+y)$?
+A. $55$.
+B. $57$.
+C. $58$.
+D. $56$.</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>D. $56$.</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>Điều kiện $x+y&gt;0, x^2+y&gt;0$. Đặt $t=x+y$ ($t\ge1$ do $x,y$ nguyên). Bất phương trình $\Leftrightarrow x^2-x\ge t^{\log_{3}4}-t=f(t)$, với $f$ đồng biến trên $[1;+\infty)$. Có không quá 242 số nguyên $y$ (tức $t$) thỏa mãn khi $x^2-x&lt;f(243)\approx781.00$. Giải ra $x\in\{-27,\ldots,28\}$, có $56$ số nguyên $x$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>641</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>D79</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>p204_q49</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ sao cho ứng với mỗi $x$ có không quá 300 số nguyên $y$ thỏa mãn $\log_{9}(x^2+y)\ge \log_{5}(x+y)$?
+A. $91$.
+B. $92$.
+C. $94$.
+D. $93$.</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>B. $92$.</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>Điều kiện $x+y&gt;0, x^2+y&gt;0$. Đặt $t=x+y$ ($t\ge1$ do $x,y$ nguyên). Bất phương trình $\Leftrightarrow x^2-x\ge t^{\log_{5}9}-t=f(t)$, với $f$ đồng biến trên $[1;+\infty)$. Có không quá 300 số nguyên $y$ (tức $t$) thỏa mãn khi $x^2-x&lt;f(301)\approx2118.75$. Giải ra $x\in\{-45,\ldots,46\}$, có $92$ số nguyên $x$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>642</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>D79</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>p204_q49</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ sao cho ứng với mỗi $x$ có không quá 100 số nguyên $y$ thỏa mãn $\log_{4}(x^2+y)\ge \log_{3}(x+y)$?
+A. $30$.
+B. $31$.
+C. $32$.
+D. $29$.</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>A. $30$.</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Điều kiện $x+y&gt;0, x^2+y&gt;0$. Đặt $t=x+y$ ($t\ge1$ do $x,y$ nguyên). Bất phương trình $\Leftrightarrow x^2-x\ge t^{\log_{3}4}-t=f(t)$, với $f$ đồng biến trên $[1;+\infty)$. Có không quá 100 số nguyên $y$ (tức $t$) thỏa mãn khi $x^2-x&lt;f(101)\approx237.20$. Giải ra $x\in\{-14,\ldots,15\}$, có $30$ số nguyên $x$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>643</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>D79</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>p204_q49</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ sao cho ứng với mỗi $x$ có không quá 150 số nguyên $y$ thỏa mãn $\log_{3}(x^2+y)\ge \log_{2}(x+y)$?
+A. $103$.
+B. $105$.
+C. $106$.
+D. $104$.</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>D. $104$.</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>Điều kiện $x+y&gt;0, x^2+y&gt;0$. Đặt $t=x+y$ ($t\ge1$ do $x,y$ nguyên). Bất phương trình $\Leftrightarrow x^2-x\ge t^{\log_{2}3}-t=f(t)$, với $f$ đồng biến trên $[1;+\infty)$. Có không quá 150 số nguyên $y$ (tức $t$) thỏa mãn khi $x^2-x&lt;f(151)\approx2690.82$. Giải ra $x\in\{-51,\ldots,52\}$, có $104$ số nguyên $x$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="n">
+        <v>644</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>D79</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>p204_q49</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ sao cho ứng với mỗi $x$ có không quá 200 số nguyên $y$ thỏa mãn $\log_{8}(x^2+y)\ge \log_{5}(x+y)$?
+A. $54$.
+B. $53$.
+C. $56$.
+D. $55$.</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>A. $54$.</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>Điều kiện $x+y&gt;0, x^2+y&gt;0$. Đặt $t=x+y$ ($t\ge1$ do $x,y$ nguyên). Bất phương trình $\Leftrightarrow x^2-x\ge t^{\log_{5}8}-t=f(t)$, với $f$ đồng biến trên $[1;+\infty)$. Có không quá 200 số nguyên $y$ (tức $t$) thỏa mãn khi $x^2-x&lt;f(201)\approx744.80$. Giải ra $x\in\{-26,\ldots,27\}$, có $54$ số nguyên $x$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="n">
+        <v>645</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>D89</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>p230_q45</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên dương $y$ sao cho tồn tại số thực $x\in(1;5)$ thỏa mãn $4(x-1)e^x=y(e^x+xy-2x^2-3)$?
+A. $12$.
+B. $13$.
+C. $14$.
+D. $11$.</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>A. $12$.</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>Xét $f(x)=4(x-1)e^x-y(e^x+xy-2x^2-3)$ trên $[1;5]$. Có thể chứng minh $f$ đơn điệu theo từng khoảng ứng với $x=y/4$ (tương tự bản gốc), nên phương trình có nghiệm $x\in(1;5)$ khi và chỉ khi $f(1)\cdot f(5)\le0$. Kiểm tra trực tiếp cho $y\in\mathbb{Z}^+$ ta được $y\in\{3,\ldots,14\}$, có $12$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="n">
+        <v>646</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>D89</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>p230_q45</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên dương $y$ sao cho tồn tại số thực $x\in(1;6)$ thỏa mãn $3(x-1)e^x=y(e^x+xy-2x^2-4)$?
+A. $11$.
+B. $12$.
+C. $10$.
+D. $13$.</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>A. $11$.</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>Xét $f(x)=3(x-1)e^x-y(e^x+xy-2x^2-4)$ trên $[1;6]$. Có thể chứng minh $f$ đơn điệu theo từng khoảng ứng với $x=y/3$ (tương tự bản gốc), nên phương trình có nghiệm $x\in(1;6)$ khi và chỉ khi $f(1)\cdot f(6)\le0$. Kiểm tra trực tiếp cho $y\in\mathbb{Z}^+$ ta được $y\in\{4,\ldots,14\}$, có $11$ giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="n">
+        <v>647</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>D89</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>p230_q45</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên dương $y$ sao cho tồn tại số thực $x\in(1;5)$ thỏa mãn $4(x-1)e^x=y(e^x+xy-x^2-3)$?
+A. $13$.
+B. $11$.
+C. $12$.
+D. $10$.</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>B. $11$.</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>Xét $f(x)=4(x-1)e^x-y(e^x+xy-x^2-3)$ trên $[1;5]$. Có thể chứng minh $f$ đơn điệu theo từng khoảng ứng với $x=y/4$ (tương tự bản gốc), nên phương trình có nghiệm $x\in(1;5)$ khi và chỉ khi $f(1)\cdot f(5)\le0$. Kiểm tra trực tiếp cho $y\in\mathbb{Z}^+$ ta được $y\in\{2,\ldots,12\}$, có $11$ giá trị.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
+++ b/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H648"/>
+  <dimension ref="A1:H658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28093,6 +28093,446 @@
         </is>
       </c>
     </row>
+    <row r="649">
+      <c r="A649" t="n">
+        <v>648</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>p021_q21</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = \log^2_{\frac{a}{b}}a + 4\log_b\left(\dfrac{a}{b}\right)$.
+A. $P_{\min}=7$.
+B. $P_{\min}=16$.
+C. $P_{\min}=8$.
+D. $P_{\min}=9$.</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>C. $P_{\min}=8$.</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{a/b}b&gt;0$. Ta có $\log_{a/b}a=1+t$ và $\log_b(a/b)=\dfrac1t$, nên $P=(1+t)^2+\dfrac{4}{t}=f(t)$. Xét $f'(t)=2(1+t)-\dfrac{4}{t^2}$, $f'(t)=0$ tại $t=1$ (nghiệm dương duy nhất). $f\left(1\right)=8$ là giá trị nhỏ nhất. Vậy $P_{\min}=8$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="n">
+        <v>649</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>p021_q21</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 2\log^2_{\frac{a}{b}}a + 8\log_b\left(\dfrac{a}{b}\right)$.
+A. $P_{\min}=32$.
+B. $P_{\min}=16$.
+C. $P_{\min}=17$.
+D. $P_{\min}=15$.</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>B. $P_{\min}=16$.</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{a/b}b&gt;0$. Ta có $\log_{a/b}a=1+t$ và $\log_b(a/b)=\dfrac1t$, nên $P=2(1+t)^2+\dfrac{8}{t}=f(t)$. Xét $f'(t)=4(1+t)-\dfrac{8}{t^2}$, $f'(t)=0$ tại $t=1$ (nghiệm dương duy nhất). $f\left(1\right)=16$ là giá trị nhỏ nhất. Vậy $P_{\min}=16$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>650</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>p021_q21</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 3\log^2_{\frac{a}{b}}a + 12\log_b\left(\dfrac{a}{b}\right)$.
+A. $P_{\min}=23$.
+B. $P_{\min}=25$.
+C. $P_{\min}=24$.
+D. $P_{\min}=48$.</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>C. $P_{\min}=24$.</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{a/b}b&gt;0$. Ta có $\log_{a/b}a=1+t$ và $\log_b(a/b)=\dfrac1t$, nên $P=3(1+t)^2+\dfrac{12}{t}=f(t)$. Xét $f'(t)=6(1+t)-\dfrac{12}{t^2}$, $f'(t)=0$ tại $t=1$ (nghiệm dương duy nhất). $f\left(1\right)=24$ là giá trị nhỏ nhất. Vậy $P_{\min}=24$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="n">
+        <v>651</v>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>p021_q21</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 4\log^2_{\frac{a}{b}}a + 3\log_b\left(\dfrac{a}{b}\right)$.
+A. $P_{\min}=30$.
+B. $P_{\min}=16$.
+C. $P_{\min}=15$.
+D. $P_{\min}=14$.</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>C. $P_{\min}=15$.</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{a/b}b&gt;0$. Ta có $\log_{a/b}a=1+t$ và $\log_b(a/b)=\dfrac1t$, nên $P=4(1+t)^2+\dfrac{3}{t}=f(t)$. Xét $f'(t)=8(1+t)-\dfrac{3}{t^2}$, $f'(t)=0$ tại $t=\dfrac{1}{2}$ (nghiệm dương duy nhất). $f\left(\dfrac{1}{2}\right)=15$ là giá trị nhỏ nhất. Vậy $P_{\min}=15$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="n">
+        <v>652</v>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>p021_q21</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 5\log^2_{\frac{a}{b}}a + 20\log_b\left(\dfrac{a}{b}\right)$.
+A. $P_{\min}=39$.
+B. $P_{\min}=40$.
+C. $P_{\min}=80$.
+D. $P_{\min}=41$.</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>B. $P_{\min}=40$.</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{a/b}b&gt;0$. Ta có $\log_{a/b}a=1+t$ và $\log_b(a/b)=\dfrac1t$, nên $P=5(1+t)^2+\dfrac{20}{t}=f(t)$. Xét $f'(t)=10(1+t)-\dfrac{20}{t^2}$, $f'(t)=0$ tại $t=1$ (nghiệm dương duy nhất). $f\left(1\right)=40$ là giá trị nhỏ nhất. Vậy $P_{\min}=40$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="n">
+        <v>653</v>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>p021_q21</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 6\log^2_{\frac{a}{b}}a + 24\log_b\left(\dfrac{a}{b}\right)$.
+A. $P_{\min}=48$.
+B. $P_{\min}=49$.
+C. $P_{\min}=47$.
+D. $P_{\min}=96$.</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>A. $P_{\min}=48$.</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{a/b}b&gt;0$. Ta có $\log_{a/b}a=1+t$ và $\log_b(a/b)=\dfrac1t$, nên $P=6(1+t)^2+\dfrac{24}{t}=f(t)$. Xét $f'(t)=12(1+t)-\dfrac{24}{t^2}$, $f'(t)=0$ tại $t=1$ (nghiệm dương duy nhất). $f\left(1\right)=48$ là giá trị nhỏ nhất. Vậy $P_{\min}=48$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="n">
+        <v>654</v>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>p021_q21</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 7\log^2_{\frac{a}{b}}a + 28\log_b\left(\dfrac{a}{b}\right)$.
+A. $P_{\min}=55$.
+B. $P_{\min}=57$.
+C. $P_{\min}=56$.
+D. $P_{\min}=112$.</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>C. $P_{\min}=56$.</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{a/b}b&gt;0$. Ta có $\log_{a/b}a=1+t$ và $\log_b(a/b)=\dfrac1t$, nên $P=7(1+t)^2+\dfrac{28}{t}=f(t)$. Xét $f'(t)=14(1+t)-\dfrac{28}{t^2}$, $f'(t)=0$ tại $t=1$ (nghiệm dương duy nhất). $f\left(1\right)=56$ là giá trị nhỏ nhất. Vậy $P_{\min}=56$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="n">
+        <v>655</v>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>p021_q21</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = \log^2_{\frac{a}{b}}a + 24\log_b\left(\dfrac{a}{b}\right)$.
+A. $P_{\min}=42$.
+B. $P_{\min}=21$.
+C. $P_{\min}=22$.
+D. $P_{\min}=20$.</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>B. $P_{\min}=21$.</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{a/b}b&gt;0$. Ta có $\log_{a/b}a=1+t$ và $\log_b(a/b)=\dfrac1t$, nên $P=(1+t)^2+\dfrac{24}{t}=f(t)$. Xét $f'(t)=2(1+t)-\dfrac{24}{t^2}$, $f'(t)=0$ tại $t=2$ (nghiệm dương duy nhất). $f\left(2\right)=21$ là giá trị nhỏ nhất. Vậy $P_{\min}=21$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="n">
+        <v>656</v>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>p021_q21</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 2\log^2_{\frac{a}{b}}a + 48\log_b\left(\dfrac{a}{b}\right)$.
+A. $P_{\min}=84$.
+B. $P_{\min}=42$.
+C. $P_{\min}=43$.
+D. $P_{\min}=41$.</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>B. $P_{\min}=42$.</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{a/b}b&gt;0$. Ta có $\log_{a/b}a=1+t$ và $\log_b(a/b)=\dfrac1t$, nên $P=2(1+t)^2+\dfrac{48}{t}=f(t)$. Xét $f'(t)=4(1+t)-\dfrac{48}{t^2}$, $f'(t)=0$ tại $t=2$ (nghiệm dương duy nhất). $f\left(2\right)=42$ là giá trị nhỏ nhất. Vậy $P_{\min}=42$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="n">
+        <v>657</v>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>p021_q21</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 3\log^2_{\frac{a}{b}}a + 72\log_b\left(\dfrac{a}{b}\right)$.
+A. $P_{\min}=62$.
+B. $P_{\min}=126$.
+C. $P_{\min}=63$.
+D. $P_{\min}=64$.</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>C. $P_{\min}=63$.</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>Đặt $t=\log_{a/b}b&gt;0$. Ta có $\log_{a/b}a=1+t$ và $\log_b(a/b)=\dfrac1t$, nên $P=3(1+t)^2+\dfrac{72}{t}=f(t)$. Xét $f'(t)=6(1+t)-\dfrac{72}{t^2}$, $f'(t)=0$ tại $t=2$ (nghiệm dương duy nhất). $f\left(2\right)=63$ là giá trị nhỏ nhất. Vậy $P_{\min}=63$.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
+++ b/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H658"/>
+  <dimension ref="A1:H663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28120,15 +28120,15 @@
       <c r="F649" t="inlineStr">
         <is>
           <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = \log^2_{\frac{a}{b}}a + 4\log_b\left(\dfrac{a}{b}\right)$.
-A. $P_{\min}=7$.
-B. $P_{\min}=16$.
-C. $P_{\min}=8$.
-D. $P_{\min}=9$.</t>
+A. $P_{\min}=9$.
+B. $P_{\min}=8$.
+C. $P_{\min}=16$.
+D. $P_{\min}=7$.</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>C. $P_{\min}=8$.</t>
+          <t>B. $P_{\min}=8$.</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -28165,14 +28165,14 @@
         <is>
           <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 2\log^2_{\frac{a}{b}}a + 8\log_b\left(\dfrac{a}{b}\right)$.
 A. $P_{\min}=32$.
-B. $P_{\min}=16$.
-C. $P_{\min}=17$.
+B. $P_{\min}=17$.
+C. $P_{\min}=16$.
 D. $P_{\min}=15$.</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>B. $P_{\min}=16$.</t>
+          <t>C. $P_{\min}=16$.</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -28208,15 +28208,15 @@
       <c r="F651" t="inlineStr">
         <is>
           <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 3\log^2_{\frac{a}{b}}a + 12\log_b\left(\dfrac{a}{b}\right)$.
-A. $P_{\min}=23$.
-B. $P_{\min}=25$.
-C. $P_{\min}=24$.
-D. $P_{\min}=48$.</t>
+A. $P_{\min}=48$.
+B. $P_{\min}=24$.
+C. $P_{\min}=25$.
+D. $P_{\min}=23$.</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>C. $P_{\min}=24$.</t>
+          <t>B. $P_{\min}=24$.</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
@@ -28252,10 +28252,10 @@
       <c r="F652" t="inlineStr">
         <is>
           <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 4\log^2_{\frac{a}{b}}a + 3\log_b\left(\dfrac{a}{b}\right)$.
-A. $P_{\min}=30$.
-B. $P_{\min}=16$.
+A. $P_{\min}=16$.
+B. $P_{\min}=14$.
 C. $P_{\min}=15$.
-D. $P_{\min}=14$.</t>
+D. $P_{\min}=30$.</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -28296,15 +28296,15 @@
       <c r="F653" t="inlineStr">
         <is>
           <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 5\log^2_{\frac{a}{b}}a + 20\log_b\left(\dfrac{a}{b}\right)$.
-A. $P_{\min}=39$.
-B. $P_{\min}=40$.
-C. $P_{\min}=80$.
-D. $P_{\min}=41$.</t>
+A. $P_{\min}=40$.
+B. $P_{\min}=80$.
+C. $P_{\min}=41$.
+D. $P_{\min}=39$.</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>B. $P_{\min}=40$.</t>
+          <t>A. $P_{\min}=40$.</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -28340,15 +28340,15 @@
       <c r="F654" t="inlineStr">
         <is>
           <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 6\log^2_{\frac{a}{b}}a + 24\log_b\left(\dfrac{a}{b}\right)$.
-A. $P_{\min}=48$.
-B. $P_{\min}=49$.
-C. $P_{\min}=47$.
-D. $P_{\min}=96$.</t>
+A. $P_{\min}=96$.
+B. $P_{\min}=48$.
+C. $P_{\min}=49$.
+D. $P_{\min}=47$.</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>A. $P_{\min}=48$.</t>
+          <t>B. $P_{\min}=48$.</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -28385,14 +28385,14 @@
         <is>
           <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 7\log^2_{\frac{a}{b}}a + 28\log_b\left(\dfrac{a}{b}\right)$.
 A. $P_{\min}=55$.
-B. $P_{\min}=57$.
-C. $P_{\min}=56$.
+B. $P_{\min}=56$.
+C. $P_{\min}=57$.
 D. $P_{\min}=112$.</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>C. $P_{\min}=56$.</t>
+          <t>B. $P_{\min}=56$.</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -28428,9 +28428,9 @@
       <c r="F656" t="inlineStr">
         <is>
           <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = \log^2_{\frac{a}{b}}a + 24\log_b\left(\dfrac{a}{b}\right)$.
-A. $P_{\min}=42$.
+A. $P_{\min}=22$.
 B. $P_{\min}=21$.
-C. $P_{\min}=22$.
+C. $P_{\min}=42$.
 D. $P_{\min}=20$.</t>
         </is>
       </c>
@@ -28472,15 +28472,15 @@
       <c r="F657" t="inlineStr">
         <is>
           <t>Xét các số thực $a, b$ thỏa mãn $a&gt;b&gt;1$. Tìm giá trị nhỏ nhất $P_{\min}$ của biểu thức $P = 2\log^2_{\frac{a}{b}}a + 48\log_b\left(\dfrac{a}{b}\right)$.
-A. $P_{\min}=84$.
-B. $P_{\min}=42$.
-C. $P_{\min}=43$.
+A. $P_{\min}=42$.
+B. $P_{\min}=43$.
+C. $P_{\min}=84$.
 D. $P_{\min}=41$.</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>B. $P_{\min}=42$.</t>
+          <t>A. $P_{\min}=42$.</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -28533,6 +28533,226 @@
         </is>
       </c>
     </row>
+    <row r="659">
+      <c r="A659" t="n">
+        <v>658</v>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>D65</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>p148_q47</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Xét các số thực dương $x,y$ thỏa mãn $\log_{3}\dfrac{1-xy}{x+2y}=3xy+x+2y-4$. Tìm giá trị nhỏ nhất $P_{\min}$ của $P=x+y$.
+A. $P_{\min}=-1 + \dfrac{2 \sqrt{11}}{3}$.
+B. $P_{\min}=-2 + \dfrac{4 \sqrt{11}}{3}$.
+C. $P_{\min}=1 - \dfrac{2 \sqrt{11}}{3}$.
+D. $P_{\min}=\dfrac{2 \sqrt{11}}{3}$.</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>A. $P_{\min}=-1 + \dfrac{2 \sqrt{11}}{3}$.</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>Xét $f(t)=\log_{3}t+t$ đồng biến trên $(0;+\infty)$. Biến đổi giả thiết về dạng $f\left(3(1-xy)\right)=f(x+2y)$, suy ra $3(1-xy)=x+2y\Rightarrow y=\dfrac{3-x}{3x+2}$ (với $0&lt;x&lt;3$ để $y&gt;0$). Khảo sát $P=x+y$ theo $x$ trên miền này, đạt giá trị nhỏ nhất tại $x=- \dfrac{2}{3} + \dfrac{\sqrt{11}}{3}$, $P_{\min}=-1 + \dfrac{2 \sqrt{11}}{3}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="n">
+        <v>659</v>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>D65</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>p148_q47</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Xét các số thực dương $x,y$ thỏa mãn $\log_{2}\dfrac{1-xy}{x+y}=2xy+x+y-3$. Tìm giá trị nhỏ nhất $P_{\min}$ của $P=x+y$.
+A. $P_{\min}=\sqrt{5}$.
+B. $P_{\min}=1 - \sqrt{5}$.
+C. $P_{\min}=-1 + \sqrt{5}$.
+D. $P_{\min}=-2 + 2 \sqrt{5}$.</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>C. $P_{\min}=-1 + \sqrt{5}$.</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>Xét $f(t)=\log_{2}t+t$ đồng biến trên $(0;+\infty)$. Biến đổi giả thiết về dạng $f\left(2(1-xy)\right)=f(x+y)$, suy ra $2(1-xy)=x+y\Rightarrow y=\dfrac{2-x}{2x+1}$ (với $0&lt;x&lt;2$ để $y&gt;0$). Khảo sát $P=x+y$ theo $x$ trên miền này, đạt giá trị nhỏ nhất tại $x=- \dfrac{1}{2} + \dfrac{\sqrt{5}}{2}$, $P_{\min}=-1 + \sqrt{5}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="n">
+        <v>660</v>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>D65</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>p148_q47</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Xét các số thực dương $x,y$ thỏa mãn $\log_{3}\dfrac{2-xy}{x+3y}=3xy+x+3y-7$. Tìm giá trị nhỏ nhất $P_{\min}$ của $P=x+y$.
+A. $P_{\min}=- \dfrac{4}{3} + \dfrac{2 \sqrt{21}}{3}$.
+B. $P_{\min}=- \dfrac{8}{3} + \dfrac{4 \sqrt{21}}{3}$.
+C. $P_{\min}=\dfrac{4}{3} - \dfrac{2 \sqrt{21}}{3}$.
+D. $P_{\min}=- \dfrac{1}{3} + \dfrac{2 \sqrt{21}}{3}$.</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>A. $P_{\min}=- \dfrac{4}{3} + \dfrac{2 \sqrt{21}}{3}$.</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>Xét $f(t)=\log_{3}t+t$ đồng biến trên $(0;+\infty)$. Biến đổi giả thiết về dạng $f\left(3(2-xy)\right)=f(x+3y)$, suy ra $3(2-xy)=x+3y\Rightarrow y=\dfrac{6-x}{3x+3}$ (với $0&lt;x&lt;6$ để $y&gt;0$). Khảo sát $P=x+y$ theo $x$ trên miền này, đạt giá trị nhỏ nhất tại $x=-1 + \dfrac{\sqrt{21}}{3}$, $P_{\min}=- \dfrac{4}{3} + \dfrac{2 \sqrt{21}}{3}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="n">
+        <v>661</v>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>D65</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>p148_q47</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Xét các số thực dương $x,y$ thỏa mãn $\log_{2}\dfrac{2-xy}{x+2y}=2xy+x+2y-5$. Tìm giá trị nhỏ nhất $P_{\min}$ của $P=x+y$.
+A. $P_{\min}=-3 + 2 \sqrt{10}$.
+B. $P_{\min}=- \dfrac{1}{2} + \sqrt{10}$.
+C. $P_{\min}=- \dfrac{3}{2} + \sqrt{10}$.
+D. $P_{\min}=\dfrac{3}{2} - \sqrt{10}$.</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>C. $P_{\min}=- \dfrac{3}{2} + \sqrt{10}$.</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>Xét $f(t)=\log_{2}t+t$ đồng biến trên $(0;+\infty)$. Biến đổi giả thiết về dạng $f\left(2(2-xy)\right)=f(x+2y)$, suy ra $2(2-xy)=x+2y\Rightarrow y=\dfrac{4-x}{2x+2}$ (với $0&lt;x&lt;4$ để $y&gt;0$). Khảo sát $P=x+y$ theo $x$ trên miền này, đạt giá trị nhỏ nhất tại $x=-1 + \dfrac{\sqrt{10}}{2}$, $P_{\min}=- \dfrac{3}{2} + \sqrt{10}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="n">
+        <v>662</v>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>D65</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>p148_q47</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Xét các số thực dương $x,y$ thỏa mãn $\log_{3}\dfrac{1-xy}{2x+y}=3xy+2x+y-4$. Tìm giá trị nhỏ nhất $P_{\min}$ của $P=x+y$.
+A. $P_{\min}=1 - \dfrac{2 \sqrt{11}}{3}$.
+B. $P_{\min}=-2 + \dfrac{4 \sqrt{11}}{3}$.
+C. $P_{\min}=\dfrac{2 \sqrt{11}}{3}$.
+D. $P_{\min}=-1 + \dfrac{2 \sqrt{11}}{3}$.</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>D. $P_{\min}=-1 + \dfrac{2 \sqrt{11}}{3}$.</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Xét $f(t)=\log_{3}t+t$ đồng biến trên $(0;+\infty)$. Biến đổi giả thiết về dạng $f\left(3(1-xy)\right)=f(2x+y)$, suy ra $3(1-xy)=2x+y\Rightarrow y=\dfrac{3-2x}{3x+1}$ (với $0&lt;x&lt;\dfrac{3}{2}$ để $y&gt;0$). Khảo sát $P=x+y$ theo $x$ trên miền này, đạt giá trị nhỏ nhất tại $x=- \dfrac{1}{3} + \dfrac{\sqrt{11}}{3}$, $P_{\min}=-1 + \dfrac{2 \sqrt{11}}{3}$.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
+++ b/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H663"/>
+  <dimension ref="A1:H720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28753,6 +28753,2522 @@
         </is>
       </c>
     </row>
+    <row r="664">
+      <c r="A664" t="n">
+        <v>663</v>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>p007_q19</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Đặt $a=\log_{2}3,\ b=\log_{5}3$. Hãy biểu diễn $\log_{2\cdot 3}(3^{2}\cdot 5)$ theo $a,b$.
+A. $\log_{2\cdot 3}(3^{2}\cdot 5)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.
+B. $\log_{2\cdot 3}(3^{2}\cdot 5)=- \dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.
+C. $\log_{2\cdot 3}(3^{2}\cdot 5)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)} + 1$.
+D. $\log_{2\cdot 3}(3^{2}\cdot 5)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)} - 1$.</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>A. $\log_{2\cdot 3}(3^{2}\cdot 5)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>Đổi cơ số theo $\ln C$: $\ln p=\dfrac{\ln C}a$ và $\ln r=\dfrac{\ln C}b$. Do đó giá trị cần tìm bằng $\dfrac{2\ln C+\ln r}{\ln p+\ln C}=\dfrac{a(2b+1)}{b(1+a)}=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="n">
+        <v>664</v>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>p007_q19</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Đặt $a=\log_{2}5,\ b=\log_{3}5$. Hãy biểu diễn $\log_{2\cdot 5}(5^{2}\cdot 3)$ theo $a,b$.
+A. $\log_{2\cdot 5}(5^{2}\cdot 3)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)} - 1$.
+B. $\log_{2\cdot 5}(5^{2}\cdot 3)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)} + 1$.
+C. $\log_{2\cdot 5}(5^{2}\cdot 3)=- \dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.
+D. $\log_{2\cdot 5}(5^{2}\cdot 3)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>D. $\log_{2\cdot 5}(5^{2}\cdot 3)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>Đổi cơ số theo $\ln C$: $\ln p=\dfrac{\ln C}a$ và $\ln r=\dfrac{\ln C}b$. Do đó giá trị cần tìm bằng $\dfrac{2\ln C+\ln r}{\ln p+\ln C}=\dfrac{a(2b+1)}{b(1+a)}=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="n">
+        <v>665</v>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>p007_q19</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Đặt $a=\log_{3}2,\ b=\log_{5}2$. Hãy biểu diễn $\log_{3\cdot 2}(2^{2}\cdot 5)$ theo $a,b$.
+A. $\log_{3\cdot 2}(2^{2}\cdot 5)=- \dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.
+B. $\log_{3\cdot 2}(2^{2}\cdot 5)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.
+C. $\log_{3\cdot 2}(2^{2}\cdot 5)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)} - 1$.
+D. $\log_{3\cdot 2}(2^{2}\cdot 5)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)} + 1$.</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>B. $\log_{3\cdot 2}(2^{2}\cdot 5)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>Đổi cơ số theo $\ln C$: $\ln p=\dfrac{\ln C}a$ và $\ln r=\dfrac{\ln C}b$. Do đó giá trị cần tìm bằng $\dfrac{2\ln C+\ln r}{\ln p+\ln C}=\dfrac{a(2b+1)}{b(1+a)}=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="n">
+        <v>666</v>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>p007_q19</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Đặt $a=\log_{3}5,\ b=\log_{2}5$. Hãy biểu diễn $\log_{3\cdot 5}(5^{2}\cdot 2)$ theo $a,b$.
+A. $\log_{3\cdot 5}(5^{2}\cdot 2)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.
+B. $\log_{3\cdot 5}(5^{2}\cdot 2)=- \dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.
+C. $\log_{3\cdot 5}(5^{2}\cdot 2)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)} - 1$.
+D. $\log_{3\cdot 5}(5^{2}\cdot 2)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)} + 1$.</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>A. $\log_{3\cdot 5}(5^{2}\cdot 2)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>Đổi cơ số theo $\ln C$: $\ln p=\dfrac{\ln C}a$ và $\ln r=\dfrac{\ln C}b$. Do đó giá trị cần tìm bằng $\dfrac{2\ln C+\ln r}{\ln p+\ln C}=\dfrac{a(2b+1)}{b(1+a)}=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="n">
+        <v>667</v>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>p007_q19</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Đặt $a=\log_{2}3,\ b=\log_{7}3$. Hãy biểu diễn $\log_{2\cdot 3}(3^{3}\cdot 7)$ theo $a,b$.
+A. $\log_{2\cdot 3}(3^{3}\cdot 7)=\dfrac{a \left(3 b + 1\right)}{b \left(a + 1\right)} - 1$.
+B. $\log_{2\cdot 3}(3^{3}\cdot 7)=\dfrac{a \left(3 b + 1\right)}{b \left(a + 1\right)} + 1$.
+C. $\log_{2\cdot 3}(3^{3}\cdot 7)=\dfrac{a \left(3 b + 1\right)}{b \left(a + 1\right)}$.
+D. $\log_{2\cdot 3}(3^{3}\cdot 7)=- \dfrac{a \left(3 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>C. $\log_{2\cdot 3}(3^{3}\cdot 7)=\dfrac{a \left(3 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>Đổi cơ số theo $\ln C$: $\ln p=\dfrac{\ln C}a$ và $\ln r=\dfrac{\ln C}b$. Do đó giá trị cần tìm bằng $\dfrac{3\ln C+\ln r}{\ln p+\ln C}=\dfrac{a(3b+1)}{b(1+a)}=\dfrac{a \left(3 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="n">
+        <v>668</v>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>p007_q19</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Đặt $a=\log_{5}3,\ b=\log_{2}3$. Hãy biểu diễn $\log_{5\cdot 3}(3^{2}\cdot 2)$ theo $a,b$.
+A. $\log_{5\cdot 3}(3^{2}\cdot 2)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.
+B. $\log_{5\cdot 3}(3^{2}\cdot 2)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)} - 1$.
+C. $\log_{5\cdot 3}(3^{2}\cdot 2)=- \dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.
+D. $\log_{5\cdot 3}(3^{2}\cdot 2)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)} + 1$.</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>A. $\log_{5\cdot 3}(3^{2}\cdot 2)=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>Đổi cơ số theo $\ln C$: $\ln p=\dfrac{\ln C}a$ và $\ln r=\dfrac{\ln C}b$. Do đó giá trị cần tìm bằng $\dfrac{2\ln C+\ln r}{\ln p+\ln C}=\dfrac{a(2b+1)}{b(1+a)}=\dfrac{a \left(2 b + 1\right)}{b \left(a + 1\right)}$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="n">
+        <v>669</v>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Phương trình $3x^2-6x+\ln((x+1)^{3})-1=0$ có bao nhiêu nghiệm phân biệt?
+A. $2$.
+B. $5$.
+C. $4$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=3x^2-6x+3\ln(x+1)-1$. Ta có $f'(x)=\dfrac{6x^2-3}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=- \frac{\sqrt{2}}{2}$, f đạt cực đại xấp xỉ 1.059&gt;0, còn tại $x=\frac{\sqrt{2}}{2}$, f đạt cực tiểu xấp xỉ -2.138&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="n">
+        <v>670</v>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Phương trình $3x^2-6x+\ln((x+1)^{3})+0=0$ có bao nhiêu nghiệm phân biệt?
+A. $4$.
+B. $5$.
+C. $2$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=3x^2-6x+3\ln(x+1)+0$. Ta có $f'(x)=\dfrac{6x^2-3}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=- \frac{\sqrt{2}}{2}$, f đạt cực đại xấp xỉ 2.059&gt;0, còn tại $x=\frac{\sqrt{2}}{2}$, f đạt cực tiểu xấp xỉ -1.138&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="n">
+        <v>671</v>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Phương trình $3x^2-5x+\ln((x+1)^{3})-1=0$ có bao nhiêu nghiệm phân biệt?
+A. $5$.
+B. $4$.
+C. $2$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=3x^2-5x+3\ln(x+1)-1$. Ta có $f'(x)=\dfrac{6x^2+1x-2}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=- \frac{2}{3}$, f đạt cực đại xấp xỉ 0.371&gt;0, còn tại $x=\frac{1}{2}$, f đạt cực tiểu xấp xỉ -1.534&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="n">
+        <v>672</v>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Phương trình $3x^2-5x+\ln((x+1)^{3})+0=0$ có bao nhiêu nghiệm phân biệt?
+A. $5$.
+B. $2$.
+C. $4$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=3x^2-5x+3\ln(x+1)+0$. Ta có $f'(x)=\dfrac{6x^2+1x-2}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=- \frac{2}{3}$, f đạt cực đại xấp xỉ 1.371&gt;0, còn tại $x=\frac{1}{2}$, f đạt cực tiểu xấp xỉ -0.534&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="n">
+        <v>673</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Phương trình $4x^2-8x+\ln((x+1)^{3})-2=0$ có bao nhiêu nghiệm phân biệt?
+A. $4$.
+B. $5$.
+C. $3$.
+D. $2$.</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>C. $3$.</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=4x^2-8x+3\ln(x+1)-2$. Ta có $f'(x)=\dfrac{8x^2-5}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=- \frac{\sqrt{10}}{4}$, f đạt cực đại xấp xỉ 2.134&gt;0, còn tại $x=\frac{\sqrt{10}}{4}$, f đạt cực tiểu xấp xỉ -4.077&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="n">
+        <v>674</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Phương trình $4x^2-8x+\ln((x+1)^{3})-1=0$ có bao nhiêu nghiệm phân biệt?
+A. $2$.
+B. $4$.
+C. $3$.
+D. $5$.</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>C. $3$.</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=4x^2-8x+3\ln(x+1)-1$. Ta có $f'(x)=\dfrac{8x^2-5}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=- \frac{\sqrt{10}}{4}$, f đạt cực đại xấp xỉ 3.134&gt;0, còn tại $x=\frac{\sqrt{10}}{4}$, f đạt cực tiểu xấp xỉ -3.077&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="n">
+        <v>675</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Phương trình $4x^2-8x+\ln((x+1)^{3})+0=0$ có bao nhiêu nghiệm phân biệt?
+A. $2$.
+B. $4$.
+C. $5$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=4x^2-8x+3\ln(x+1)+0$. Ta có $f'(x)=\dfrac{8x^2-5}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=- \frac{\sqrt{10}}{4}$, f đạt cực đại xấp xỉ 4.134&gt;0, còn tại $x=\frac{\sqrt{10}}{4}$, f đạt cực tiểu xấp xỉ -2.077&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="n">
+        <v>676</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>Phương trình $4x^2-8x+\ln((x+1)^{3})+1=0$ có bao nhiêu nghiệm phân biệt?
+A. $5$.
+B. $2$.
+C. $4$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=4x^2-8x+3\ln(x+1)+1$. Ta có $f'(x)=\dfrac{8x^2-5}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=- \frac{\sqrt{10}}{4}$, f đạt cực đại xấp xỉ 5.134&gt;0, còn tại $x=\frac{\sqrt{10}}{4}$, f đạt cực tiểu xấp xỉ -1.077&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="n">
+        <v>677</v>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Phương trình $4x^2-8x+\ln((x+1)^{3})+2=0$ có bao nhiêu nghiệm phân biệt?
+A. $4$.
+B. $5$.
+C. $2$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=4x^2-8x+3\ln(x+1)+2$. Ta có $f'(x)=\dfrac{8x^2-5}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=- \frac{\sqrt{10}}{4}$, f đạt cực đại xấp xỉ 6.134&gt;0, còn tại $x=\frac{\sqrt{10}}{4}$, f đạt cực tiểu xấp xỉ -0.077&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>678</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Phương trình $3x^2-7x+\ln((x+1)^{4})-1=0$ có bao nhiêu nghiệm phân biệt?
+A. $5$.
+B. $2$.
+C. $4$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=3x^2-7x+4\ln(x+1)-1$. Ta có $f'(x)=\dfrac{6x^2-1x-3}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=\frac{1}{12} - \frac{\sqrt{73}}{12}$, f đạt cực đại xấp xỉ 0.624&gt;0, còn tại $x=\frac{1}{12} + \frac{\sqrt{73}}{12}$, f đạt cực tiểu xấp xỉ -2.329&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="n">
+        <v>679</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Phương trình $3x^2-7x+\ln((x+1)^{4})+0=0$ có bao nhiêu nghiệm phân biệt?
+A. $4$.
+B. $3$.
+C. $5$.
+D. $2$.</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>B. $3$.</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=3x^2-7x+4\ln(x+1)+0$. Ta có $f'(x)=\dfrac{6x^2-1x-3}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=\frac{1}{12} - \frac{\sqrt{73}}{12}$, f đạt cực đại xấp xỉ 1.624&gt;0, còn tại $x=\frac{1}{12} + \frac{\sqrt{73}}{12}$, f đạt cực tiểu xấp xỉ -1.329&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>680</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Phương trình $3x^2-7x+\ln((x+1)^{4})+1=0$ có bao nhiêu nghiệm phân biệt?
+A. $3$.
+B. $4$.
+C. $5$.
+D. $2$.</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>A. $3$.</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=3x^2-7x+4\ln(x+1)+1$. Ta có $f'(x)=\dfrac{6x^2-1x-3}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=\frac{1}{12} - \frac{\sqrt{73}}{12}$, f đạt cực đại xấp xỉ 2.624&gt;0, còn tại $x=\frac{1}{12} + \frac{\sqrt{73}}{12}$, f đạt cực tiểu xấp xỉ -0.329&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="n">
+        <v>681</v>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Phương trình $2x^2-6x+\ln((x+1)^{3})-1=0$ có bao nhiêu nghiệm phân biệt?
+A. $5$.
+B. $3$.
+C. $2$.
+D. $4$.</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>B. $3$.</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=2x^2-6x+3\ln(x+1)-1$. Ta có $f'(x)=\dfrac{4x^2-2x-3}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=\frac{1}{4} - \frac{\sqrt{13}}{4}$, f đạt cực đại xấp xỉ 0.596&gt;0, còn tại $x=\frac{1}{4} + \frac{\sqrt{13}}{4}$, f đạt cực tiểu xấp xỉ -2.959&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="n">
+        <v>682</v>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Phương trình $2x^2-6x+\ln((x+1)^{3})+0=0$ có bao nhiêu nghiệm phân biệt?
+A. $5$.
+B. $2$.
+C. $4$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=2x^2-6x+3\ln(x+1)+0$. Ta có $f'(x)=\dfrac{4x^2-2x-3}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=\frac{1}{4} - \frac{\sqrt{13}}{4}$, f đạt cực đại xấp xỉ 1.596&gt;0, còn tại $x=\frac{1}{4} + \frac{\sqrt{13}}{4}$, f đạt cực tiểu xấp xỉ -1.959&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="n">
+        <v>683</v>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>p039_q35</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Phương trình $2x^2-6x+\ln((x+1)^{3})+1=0$ có bao nhiêu nghiệm phân biệt?
+A. $4$.
+B. $3$.
+C. $2$.
+D. $5$.</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>B. $3$.</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>Điều kiện $x&gt;-1$. Xét $f(x)=2x^2-6x+3\ln(x+1)+1$. Ta có $f'(x)=\dfrac{4x^2-2x-3}{x+1}$. Dấu của đạo hàm lần lượt là $+,-,+$; tại $x=\frac{1}{4} - \frac{\sqrt{13}}{4}$, f đạt cực đại xấp xỉ 2.596&gt;0, còn tại $x=\frac{1}{4} + \frac{\sqrt{13}}{4}$, f đạt cực tiểu xấp xỉ -0.959&lt;0. Kết hợp $\lim_{x\to-1^+}f(x)=-\infty$ và $\lim_{x\to+\infty}f(x)=+\infty$, phương trình có đúng 3 nghiệm phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>684</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>D47</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>p106_q50</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ để tồn tại số thực $y$ thỏa mãn $\log_{32}(x+y)=\log_{64}(x^2+y^2)$?
+A. $4$.
+B. $2$.
+C. $1$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>B. $2$.</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>Đặt $t=x+y&gt;0$. Khi đó phương trình tương đương $x^2+(t-x)^2=t^{6/5}$. Thay $t=u^{5}$ ($u&gt;0$), ta được $u^{10}-u^{6}-2xu^{5}+2x^2=0$. Đếm các giá trị nguyên $x$ có nghiệm dương, thu được $x\in\{0,1\}$, có 2 giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="n">
+        <v>685</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>D47</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>p106_q50</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ để tồn tại số thực $y$ thỏa mãn $\log_{16}(x+y)=\log_{32}(x^2+y^2)$?
+A. $4$.
+B. $1$.
+C. $2$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>C. $2$.</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>Đặt $t=x+y&gt;0$. Khi đó phương trình tương đương $x^2+(t-x)^2=t^{5/4}$. Thay $t=u^{4}$ ($u&gt;0$), ta được $u^{8}-u^{5}-2xu^{4}+2x^2=0$. Đếm các giá trị nguyên $x$ có nghiệm dương, thu được $x\in\{0,1\}$, có 2 giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="n">
+        <v>686</v>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>D47</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>p106_q50</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ để tồn tại số thực $y$ thỏa mãn $\log_{32}(x+y)=\log_{128}(x^2+y^2)$?
+A. $3$.
+B. $4$.
+C. $1$.
+D. $2$.</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>D. $2$.</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>Đặt $t=x+y&gt;0$. Khi đó phương trình tương đương $x^2+(t-x)^2=t^{7/5}$. Thay $t=u^{5}$ ($u&gt;0$), ta được $u^{10}-u^{7}-2xu^{5}+2x^2=0$. Đếm các giá trị nguyên $x$ có nghiệm dương, thu được $x\in\{0,1\}$, có 2 giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="n">
+        <v>687</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>D47</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>p106_q50</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ để tồn tại số thực $y$ thỏa mãn $\log_{32}(x+y)=\log_{256}(x^2+y^2)$?
+A. $6$.
+B. $4$.
+C. $3$.
+D. $5$.</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>B. $4$.</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>Đặt $t=x+y&gt;0$. Khi đó phương trình tương đương $x^2+(t-x)^2=t^{8/5}$. Thay $t=u^{5}$ ($u&gt;0$), ta được $u^{10}-u^{8}-2xu^{5}+2x^2=0$. Đếm các giá trị nguyên $x$ có nghiệm dương, thu được $x\in\{0,1,2,3\}$, có 4 giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>688</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>D47</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>p106_q50</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ để tồn tại số thực $y$ thỏa mãn $\log_{16}(x+y)=\log_{128}(x^2+y^2)$?
+A. $10$.
+B. $11$.
+C. $8$.
+D. $9$.</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>D. $9$.</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>Đặt $t=x+y&gt;0$. Khi đó phương trình tương đương $x^2+(t-x)^2=t^{7/4}$. Thay $t=u^{4}$ ($u&gt;0$), ta được $u^{8}-u^{7}-2xu^{4}+2x^2=0$. Đếm các giá trị nguyên $x$ có nghiệm dương, thu được $x\in\{0,1,2,3,4,5,6,7,8\}$, có 9 giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>689</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>D47</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>p106_q50</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ để tồn tại số thực $y$ thỏa mãn $\log_{8}(x+y)=\log_{32}(x^2+y^2)$?
+A. $4$.
+B. $6$.
+C. $5$.
+D. $7$.</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>C. $5$.</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>Đặt $t=x+y&gt;0$. Khi đó phương trình tương đương $x^2+(t-x)^2=t^{5/3}$. Thay $t=u^{3}$ ($u&gt;0$), ta được $u^{6}-u^{5}-2xu^{3}+2x^2=0$. Đếm các giá trị nguyên $x$ có nghiệm dương, thu được $x\in\{0,1,2,3,4\}$, có 5 giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="n">
+        <v>690</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>D47</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>p106_q50</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ để tồn tại số thực $y$ thỏa mãn $\log_{4}(x+y)=\log_{8}(x^2+y^2)$?
+A. $5$.
+B. $4$.
+C. $2$.
+D. $3$.</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>D. $3$.</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>Đặt $t=x+y&gt;0$. Khi đó phương trình tương đương $x^2+(t-x)^2=t^{3/2}$. Thay $t=u^{2}$ ($u&gt;0$), ta được $u^{4}-u^{3}-2xu^{2}+2x^2=0$. Đếm các giá trị nguyên $x$ có nghiệm dương, thu được $x\in\{0,1,2\}$, có 3 giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>691</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>D47</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>p106_q50</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $x$ để tồn tại số thực $y$ thỏa mãn $\log_{32}(x+y)=\log_{512}(x^2+y^2)$?
+A. $18$.
+B. $19$.
+C. $16$.
+D. $17$.</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>D. $17$.</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>Đặt $t=x+y&gt;0$. Khi đó phương trình tương đương $x^2+(t-x)^2=t^{9/5}$. Thay $t=u^{5}$ ($u&gt;0$), ta được $u^{10}-u^{9}-2xu^{5}+2x^2=0$. Đếm các giá trị nguyên $x$ có nghiệm dương, thu được $x\in\{0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16\}$, có 17 giá trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>692</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>D52</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>p119_q48</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $a$ sao cho có ít nhất 4 số nguyên $b\in(-8;8)$ thỏa mãn $3^{a^2+b}\le 2^{b-a}+20$?
+A. $4$.
+B. $6$.
+C. $5$.
+D. $7$.</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>C. $5$.</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>Với mỗi số nguyên $a$, đếm trực tiếp các số nguyên $b\in\{-7,\ldots,7\}$ thỏa bất đẳng thức. Điều kiện có ít nhất 4 giá trị $b$ đúng với $a\in\{-2,-1,0,1,2\}$. Với $a\ge4$, vế trái tăng còn vế phải giảm theo $a$; với $a\le-4$, phần mũ bậc hai làm vế trái tăng nhanh hơn vế phải. Kiểm tra biên cho thấy ngoài khoảng này không có giá trị phù hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>693</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>D52</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>p119_q48</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $a$ sao cho có ít nhất 4 số nguyên $b\in(-8;8)$ thỏa mãn $5^{a^2+b}\le 3^{b-a}+100$?
+A. $6$.
+B. $7$.
+C. $5$.
+D. $4$.</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>C. $5$.</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>Với mỗi số nguyên $a$, đếm trực tiếp các số nguyên $b\in\{-7,\ldots,7\}$ thỏa bất đẳng thức. Điều kiện có ít nhất 4 giá trị $b$ đúng với $a\in\{-2,-1,0,1,2\}$. Với $a\ge4$, vế trái tăng còn vế phải giảm theo $a$; với $a\le-4$, phần mũ bậc hai làm vế trái tăng nhanh hơn vế phải. Kiểm tra biên cho thấy ngoài khoảng này không có giá trị phù hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="n">
+        <v>694</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>D52</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>p119_q48</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $a$ sao cho có ít nhất 4 số nguyên $b\in(-7;7)$ thỏa mãn $3^{a^2+b}\le 2^{b-a}+50$?
+A. $7$.
+B. $6$.
+C. $4$.
+D. $5$.</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>D. $5$.</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>Với mỗi số nguyên $a$, đếm trực tiếp các số nguyên $b\in\{-6,\ldots,6\}$ thỏa bất đẳng thức. Điều kiện có ít nhất 4 giá trị $b$ đúng với $a\in\{-2,-1,0,1,2\}$. Với $a\ge4$, vế trái tăng còn vế phải giảm theo $a$; với $a\le-4$, phần mũ bậc hai làm vế trái tăng nhanh hơn vế phải. Kiểm tra biên cho thấy ngoài khoảng này không có giá trị phù hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="n">
+        <v>695</v>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>D52</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>p119_q48</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $a$ sao cho có ít nhất 4 số nguyên $b\in(-8;8)$ thỏa mãn $4^{a^2+b}\le 3^{b-a}+30$?
+A. $5$.
+B. $6$.
+C. $7$.
+D. $4$.</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>A. $5$.</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>Với mỗi số nguyên $a$, đếm trực tiếp các số nguyên $b\in\{-7,\ldots,7\}$ thỏa bất đẳng thức. Điều kiện có ít nhất 4 giá trị $b$ đúng với $a\in\{-2,-1,0,1,2\}$. Với $a\ge4$, vế trái tăng còn vế phải giảm theo $a$; với $a\le-4$, phần mũ bậc hai làm vế trái tăng nhanh hơn vế phải. Kiểm tra biên cho thấy ngoài khoảng này không có giá trị phù hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="n">
+        <v>696</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>D52</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>p119_q48</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $a$ sao cho có ít nhất 4 số nguyên $b\in(-9;9)$ thỏa mãn $3^{a^2+b}\le 5^{b-a}+75$?
+A. $4$.
+B. $7$.
+C. $5$.
+D. $6$.</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>C. $5$.</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>Với mỗi số nguyên $a$, đếm trực tiếp các số nguyên $b\in\{-8,\ldots,8\}$ thỏa bất đẳng thức. Điều kiện có ít nhất 4 giá trị $b$ đúng với $a\in\{-2,-1,0,1,2\}$. Với $a\ge4$, vế trái tăng còn vế phải giảm theo $a$; với $a\le-4$, phần mũ bậc hai làm vế trái tăng nhanh hơn vế phải. Kiểm tra biên cho thấy ngoài khoảng này không có giá trị phù hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>697</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>D52</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>p119_q48</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $a$ sao cho có ít nhất 4 số nguyên $b\in(-7;7)$ thỏa mãn $5^{a^2+b}\le 2^{b-a}+50$?
+A. $7$.
+B. $6$.
+C. $4$.
+D. $5$.</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>D. $5$.</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>Với mỗi số nguyên $a$, đếm trực tiếp các số nguyên $b\in\{-6,\ldots,6\}$ thỏa bất đẳng thức. Điều kiện có ít nhất 4 giá trị $b$ đúng với $a\in\{-2,-1,0,1,2\}$. Với $a\ge3$, vế trái tăng còn vế phải giảm theo $a$; với $a\le-3$, phần mũ bậc hai làm vế trái tăng nhanh hơn vế phải. Kiểm tra biên cho thấy ngoài khoảng này không có giá trị phù hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="n">
+        <v>698</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>D52</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>p119_q48</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $a$ sao cho có ít nhất 3 số nguyên $b\in(-6;6)$ thỏa mãn $2^{a^2+b}\le 3^{b-a}+100$?
+A. $6$.
+B. $8$.
+C. $9$.
+D. $7$.</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>D. $7$.</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>Với mỗi số nguyên $a$, đếm trực tiếp các số nguyên $b\in\{-5,\ldots,5\}$ thỏa bất đẳng thức. Điều kiện có ít nhất 3 giá trị $b$ đúng với $a\in\{-3,-2,-1,0,1,2,3\}$. Với $a\ge4$, vế trái tăng còn vế phải giảm theo $a$; với $a\le-4$, phần mũ bậc hai làm vế trái tăng nhanh hơn vế phải. Kiểm tra biên cho thấy ngoài khoảng này không có giá trị phù hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="n">
+        <v>699</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>D52</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>p119_q48</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $a$ sao cho có ít nhất 3 số nguyên $b\in(-8;8)$ thỏa mãn $2^{a^2+b}\le 5^{b-a}+100$?
+A. $8$.
+B. $9$.
+C. $6$.
+D. $7$.</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>D. $7$.</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>Với mỗi số nguyên $a$, đếm trực tiếp các số nguyên $b\in\{-7,\ldots,7\}$ thỏa bất đẳng thức. Điều kiện có ít nhất 3 giá trị $b$ đúng với $a\in\{-3,-2,-1,0,1,2,3\}$. Với $a\ge5$, vế trái tăng còn vế phải giảm theo $a$; với $a\le-5$, phần mũ bậc hai làm vế trái tăng nhanh hơn vế phải. Kiểm tra biên cho thấy ngoài khoảng này không có giá trị phù hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="n">
+        <v>700</v>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>D57</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>p133_q47</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $x&gt;0$ và
+$\log_2(x^2+y^2+x)+\log_4(x^2+y^2)\le\log_2 x+\log_4(x^2+y^2+96x)$?
+A. $12$.
+B. $13$.
+C. $14$.
+D. $11$.</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>A. $12$.</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>Đặt $Q=x^2+y^2$ và $t=Q/x&gt;0$. Bất đẳng thức tương đương $\log_2(1+t)\le\log_4(1+96/t)$. Vế trái tăng, vế phải giảm; hai vế bằng nhau tại $t=4$ vì $1+96/4=(4+1)^2$. Do đó $t\le4$, hay $x^2+y^2\le4x$. Với mỗi $x=1,\ldots,4$, số giá trị $y$ là $2\lfloor\sqrt{x(4-x)}\rfloor+1$; tổng bằng 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="n">
+        <v>701</v>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>D57</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>p133_q47</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $x&gt;0$ và
+$\log_2(x^2+y^2+x)+\log_4(x^2+y^2)\le\log_2 x+\log_4(x^2+y^2+175x)$?
+A. $22$.
+B. $21$.
+C. $20$.
+D. $23$.</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>B. $21$.</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>Đặt $Q=x^2+y^2$ và $t=Q/x&gt;0$. Bất đẳng thức tương đương $\log_2(1+t)\le\log_4(1+175/t)$. Vế trái tăng, vế phải giảm; hai vế bằng nhau tại $t=5$ vì $1+175/5=(5+1)^2$. Do đó $t\le5$, hay $x^2+y^2\le5x$. Với mỗi $x=1,\ldots,5$, số giá trị $y$ là $2\lfloor\sqrt{x(5-x)}\rfloor+1$; tổng bằng 21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="n">
+        <v>702</v>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>D57</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>p133_q47</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $x&gt;0$ và
+$\log_2(x^2+y^2+x)+\log_4(x^2+y^2)\le\log_2 x+\log_4(x^2+y^2+288x)$?
+A. $28$.
+B. $30$.
+C. $29$.
+D. $27$.</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>A. $28$.</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>Đặt $Q=x^2+y^2$ và $t=Q/x&gt;0$. Bất đẳng thức tương đương $\log_2(1+t)\le\log_4(1+288/t)$. Vế trái tăng, vế phải giảm; hai vế bằng nhau tại $t=6$ vì $1+288/6=(6+1)^2$. Do đó $t\le6$, hay $x^2+y^2\le6x$. Với mỗi $x=1,\ldots,6$, số giá trị $y$ là $2\lfloor\sqrt{x(6-x)}\rfloor+1$; tổng bằng 28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="n">
+        <v>703</v>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>D57</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>p133_q47</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $x&gt;0$ và
+$\log_2(x^2+y^2+x)+\log_4(x^2+y^2)\le\log_2 x+\log_4(x^2+y^2+441x)$?
+A. $38$.
+B. $40$.
+C. $41$.
+D. $39$.</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>D. $39$.</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>Đặt $Q=x^2+y^2$ và $t=Q/x&gt;0$. Bất đẳng thức tương đương $\log_2(1+t)\le\log_4(1+441/t)$. Vế trái tăng, vế phải giảm; hai vế bằng nhau tại $t=7$ vì $1+441/7=(7+1)^2$. Do đó $t\le7$, hay $x^2+y^2\le7x$. Với mỗi $x=1,\ldots,7$, số giá trị $y$ là $2\lfloor\sqrt{x(7-x)}\rfloor+1$; tổng bằng 39.</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="n">
+        <v>704</v>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>D57</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>p133_q47</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $x&gt;0$ và
+$\log_2(x^2+y^2+x)+\log_4(x^2+y^2)\le\log_2 x+\log_4(x^2+y^2+640x)$?
+A. $49$.
+B. $48$.
+C. $50$.
+D. $47$.</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>B. $48$.</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>Đặt $Q=x^2+y^2$ và $t=Q/x&gt;0$. Bất đẳng thức tương đương $\log_2(1+t)\le\log_4(1+640/t)$. Vế trái tăng, vế phải giảm; hai vế bằng nhau tại $t=8$ vì $1+640/8=(8+1)^2$. Do đó $t\le8$, hay $x^2+y^2\le8x$. Với mỗi $x=1,\ldots,8$, số giá trị $y$ là $2\lfloor\sqrt{x(8-x)}\rfloor+1$; tổng bằng 48.</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="n">
+        <v>705</v>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>D57</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>p133_q47</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $x&gt;0$ và
+$\log_2(x^2+y^2+x)+\log_4(x^2+y^2)\le\log_2 x+\log_4(x^2+y^2+891x)$?
+A. $62$.
+B. $63$.
+C. $61$.
+D. $60$.</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>C. $61$.</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>Đặt $Q=x^2+y^2$ và $t=Q/x&gt;0$. Bất đẳng thức tương đương $\log_2(1+t)\le\log_4(1+891/t)$. Vế trái tăng, vế phải giảm; hai vế bằng nhau tại $t=9$ vì $1+891/9=(9+1)^2$. Do đó $t\le9$, hay $x^2+y^2\le9x$. Với mỗi $x=1,\ldots,9$, số giá trị $y$ là $2\lfloor\sqrt{x(9-x)}\rfloor+1$; tổng bằng 61.</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="n">
+        <v>706</v>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>D57</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>p133_q47</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $x&gt;0$ và
+$\log_2(x^2+y^2+x)+\log_4(x^2+y^2)\le\log_2 x+\log_4(x^2+y^2+1200x)$?
+A. $81$.
+B. $82$.
+C. $80$.
+D. $79$.</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>C. $80$.</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>Đặt $Q=x^2+y^2$ và $t=Q/x&gt;0$. Bất đẳng thức tương đương $\log_2(1+t)\le\log_4(1+1200/t)$. Vế trái tăng, vế phải giảm; hai vế bằng nhau tại $t=10$ vì $1+1200/10=(10+1)^2$. Do đó $t\le10$, hay $x^2+y^2\le10x$. Với mỗi $x=1,\ldots,10$, số giá trị $y$ là $2\lfloor\sqrt{x(10-x)}\rfloor+1$; tổng bằng 80.</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="n">
+        <v>707</v>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>D57</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>p133_q47</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu cặp số nguyên $(x;y)$ thỏa mãn $x&gt;0$ và
+$\log_2(x^2+y^2+x)+\log_4(x^2+y^2)\le\log_2 x+\log_4(x^2+y^2+1573x)$?
+A. $96$.
+B. $94$.
+C. $95$.
+D. $97$.</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>C. $95$.</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>Đặt $Q=x^2+y^2$ và $t=Q/x&gt;0$. Bất đẳng thức tương đương $\log_2(1+t)\le\log_4(1+1573/t)$. Vế trái tăng, vế phải giảm; hai vế bằng nhau tại $t=11$ vì $1+1573/11=(11+1)^2$. Do đó $t\le11$, hay $x^2+y^2\le11x$. Với mỗi $x=1,\ldots,11$, số giá trị $y$ là $2\lfloor\sqrt{x(11-x)}\rfloor+1$; tổng bằng 95.</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="n">
+        <v>708</v>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>p203_q48</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Xét các số thực không âm $x,y$ thỏa mãn $2x+y\cdot4^{x+y-1}\ge3$. Giá trị nhỏ nhất của $P=x^2+y^2+x+y$ bằng
+A. $P_{\min}=\dfrac{29}{8}$.
+B. $P_{\min}=\dfrac{21}{8}$.
+C. $P_{\min}=\dfrac{13}{8}$.
+D. $P_{\min}=\dfrac{21}{4}$.</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>B. $P_{\min}=\dfrac{21}{8}$.</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>Đặt $s=x+y$. Nếu $s&lt;3/2$ thì $4^{s-1}&lt;2$, nên $2x+y4^{s-1}&lt;2x+2y&lt;3$, trái điều kiện. Nếu $s\ge3/2$ thì $4^{s-1}\ge2$ và điều kiện được thỏa mãn. Vậy miền khả thi là $x,y\ge0$, $x+y\ge3/2$. Với $x\ge3/2$, $P\ge(3/2)^2+1(3/2)=\dfrac{15}{4}$. Với $0\le x&lt;3/2$, ta có $y\ge3/2-x$; do $y^2+1y$ tăng theo $y\ge0$, P không nhỏ hơn giá trị trên biên $y=3/2-x$. Giá trị này nhỏ nhất tại $x=\dfrac{3}{4}$, bằng $P_{\min}=\dfrac{21}{8}&lt;\dfrac{15}{4}$. Đây là GTNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="n">
+        <v>709</v>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>p203_q48</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Xét các số thực không âm $x,y$ thỏa mãn $2x+y\cdot4^{x+y-1}\ge3$. Giá trị nhỏ nhất của $P=x^2+y^2+x+2y$ bằng
+A. $P_{\min}=\dfrac{13}{2}$.
+B. $P_{\min}=\dfrac{9}{4}$.
+C. $P_{\min}=\dfrac{13}{4}$.
+D. $P_{\min}=\dfrac{17}{4}$.</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>C. $P_{\min}=\dfrac{13}{4}$.</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>Đặt $s=x+y$. Nếu $s&lt;3/2$ thì $4^{s-1}&lt;2$, nên $2x+y4^{s-1}&lt;2x+2y&lt;3$, trái điều kiện. Nếu $s\ge3/2$ thì $4^{s-1}\ge2$ và điều kiện được thỏa mãn. Vậy miền khả thi là $x,y\ge0$, $x+y\ge3/2$. Với $x\ge3/2$, $P\ge(3/2)^2+1(3/2)=\dfrac{15}{4}$. Với $0\le x&lt;3/2$, ta có $y\ge3/2-x$; do $y^2+2y$ tăng theo $y\ge0$, P không nhỏ hơn giá trị trên biên $y=3/2-x$. Giá trị này nhỏ nhất tại $x=1$, bằng $P_{\min}=\dfrac{13}{4}&lt;\dfrac{15}{4}$. Đây là GTNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="n">
+        <v>710</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>p203_q48</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Xét các số thực không âm $x,y$ thỏa mãn $2x+y\cdot4^{x+y-1}\ge3$. Giá trị nhỏ nhất của $P=x^2+y^2+x+3y$ bằng
+A. $P_{\min}=\dfrac{29}{4}$.
+B. $P_{\min}=\dfrac{21}{8}$.
+C. $P_{\min}=\dfrac{37}{8}$.
+D. $P_{\min}=\dfrac{29}{8}$.</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>D. $P_{\min}=\dfrac{29}{8}$.</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>Đặt $s=x+y$. Nếu $s&lt;3/2$ thì $4^{s-1}&lt;2$, nên $2x+y4^{s-1}&lt;2x+2y&lt;3$, trái điều kiện. Nếu $s\ge3/2$ thì $4^{s-1}\ge2$ và điều kiện được thỏa mãn. Vậy miền khả thi là $x,y\ge0$, $x+y\ge3/2$. Với $x\ge3/2$, $P\ge(3/2)^2+1(3/2)=\dfrac{15}{4}$. Với $0\le x&lt;3/2$, ta có $y\ge3/2-x$; do $y^2+3y$ tăng theo $y\ge0$, P không nhỏ hơn giá trị trên biên $y=3/2-x$. Giá trị này nhỏ nhất tại $x=\dfrac{5}{4}$, bằng $P_{\min}=\dfrac{29}{8}&lt;\dfrac{15}{4}$. Đây là GTNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="n">
+        <v>711</v>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>p203_q48</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Xét các số thực không âm $x,y$ thỏa mãn $2x+y\cdot4^{x+y-1}\ge3$. Giá trị nhỏ nhất của $P=x^2+y^2+2x+y$ bằng
+A. $P_{\min}=\dfrac{9}{4}$.
+B. $P_{\min}=\dfrac{13}{4}$.
+C. $P_{\min}=\dfrac{17}{4}$.
+D. $P_{\min}=\dfrac{13}{2}$.</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>B. $P_{\min}=\dfrac{13}{4}$.</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>Đặt $s=x+y$. Nếu $s&lt;3/2$ thì $4^{s-1}&lt;2$, nên $2x+y4^{s-1}&lt;2x+2y&lt;3$, trái điều kiện. Nếu $s\ge3/2$ thì $4^{s-1}\ge2$ và điều kiện được thỏa mãn. Vậy miền khả thi là $x,y\ge0$, $x+y\ge3/2$. Với $x\ge3/2$, $P\ge(3/2)^2+2(3/2)=\dfrac{21}{4}$. Với $0\le x&lt;3/2$, ta có $y\ge3/2-x$; do $y^2+1y$ tăng theo $y\ge0$, P không nhỏ hơn giá trị trên biên $y=3/2-x$. Giá trị này nhỏ nhất tại $x=\dfrac{1}{2}$, bằng $P_{\min}=\dfrac{13}{4}&lt;\dfrac{21}{4}$. Đây là GTNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="n">
+        <v>712</v>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>p203_q48</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Xét các số thực không âm $x,y$ thỏa mãn $2x+y\cdot4^{x+y-1}\ge3$. Giá trị nhỏ nhất của $P=x^2+y^2+2x+2y$ bằng
+A. $P_{\min}=\dfrac{41}{8}$.
+B. $P_{\min}=\dfrac{25}{8}$.
+C. $P_{\min}=\dfrac{33}{8}$.
+D. $P_{\min}=\dfrac{33}{4}$.</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>C. $P_{\min}=\dfrac{33}{8}$.</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>Đặt $s=x+y$. Nếu $s&lt;3/2$ thì $4^{s-1}&lt;2$, nên $2x+y4^{s-1}&lt;2x+2y&lt;3$, trái điều kiện. Nếu $s\ge3/2$ thì $4^{s-1}\ge2$ và điều kiện được thỏa mãn. Vậy miền khả thi là $x,y\ge0$, $x+y\ge3/2$. Với $x\ge3/2$, $P\ge(3/2)^2+2(3/2)=\dfrac{21}{4}$. Với $0\le x&lt;3/2$, ta có $y\ge3/2-x$; do $y^2+2y$ tăng theo $y\ge0$, P không nhỏ hơn giá trị trên biên $y=3/2-x$. Giá trị này nhỏ nhất tại $x=\dfrac{3}{4}$, bằng $P_{\min}=\dfrac{33}{8}&lt;\dfrac{21}{4}$. Đây là GTNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="n">
+        <v>713</v>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>p203_q48</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Xét các số thực không âm $x,y$ thỏa mãn $2x+y\cdot4^{x+y-1}\ge3$. Giá trị nhỏ nhất của $P=x^2+y^2+2x+3y$ bằng
+A. $P_{\min}=\dfrac{19}{4}$.
+B. $P_{\min}=\dfrac{19}{2}$.
+C. $P_{\min}=\dfrac{23}{4}$.
+D. $P_{\min}=\dfrac{15}{4}$.</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>A. $P_{\min}=\dfrac{19}{4}$.</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>Đặt $s=x+y$. Nếu $s&lt;3/2$ thì $4^{s-1}&lt;2$, nên $2x+y4^{s-1}&lt;2x+2y&lt;3$, trái điều kiện. Nếu $s\ge3/2$ thì $4^{s-1}\ge2$ và điều kiện được thỏa mãn. Vậy miền khả thi là $x,y\ge0$, $x+y\ge3/2$. Với $x\ge3/2$, $P\ge(3/2)^2+2(3/2)=\dfrac{21}{4}$. Với $0\le x&lt;3/2$, ta có $y\ge3/2-x$; do $y^2+3y$ tăng theo $y\ge0$, P không nhỏ hơn giá trị trên biên $y=3/2-x$. Giá trị này nhỏ nhất tại $x=1$, bằng $P_{\min}=\dfrac{19}{4}&lt;\dfrac{21}{4}$. Đây là GTNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="n">
+        <v>714</v>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>p203_q48</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Xét các số thực không âm $x,y$ thỏa mãn $2x+y\cdot4^{x+y-1}\ge3$. Giá trị nhỏ nhất của $P=x^2+y^2+2x+4y$ bằng
+A. $P_{\min}=\dfrac{33}{8}$.
+B. $P_{\min}=\dfrac{49}{8}$.
+C. $P_{\min}=\dfrac{41}{4}$.
+D. $P_{\min}=\dfrac{41}{8}$.</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>D. $P_{\min}=\dfrac{41}{8}$.</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>Đặt $s=x+y$. Nếu $s&lt;3/2$ thì $4^{s-1}&lt;2$, nên $2x+y4^{s-1}&lt;2x+2y&lt;3$, trái điều kiện. Nếu $s\ge3/2$ thì $4^{s-1}\ge2$ và điều kiện được thỏa mãn. Vậy miền khả thi là $x,y\ge0$, $x+y\ge3/2$. Với $x\ge3/2$, $P\ge(3/2)^2+2(3/2)=\dfrac{21}{4}$. Với $0\le x&lt;3/2$, ta có $y\ge3/2-x$; do $y^2+4y$ tăng theo $y\ge0$, P không nhỏ hơn giá trị trên biên $y=3/2-x$. Giá trị này nhỏ nhất tại $x=\dfrac{5}{4}$, bằng $P_{\min}=\dfrac{41}{8}&lt;\dfrac{21}{4}$. Đây là GTNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>715</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>p203_q48</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Xét các số thực không âm $x,y$ thỏa mãn $2x+y\cdot4^{x+y-1}\ge3$. Giá trị nhỏ nhất của $P=x^2+y^2+3x+y$ bằng
+A. $P_{\min}=\dfrac{29}{4}$.
+B. $P_{\min}=\dfrac{21}{8}$.
+C. $P_{\min}=\dfrac{37}{8}$.
+D. $P_{\min}=\dfrac{29}{8}$.</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>D. $P_{\min}=\dfrac{29}{8}$.</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>Đặt $s=x+y$. Nếu $s&lt;3/2$ thì $4^{s-1}&lt;2$, nên $2x+y4^{s-1}&lt;2x+2y&lt;3$, trái điều kiện. Nếu $s\ge3/2$ thì $4^{s-1}\ge2$ và điều kiện được thỏa mãn. Vậy miền khả thi là $x,y\ge0$, $x+y\ge3/2$. Với $x\ge3/2$, $P\ge(3/2)^2+3(3/2)=\dfrac{27}{4}$. Với $0\le x&lt;3/2$, ta có $y\ge3/2-x$; do $y^2+1y$ tăng theo $y\ge0$, P không nhỏ hơn giá trị trên biên $y=3/2-x$. Giá trị này nhỏ nhất tại $x=\dfrac{1}{4}$, bằng $P_{\min}=\dfrac{29}{8}&lt;\dfrac{27}{4}$. Đây là GTNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>716</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>p203_q48</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Xét các số thực không âm $x,y$ thỏa mãn $2x+y\cdot4^{x+y-1}\ge3$. Giá trị nhỏ nhất của $P=x^2+y^2+3x+2y$ bằng
+A. $P_{\min}=\dfrac{15}{4}$.
+B. $P_{\min}=\dfrac{19}{2}$.
+C. $P_{\min}=\dfrac{19}{4}$.
+D. $P_{\min}=\dfrac{23}{4}$.</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>C. $P_{\min}=\dfrac{19}{4}$.</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>Đặt $s=x+y$. Nếu $s&lt;3/2$ thì $4^{s-1}&lt;2$, nên $2x+y4^{s-1}&lt;2x+2y&lt;3$, trái điều kiện. Nếu $s\ge3/2$ thì $4^{s-1}\ge2$ và điều kiện được thỏa mãn. Vậy miền khả thi là $x,y\ge0$, $x+y\ge3/2$. Với $x\ge3/2$, $P\ge(3/2)^2+3(3/2)=\dfrac{27}{4}$. Với $0\le x&lt;3/2$, ta có $y\ge3/2-x$; do $y^2+2y$ tăng theo $y\ge0$, P không nhỏ hơn giá trị trên biên $y=3/2-x$. Giá trị này nhỏ nhất tại $x=\dfrac{1}{2}$, bằng $P_{\min}=\dfrac{19}{4}&lt;\dfrac{27}{4}$. Đây là GTNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>717</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>p203_q48</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Xét các số thực không âm $x,y$ thỏa mãn $2x+y\cdot4^{x+y-1}\ge3$. Giá trị nhỏ nhất của $P=x^2+y^2+3x+3y$ bằng
+A. $P_{\min}=\dfrac{37}{8}$.
+B. $P_{\min}=\dfrac{45}{8}$.
+C. $P_{\min}=\dfrac{45}{4}$.
+D. $P_{\min}=\dfrac{53}{8}$.</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>B. $P_{\min}=\dfrac{45}{8}$.</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>Đặt $s=x+y$. Nếu $s&lt;3/2$ thì $4^{s-1}&lt;2$, nên $2x+y4^{s-1}&lt;2x+2y&lt;3$, trái điều kiện. Nếu $s\ge3/2$ thì $4^{s-1}\ge2$ và điều kiện được thỏa mãn. Vậy miền khả thi là $x,y\ge0$, $x+y\ge3/2$. Với $x\ge3/2$, $P\ge(3/2)^2+3(3/2)=\dfrac{27}{4}$. Với $0\le x&lt;3/2$, ta có $y\ge3/2-x$; do $y^2+3y$ tăng theo $y\ge0$, P không nhỏ hơn giá trị trên biên $y=3/2-x$. Giá trị này nhỏ nhất tại $x=\dfrac{3}{4}$, bằng $P_{\min}=\dfrac{45}{8}&lt;\dfrac{27}{4}$. Đây là GTNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>718</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>p203_q48</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Xét các số thực không âm $x,y$ thỏa mãn $2x+y\cdot4^{x+y-1}\ge3$. Giá trị nhỏ nhất của $P=x^2+y^2+3x+4y$ bằng
+A. $P_{\min}=\dfrac{25}{2}$.
+B. $P_{\min}=\dfrac{25}{4}$.
+C. $P_{\min}=\dfrac{21}{4}$.
+D. $P_{\min}=\dfrac{29}{4}$.</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>B. $P_{\min}=\dfrac{25}{4}$.</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>Đặt $s=x+y$. Nếu $s&lt;3/2$ thì $4^{s-1}&lt;2$, nên $2x+y4^{s-1}&lt;2x+2y&lt;3$, trái điều kiện. Nếu $s\ge3/2$ thì $4^{s-1}\ge2$ và điều kiện được thỏa mãn. Vậy miền khả thi là $x,y\ge0$, $x+y\ge3/2$. Với $x\ge3/2$, $P\ge(3/2)^2+3(3/2)=\dfrac{27}{4}$. Với $0\le x&lt;3/2$, ta có $y\ge3/2-x$; do $y^2+4y$ tăng theo $y\ge0$, P không nhỏ hơn giá trị trên biên $y=3/2-x$. Giá trị này nhỏ nhất tại $x=1$, bằng $P_{\min}=\dfrac{25}{4}&lt;\dfrac{27}{4}$. Đây là GTNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>719</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>D78</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>p203_q48</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Xét các số thực không âm $x,y$ thỏa mãn $2x+y\cdot4^{x+y-1}\ge3$. Giá trị nhỏ nhất của $P=x^2+y^2+3x+5y$ bằng
+A. $P_{\min}=\dfrac{53}{8}$.
+B. $P_{\min}=\dfrac{45}{8}$.
+C. $P_{\min}=\dfrac{61}{8}$.
+D. $P_{\min}=\dfrac{53}{4}$.</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>A. $P_{\min}=\dfrac{53}{8}$.</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>Đặt $s=x+y$. Nếu $s&lt;3/2$ thì $4^{s-1}&lt;2$, nên $2x+y4^{s-1}&lt;2x+2y&lt;3$, trái điều kiện. Nếu $s\ge3/2$ thì $4^{s-1}\ge2$ và điều kiện được thỏa mãn. Vậy miền khả thi là $x,y\ge0$, $x+y\ge3/2$. Với $x\ge3/2$, $P\ge(3/2)^2+3(3/2)=\dfrac{27}{4}$. Với $0\le x&lt;3/2$, ta có $y\ge3/2-x$; do $y^2+5y$ tăng theo $y\ge0$, P không nhỏ hơn giá trị trên biên $y=3/2-x$. Giá trị này nhỏ nhất tại $x=\dfrac{5}{4}$, bằng $P_{\min}=\dfrac{53}{8}&lt;\dfrac{27}{4}$. Đây là GTNN.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
+++ b/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_bien_the_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H718"/>
+  <dimension ref="A1:H722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31197,6 +31197,186 @@
         </is>
       </c>
     </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>718</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>D84</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>p216_q45</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $y$ tồn tại sao cho $x\in\left(\dfrac{1}{3};3\right)$ thỏa mãn $27^{3x^2+xy}=(1+xy)27^{9x}$?
+A. $12$.
+B. $10$.
+C. $11$.
+D. $13$.</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>C. $11$.</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>Đặt $g_y(x)=3x-9-\dfrac{\log_{27}(1+xy)}x+y$. Với $y\ge1$, phương trình tương đương $g_y(x)=0$. Ta có $g_y'(x)=3+\dfrac{\ln(1+xy)}{x^2\ln27}-\dfrac{y}{x(1+xy)\ln27}&gt;3-\dfrac1{x^2\ln27}&gt;=3-\dfrac3{\ln3}&gt;0$, nên $g_y$ đồng biến trên $[1/3;3]$. Tại $x=3$, $g_y(U)=y-\dfrac{\log_{27}(1+3y)}{3}&gt;0$, vì $\ln(1+u)&lt;u$ và $\ln27&gt;1$. Do đó phương trình có nghiệm trong khoảng mở khi và chỉ khi $g_y(1/3)&lt;0$, tức là $h(y)=y-\log_3(1+y/3)&lt;8$. Hàm $h$ đồng biến với $y\ge1$ vì $h'(y)=1-1/((y+3)\ln3)&gt;0$. Với $U\in\{3,5,6,7\}$, ta có $h(3U)&lt;3U-1$ và $h(3U+1)&gt;3U-1$; vì vậy các giá trị nguyên dương phù hợp là $y=1,\ldots,9$, gồm $9$ giá trị.
+Nếu $y\le-3$ thì $x&gt;1/3$ kéo theo $1+xy&lt;0$, không thể thỏa mãn. Với $y=0$, phương trình tương đương $3x(x-U)=0$, chỉ có $x=0$ hoặc $x=3$, đều không thuộc khoảng mở. Với $y=-1$ và $y=-2$, xét $F_y(x)=27^{3x^2+(y-9)x}-(1+xy)$ trên $(1/3,-1/y)$. Tại $x=1/3$, $F_y(x)&lt;0$; khi $x$ tiến đến $-1/y$ từ bên trái, $F_y(x)$ tiến đến một giá trị dương. Theo định lý giá trị trung gian, mỗi giá trị $y=-1,-2$ đều cho một nghiệm. Tổng cộng có $3U+2=11$ giá trị nguyên của $y$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>719</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>D84</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>p216_q45</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $y$ tồn tại sao cho $x\in\left(\dfrac{1}{3};5\right)$ thỏa mãn $27^{3x^2+xy}=(1+xy)27^{15x}$?
+A. $19$.
+B. $18$.
+C. $17$.
+D. $16$.</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>C. $17$.</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>Đặt $g_y(x)=3x-15-\dfrac{\log_{27}(1+xy)}x+y$. Với $y\ge1$, phương trình tương đương $g_y(x)=0$. Ta có $g_y'(x)=3+\dfrac{\ln(1+xy)}{x^2\ln27}-\dfrac{y}{x(1+xy)\ln27}&gt;3-\dfrac1{x^2\ln27}&gt;=3-\dfrac3{\ln3}&gt;0$, nên $g_y$ đồng biến trên $[1/3;5]$. Tại $x=5$, $g_y(U)=y-\dfrac{\log_{27}(1+5y)}{5}&gt;0$, vì $\ln(1+u)&lt;u$ và $\ln27&gt;1$. Do đó phương trình có nghiệm trong khoảng mở khi và chỉ khi $g_y(1/3)&lt;0$, tức là $h(y)=y-\log_3(1+y/3)&lt;14$. Hàm $h$ đồng biến với $y\ge1$ vì $h'(y)=1-1/((y+3)\ln3)&gt;0$. Với $U\in\{3,5,6,7\}$, ta có $h(3U)&lt;3U-1$ và $h(3U+1)&gt;3U-1$; vì vậy các giá trị nguyên dương phù hợp là $y=1,\ldots,15$, gồm $15$ giá trị.
+Nếu $y\le-3$ thì $x&gt;1/3$ kéo theo $1+xy&lt;0$, không thể thỏa mãn. Với $y=0$, phương trình tương đương $3x(x-U)=0$, chỉ có $x=0$ hoặc $x=5$, đều không thuộc khoảng mở. Với $y=-1$ và $y=-2$, xét $F_y(x)=27^{3x^2+(y-15)x}-(1+xy)$ trên $(1/3,-1/y)$. Tại $x=1/3$, $F_y(x)&lt;0$; khi $x$ tiến đến $-1/y$ từ bên trái, $F_y(x)$ tiến đến một giá trị dương. Theo định lý giá trị trung gian, mỗi giá trị $y=-1,-2$ đều cho một nghiệm. Tổng cộng có $3U+2=17$ giá trị nguyên của $y$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>720</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>D84</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>p216_q45</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $y$ tồn tại sao cho $x\in\left(\dfrac{1}{3};6\right)$ thỏa mãn $27^{3x^2+xy}=(1+xy)27^{18x}$?
+A. $20$.
+B. $22$.
+C. $21$.
+D. $19$.</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>A. $20$.</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>Đặt $g_y(x)=3x-18-\dfrac{\log_{27}(1+xy)}x+y$. Với $y\ge1$, phương trình tương đương $g_y(x)=0$. Ta có $g_y'(x)=3+\dfrac{\ln(1+xy)}{x^2\ln27}-\dfrac{y}{x(1+xy)\ln27}&gt;3-\dfrac1{x^2\ln27}&gt;=3-\dfrac3{\ln3}&gt;0$, nên $g_y$ đồng biến trên $[1/3;6]$. Tại $x=6$, $g_y(U)=y-\dfrac{\log_{27}(1+6y)}{6}&gt;0$, vì $\ln(1+u)&lt;u$ và $\ln27&gt;1$. Do đó phương trình có nghiệm trong khoảng mở khi và chỉ khi $g_y(1/3)&lt;0$, tức là $h(y)=y-\log_3(1+y/3)&lt;17$. Hàm $h$ đồng biến với $y\ge1$ vì $h'(y)=1-1/((y+3)\ln3)&gt;0$. Với $U\in\{3,5,6,7\}$, ta có $h(3U)&lt;3U-1$ và $h(3U+1)&gt;3U-1$; vì vậy các giá trị nguyên dương phù hợp là $y=1,\ldots,18$, gồm $18$ giá trị.
+Nếu $y\le-3$ thì $x&gt;1/3$ kéo theo $1+xy&lt;0$, không thể thỏa mãn. Với $y=0$, phương trình tương đương $3x(x-U)=0$, chỉ có $x=0$ hoặc $x=6$, đều không thuộc khoảng mở. Với $y=-1$ và $y=-2$, xét $F_y(x)=27^{3x^2+(y-18)x}-(1+xy)$ trên $(1/3,-1/y)$. Tại $x=1/3$, $F_y(x)&lt;0$; khi $x$ tiến đến $-1/y$ từ bên trái, $F_y(x)$ tiến đến một giá trị dương. Theo định lý giá trị trung gian, mỗi giá trị $y=-1,-2$ đều cho một nghiệm. Tổng cộng có $3U+2=20$ giá trị nguyên của $y$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>721</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>D84</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>p216_q45</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>chuan</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Có bao nhiêu số nguyên $y$ tồn tại sao cho $x\in\left(\dfrac{1}{3};7\right)$ thỏa mãn $27^{3x^2+xy}=(1+xy)27^{21x}$?
+A. $24$.
+B. $25$.
+C. $22$.
+D. $23$.</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>D. $23$.</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>Đặt $g_y(x)=3x-21-\dfrac{\log_{27}(1+xy)}x+y$. Với $y\ge1$, phương trình tương đương $g_y(x)=0$. Ta có $g_y'(x)=3+\dfrac{\ln(1+xy)}{x^2\ln27}-\dfrac{y}{x(1+xy)\ln27}&gt;3-\dfrac1{x^2\ln27}&gt;=3-\dfrac3{\ln3}&gt;0$, nên $g_y$ đồng biến trên $[1/3;7]$. Tại $x=7$, $g_y(U)=y-\dfrac{\log_{27}(1+7y)}{7}&gt;0$, vì $\ln(1+u)&lt;u$ và $\ln27&gt;1$. Do đó phương trình có nghiệm trong khoảng mở khi và chỉ khi $g_y(1/3)&lt;0$, tức là $h(y)=y-\log_3(1+y/3)&lt;20$. Hàm $h$ đồng biến với $y\ge1$ vì $h'(y)=1-1/((y+3)\ln3)&gt;0$. Với $U\in\{3,5,6,7\}$, ta có $h(3U)&lt;3U-1$ và $h(3U+1)&gt;3U-1$; vì vậy các giá trị nguyên dương phù hợp là $y=1,\ldots,21$, gồm $21$ giá trị.
+Nếu $y\le-3$ thì $x&gt;1/3$ kéo theo $1+xy&lt;0$, không thể thỏa mãn. Với $y=0$, phương trình tương đương $3x(x-U)=0$, chỉ có $x=0$ hoặc $x=7$, đều không thuộc khoảng mở. Với $y=-1$ và $y=-2$, xét $F_y(x)=27^{3x^2+(y-21)x}-(1+xy)$ trên $(1/3,-1/y)$. Tại $x=1/3$, $F_y(x)&lt;0$; khi $x$ tiến đến $-1/y$ từ bên trái, $F_y(x)$ tiến đến một giá trị dương. Theo định lý giá trị trung gian, mỗi giá trị $y=-1,-2$ đều cho một nghiệm. Tổng cộng có $3U+2=23$ giá trị nguyên của $y$.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
